--- a/src/inventory/Cum.xlsx
+++ b/src/inventory/Cum.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="926">
   <si>
     <t>Code/SKU</t>
   </si>
@@ -1352,7 +1352,7 @@
     <t>৳322.50</t>
   </si>
   <si>
-    <t>৳967.50</t>
+    <t>৳790.00</t>
   </si>
   <si>
     <t>৳229.24</t>
@@ -2696,10 +2696,13 @@
     <t>Formal Shirt 003</t>
   </si>
   <si>
+    <t>৳8,940.00</t>
+  </si>
+  <si>
+    <t>৳7,450.00</t>
+  </si>
+  <si>
     <t>৳10,430.00</t>
-  </si>
-  <si>
-    <t>৳7,450.00</t>
   </si>
   <si>
     <t>৳14,900.00</t>
@@ -3129,7 +3132,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I458"/>
+  <dimension ref="A1:I457"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -7238,16 +7241,16 @@
         <v>278</v>
       </c>
       <c r="F160">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G160" t="s">
         <v>444</v>
       </c>
       <c r="H160" t="s">
+        <v>444</v>
+      </c>
+      <c r="I160" t="s">
         <v>445</v>
-      </c>
-      <c r="I160" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -9645,16 +9648,16 @@
         <v>379</v>
       </c>
       <c r="F255">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G255" t="s">
         <v>711</v>
       </c>
       <c r="H255" t="s">
-        <v>125</v>
+        <v>711</v>
       </c>
       <c r="I255" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="256" spans="1:9">
@@ -11866,62 +11869,62 @@
     </row>
     <row r="341" spans="1:9">
       <c r="A341" t="s">
-        <v>681</v>
+        <v>792</v>
       </c>
       <c r="B341" t="s">
-        <v>682</v>
+        <v>793</v>
       </c>
       <c r="C341" t="s">
-        <v>404</v>
+        <v>118</v>
       </c>
       <c r="E341" t="s">
-        <v>539</v>
+        <v>699</v>
       </c>
       <c r="F341">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G341" t="s">
-        <v>535</v>
+        <v>16</v>
       </c>
       <c r="H341" t="s">
-        <v>535</v>
+        <v>16</v>
       </c>
       <c r="I341" t="s">
-        <v>798</v>
+        <v>748</v>
       </c>
     </row>
     <row r="342" spans="1:9">
       <c r="A342" t="s">
-        <v>792</v>
+        <v>764</v>
       </c>
       <c r="B342" t="s">
-        <v>793</v>
+        <v>765</v>
       </c>
       <c r="C342" t="s">
-        <v>118</v>
+        <v>404</v>
       </c>
       <c r="E342" t="s">
-        <v>699</v>
+        <v>539</v>
       </c>
       <c r="F342">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G342" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="H342" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="I342" t="s">
-        <v>748</v>
+        <v>730</v>
       </c>
     </row>
     <row r="343" spans="1:9">
       <c r="A343" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="B343" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="C343" t="s">
         <v>404</v>
@@ -11930,131 +11933,131 @@
         <v>539</v>
       </c>
       <c r="F343">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G343" t="s">
         <v>535</v>
       </c>
       <c r="H343" t="s">
-        <v>74</v>
+        <v>535</v>
       </c>
       <c r="I343" t="s">
-        <v>730</v>
+        <v>151</v>
       </c>
     </row>
     <row r="344" spans="1:9">
       <c r="A344" t="s">
-        <v>731</v>
+        <v>448</v>
       </c>
       <c r="B344" t="s">
-        <v>732</v>
+        <v>449</v>
       </c>
       <c r="C344" t="s">
-        <v>404</v>
+        <v>104</v>
       </c>
       <c r="E344" t="s">
-        <v>539</v>
+        <v>346</v>
       </c>
       <c r="F344">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G344" t="s">
-        <v>535</v>
+        <v>829</v>
       </c>
       <c r="H344" t="s">
-        <v>535</v>
+        <v>830</v>
       </c>
       <c r="I344" t="s">
-        <v>151</v>
+        <v>452</v>
       </c>
     </row>
     <row r="345" spans="1:9">
       <c r="A345" t="s">
-        <v>448</v>
+        <v>768</v>
       </c>
       <c r="B345" t="s">
-        <v>449</v>
+        <v>769</v>
       </c>
       <c r="C345" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="E345" t="s">
         <v>346</v>
       </c>
       <c r="F345">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="G345" t="s">
-        <v>829</v>
+        <v>16</v>
       </c>
       <c r="H345" t="s">
-        <v>830</v>
+        <v>16</v>
       </c>
       <c r="I345" t="s">
-        <v>452</v>
+        <v>495</v>
       </c>
     </row>
     <row r="346" spans="1:9">
       <c r="A346" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="B346" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="C346" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E346" t="s">
-        <v>346</v>
+        <v>699</v>
       </c>
       <c r="F346">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="G346" t="s">
-        <v>16</v>
+        <v>785</v>
       </c>
       <c r="H346" t="s">
-        <v>16</v>
+        <v>831</v>
       </c>
       <c r="I346" t="s">
-        <v>495</v>
+        <v>725</v>
       </c>
     </row>
     <row r="347" spans="1:9">
       <c r="A347" t="s">
-        <v>783</v>
+        <v>832</v>
       </c>
       <c r="B347" t="s">
-        <v>784</v>
+        <v>833</v>
       </c>
       <c r="C347" t="s">
-        <v>118</v>
+        <v>378</v>
       </c>
       <c r="E347" t="s">
-        <v>699</v>
+        <v>539</v>
       </c>
       <c r="F347">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="G347" t="s">
-        <v>785</v>
+        <v>648</v>
       </c>
       <c r="H347" t="s">
-        <v>831</v>
+        <v>749</v>
       </c>
       <c r="I347" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
     </row>
     <row r="348" spans="1:9">
       <c r="A348" t="s">
-        <v>832</v>
+        <v>651</v>
       </c>
       <c r="B348" t="s">
-        <v>833</v>
+        <v>652</v>
       </c>
       <c r="C348" t="s">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="E348" t="s">
         <v>539</v>
@@ -12069,18 +12072,18 @@
         <v>749</v>
       </c>
       <c r="I348" t="s">
-        <v>730</v>
+        <v>750</v>
       </c>
     </row>
     <row r="349" spans="1:9">
       <c r="A349" t="s">
-        <v>651</v>
+        <v>834</v>
       </c>
       <c r="B349" t="s">
-        <v>652</v>
+        <v>835</v>
       </c>
       <c r="C349" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="E349" t="s">
         <v>539</v>
@@ -12100,13 +12103,13 @@
     </row>
     <row r="350" spans="1:9">
       <c r="A350" t="s">
-        <v>834</v>
+        <v>802</v>
       </c>
       <c r="B350" t="s">
-        <v>835</v>
+        <v>803</v>
       </c>
       <c r="C350" t="s">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="E350" t="s">
         <v>539</v>
@@ -12121,102 +12124,102 @@
         <v>749</v>
       </c>
       <c r="I350" t="s">
-        <v>750</v>
+        <v>159</v>
       </c>
     </row>
     <row r="351" spans="1:9">
       <c r="A351" t="s">
-        <v>802</v>
+        <v>836</v>
       </c>
       <c r="B351" t="s">
-        <v>803</v>
+        <v>837</v>
       </c>
       <c r="C351" t="s">
-        <v>426</v>
+        <v>118</v>
       </c>
       <c r="E351" t="s">
-        <v>539</v>
+        <v>346</v>
       </c>
       <c r="F351">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="G351" t="s">
-        <v>648</v>
+        <v>838</v>
       </c>
       <c r="H351" t="s">
-        <v>749</v>
+        <v>839</v>
       </c>
       <c r="I351" t="s">
-        <v>159</v>
+        <v>809</v>
       </c>
     </row>
     <row r="352" spans="1:9">
       <c r="A352" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
       <c r="B352" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
       <c r="C352" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E352" t="s">
-        <v>346</v>
+        <v>699</v>
       </c>
       <c r="F352">
         <v>8.0</v>
       </c>
       <c r="G352" t="s">
-        <v>838</v>
+        <v>785</v>
       </c>
       <c r="H352" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="I352" t="s">
-        <v>809</v>
+        <v>840</v>
       </c>
     </row>
     <row r="353" spans="1:9">
       <c r="A353" t="s">
-        <v>824</v>
+        <v>712</v>
       </c>
       <c r="B353" t="s">
-        <v>825</v>
+        <v>713</v>
       </c>
       <c r="C353" t="s">
         <v>108</v>
       </c>
       <c r="E353" t="s">
-        <v>699</v>
+        <v>241</v>
       </c>
       <c r="F353">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="G353" t="s">
-        <v>785</v>
+        <v>16</v>
       </c>
       <c r="H353" t="s">
-        <v>831</v>
+        <v>16</v>
       </c>
       <c r="I353" t="s">
-        <v>840</v>
+        <v>398</v>
       </c>
     </row>
     <row r="354" spans="1:9">
       <c r="A354" t="s">
-        <v>712</v>
+        <v>800</v>
       </c>
       <c r="B354" t="s">
-        <v>713</v>
+        <v>801</v>
       </c>
       <c r="C354" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="E354" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="F354">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G354" t="s">
         <v>16</v>
@@ -12225,24 +12228,24 @@
         <v>16</v>
       </c>
       <c r="I354" t="s">
-        <v>398</v>
+        <v>617</v>
       </c>
     </row>
     <row r="355" spans="1:9">
       <c r="A355" t="s">
-        <v>800</v>
+        <v>712</v>
       </c>
       <c r="B355" t="s">
-        <v>801</v>
+        <v>713</v>
       </c>
       <c r="C355" t="s">
         <v>119</v>
       </c>
       <c r="E355" t="s">
-        <v>346</v>
+        <v>241</v>
       </c>
       <c r="F355">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G355" t="s">
         <v>16</v>
@@ -12251,24 +12254,24 @@
         <v>16</v>
       </c>
       <c r="I355" t="s">
-        <v>617</v>
+        <v>398</v>
       </c>
     </row>
     <row r="356" spans="1:9">
       <c r="A356" t="s">
-        <v>712</v>
+        <v>792</v>
       </c>
       <c r="B356" t="s">
-        <v>713</v>
+        <v>793</v>
       </c>
       <c r="C356" t="s">
         <v>119</v>
       </c>
       <c r="E356" t="s">
-        <v>241</v>
+        <v>699</v>
       </c>
       <c r="F356">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G356" t="s">
         <v>16</v>
@@ -12277,24 +12280,24 @@
         <v>16</v>
       </c>
       <c r="I356" t="s">
-        <v>398</v>
+        <v>720</v>
       </c>
     </row>
     <row r="357" spans="1:9">
       <c r="A357" t="s">
-        <v>792</v>
+        <v>768</v>
       </c>
       <c r="B357" t="s">
-        <v>793</v>
+        <v>769</v>
       </c>
       <c r="C357" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E357" t="s">
-        <v>699</v>
+        <v>346</v>
       </c>
       <c r="F357">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G357" t="s">
         <v>16</v>
@@ -12303,59 +12306,59 @@
         <v>16</v>
       </c>
       <c r="I357" t="s">
-        <v>720</v>
+        <v>514</v>
       </c>
     </row>
     <row r="358" spans="1:9">
       <c r="A358" t="s">
-        <v>768</v>
+        <v>723</v>
       </c>
       <c r="B358" t="s">
-        <v>769</v>
+        <v>724</v>
       </c>
       <c r="C358" t="s">
-        <v>118</v>
+        <v>404</v>
       </c>
       <c r="E358" t="s">
-        <v>346</v>
+        <v>539</v>
       </c>
       <c r="F358">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G358" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="H358" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="I358" t="s">
-        <v>514</v>
+        <v>841</v>
       </c>
     </row>
     <row r="359" spans="1:9">
       <c r="A359" t="s">
-        <v>723</v>
+        <v>783</v>
       </c>
       <c r="B359" t="s">
-        <v>724</v>
+        <v>784</v>
       </c>
       <c r="C359" t="s">
-        <v>404</v>
+        <v>119</v>
       </c>
       <c r="E359" t="s">
-        <v>539</v>
+        <v>699</v>
       </c>
       <c r="F359">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
       <c r="G359" t="s">
-        <v>535</v>
+        <v>16</v>
       </c>
       <c r="H359" t="s">
-        <v>535</v>
+        <v>16</v>
       </c>
       <c r="I359" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="360" spans="1:9">
@@ -12366,13 +12369,13 @@
         <v>784</v>
       </c>
       <c r="C360" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="E360" t="s">
         <v>699</v>
       </c>
       <c r="F360">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G360" t="s">
         <v>16</v>
@@ -12381,41 +12384,41 @@
         <v>16</v>
       </c>
       <c r="I360" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="361" spans="1:9">
       <c r="A361" t="s">
-        <v>783</v>
+        <v>640</v>
       </c>
       <c r="B361" t="s">
-        <v>784</v>
+        <v>641</v>
       </c>
       <c r="C361" t="s">
-        <v>104</v>
+        <v>404</v>
       </c>
       <c r="E361" t="s">
-        <v>699</v>
+        <v>539</v>
       </c>
       <c r="F361">
-        <v>18.0</v>
+        <v>1.0</v>
       </c>
       <c r="G361" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="H361" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="I361" t="s">
-        <v>843</v>
+        <v>798</v>
       </c>
     </row>
     <row r="362" spans="1:9">
       <c r="A362" t="s">
-        <v>640</v>
+        <v>728</v>
       </c>
       <c r="B362" t="s">
-        <v>641</v>
+        <v>729</v>
       </c>
       <c r="C362" t="s">
         <v>404</v>
@@ -12438,54 +12441,54 @@
     </row>
     <row r="363" spans="1:9">
       <c r="A363" t="s">
-        <v>728</v>
+        <v>844</v>
       </c>
       <c r="B363" t="s">
-        <v>729</v>
+        <v>845</v>
       </c>
       <c r="C363" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="E363" t="s">
         <v>539</v>
       </c>
       <c r="F363">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G363" t="s">
-        <v>535</v>
+        <v>648</v>
       </c>
       <c r="H363" t="s">
-        <v>535</v>
+        <v>749</v>
       </c>
       <c r="I363" t="s">
-        <v>798</v>
+        <v>159</v>
       </c>
     </row>
     <row r="364" spans="1:9">
       <c r="A364" t="s">
-        <v>844</v>
+        <v>787</v>
       </c>
       <c r="B364" t="s">
-        <v>845</v>
+        <v>788</v>
       </c>
       <c r="C364" t="s">
-        <v>378</v>
+        <v>277</v>
       </c>
       <c r="E364" t="s">
         <v>539</v>
       </c>
       <c r="F364">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G364" t="s">
         <v>648</v>
       </c>
       <c r="H364" t="s">
-        <v>749</v>
+        <v>648</v>
       </c>
       <c r="I364" t="s">
-        <v>159</v>
+        <v>549</v>
       </c>
     </row>
     <row r="365" spans="1:9">
@@ -12496,33 +12499,33 @@
         <v>788</v>
       </c>
       <c r="C365" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="E365" t="s">
         <v>539</v>
       </c>
       <c r="F365">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G365" t="s">
         <v>648</v>
       </c>
       <c r="H365" t="s">
-        <v>648</v>
+        <v>749</v>
       </c>
       <c r="I365" t="s">
-        <v>549</v>
+        <v>159</v>
       </c>
     </row>
     <row r="366" spans="1:9">
       <c r="A366" t="s">
-        <v>787</v>
+        <v>817</v>
       </c>
       <c r="B366" t="s">
-        <v>788</v>
+        <v>818</v>
       </c>
       <c r="C366" t="s">
-        <v>426</v>
+        <v>325</v>
       </c>
       <c r="E366" t="s">
         <v>539</v>
@@ -12548,7 +12551,7 @@
         <v>818</v>
       </c>
       <c r="C367" t="s">
-        <v>325</v>
+        <v>426</v>
       </c>
       <c r="E367" t="s">
         <v>539</v>
@@ -12568,97 +12571,97 @@
     </row>
     <row r="368" spans="1:9">
       <c r="A368" t="s">
-        <v>817</v>
+        <v>800</v>
       </c>
       <c r="B368" t="s">
-        <v>818</v>
+        <v>801</v>
       </c>
       <c r="C368" t="s">
-        <v>426</v>
+        <v>108</v>
       </c>
       <c r="E368" t="s">
-        <v>539</v>
+        <v>346</v>
       </c>
       <c r="F368">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="G368" t="s">
-        <v>648</v>
+        <v>16</v>
       </c>
       <c r="H368" t="s">
-        <v>749</v>
+        <v>16</v>
       </c>
       <c r="I368" t="s">
-        <v>159</v>
+        <v>745</v>
       </c>
     </row>
     <row r="369" spans="1:9">
       <c r="A369" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="B369" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="C369" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="E369" t="s">
         <v>346</v>
       </c>
       <c r="F369">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G369" t="s">
-        <v>16</v>
+        <v>846</v>
       </c>
       <c r="H369" t="s">
-        <v>16</v>
+        <v>846</v>
       </c>
       <c r="I369" t="s">
-        <v>745</v>
+        <v>676</v>
       </c>
     </row>
     <row r="370" spans="1:9">
       <c r="A370" t="s">
-        <v>805</v>
+        <v>836</v>
       </c>
       <c r="B370" t="s">
-        <v>806</v>
+        <v>837</v>
       </c>
       <c r="C370" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="E370" t="s">
         <v>346</v>
       </c>
       <c r="F370">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G370" t="s">
-        <v>846</v>
+        <v>16</v>
       </c>
       <c r="H370" t="s">
-        <v>846</v>
+        <v>16</v>
       </c>
       <c r="I370" t="s">
-        <v>676</v>
+        <v>809</v>
       </c>
     </row>
     <row r="371" spans="1:9">
       <c r="A371" t="s">
-        <v>836</v>
+        <v>847</v>
       </c>
       <c r="B371" t="s">
-        <v>837</v>
+        <v>848</v>
       </c>
       <c r="C371" t="s">
-        <v>104</v>
+        <v>240</v>
       </c>
       <c r="E371" t="s">
-        <v>346</v>
+        <v>241</v>
       </c>
       <c r="F371">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="G371" t="s">
         <v>16</v>
@@ -12667,24 +12670,24 @@
         <v>16</v>
       </c>
       <c r="I371" t="s">
-        <v>809</v>
+        <v>292</v>
       </c>
     </row>
     <row r="372" spans="1:9">
       <c r="A372" t="s">
-        <v>847</v>
+        <v>836</v>
       </c>
       <c r="B372" t="s">
-        <v>848</v>
+        <v>837</v>
       </c>
       <c r="C372" t="s">
-        <v>240</v>
+        <v>119</v>
       </c>
       <c r="E372" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="F372">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="G372" t="s">
         <v>16</v>
@@ -12693,24 +12696,24 @@
         <v>16</v>
       </c>
       <c r="I372" t="s">
-        <v>292</v>
+        <v>355</v>
       </c>
     </row>
     <row r="373" spans="1:9">
       <c r="A373" t="s">
-        <v>836</v>
+        <v>739</v>
       </c>
       <c r="B373" t="s">
-        <v>837</v>
+        <v>740</v>
       </c>
       <c r="C373" t="s">
         <v>119</v>
       </c>
       <c r="E373" t="s">
-        <v>346</v>
+        <v>699</v>
       </c>
       <c r="F373">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G373" t="s">
         <v>16</v>
@@ -12719,44 +12722,44 @@
         <v>16</v>
       </c>
       <c r="I373" t="s">
-        <v>355</v>
+        <v>479</v>
       </c>
     </row>
     <row r="374" spans="1:9">
       <c r="A374" t="s">
-        <v>739</v>
+        <v>832</v>
       </c>
       <c r="B374" t="s">
-        <v>740</v>
+        <v>833</v>
       </c>
       <c r="C374" t="s">
-        <v>119</v>
+        <v>426</v>
       </c>
       <c r="E374" t="s">
-        <v>699</v>
+        <v>539</v>
       </c>
       <c r="F374">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G374" t="s">
-        <v>16</v>
+        <v>648</v>
       </c>
       <c r="H374" t="s">
-        <v>16</v>
+        <v>648</v>
       </c>
       <c r="I374" t="s">
-        <v>479</v>
+        <v>798</v>
       </c>
     </row>
     <row r="375" spans="1:9">
       <c r="A375" t="s">
-        <v>832</v>
+        <v>813</v>
       </c>
       <c r="B375" t="s">
-        <v>833</v>
+        <v>814</v>
       </c>
       <c r="C375" t="s">
-        <v>426</v>
+        <v>277</v>
       </c>
       <c r="E375" t="s">
         <v>539</v>
@@ -12771,18 +12774,18 @@
         <v>648</v>
       </c>
       <c r="I375" t="s">
-        <v>798</v>
+        <v>841</v>
       </c>
     </row>
     <row r="376" spans="1:9">
       <c r="A376" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B376" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C376" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="E376" t="s">
         <v>539</v>
@@ -12797,15 +12800,15 @@
         <v>648</v>
       </c>
       <c r="I376" t="s">
-        <v>841</v>
+        <v>151</v>
       </c>
     </row>
     <row r="377" spans="1:9">
       <c r="A377" t="s">
-        <v>815</v>
+        <v>844</v>
       </c>
       <c r="B377" t="s">
-        <v>816</v>
+        <v>845</v>
       </c>
       <c r="C377" t="s">
         <v>426</v>
@@ -12814,105 +12817,105 @@
         <v>539</v>
       </c>
       <c r="F377">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G377" t="s">
         <v>648</v>
       </c>
       <c r="H377" t="s">
-        <v>648</v>
+        <v>749</v>
       </c>
       <c r="I377" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="378" spans="1:9">
       <c r="A378" t="s">
-        <v>844</v>
+        <v>802</v>
       </c>
       <c r="B378" t="s">
-        <v>845</v>
+        <v>803</v>
       </c>
       <c r="C378" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="E378" t="s">
         <v>539</v>
       </c>
       <c r="F378">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G378" t="s">
         <v>648</v>
       </c>
       <c r="H378" t="s">
-        <v>749</v>
+        <v>648</v>
       </c>
       <c r="I378" t="s">
-        <v>159</v>
+        <v>549</v>
       </c>
     </row>
     <row r="379" spans="1:9">
       <c r="A379" t="s">
-        <v>802</v>
+        <v>522</v>
       </c>
       <c r="B379" t="s">
-        <v>803</v>
+        <v>523</v>
       </c>
       <c r="C379" t="s">
-        <v>404</v>
+        <v>119</v>
       </c>
       <c r="E379" t="s">
-        <v>539</v>
+        <v>346</v>
       </c>
       <c r="F379">
-        <v>1.0</v>
+        <v>22.0</v>
       </c>
       <c r="G379" t="s">
-        <v>648</v>
+        <v>849</v>
       </c>
       <c r="H379" t="s">
-        <v>648</v>
+        <v>850</v>
       </c>
       <c r="I379" t="s">
-        <v>549</v>
+        <v>359</v>
       </c>
     </row>
     <row r="380" spans="1:9">
       <c r="A380" t="s">
-        <v>522</v>
+        <v>815</v>
       </c>
       <c r="B380" t="s">
-        <v>523</v>
+        <v>816</v>
       </c>
       <c r="C380" t="s">
-        <v>119</v>
+        <v>404</v>
       </c>
       <c r="E380" t="s">
-        <v>346</v>
+        <v>539</v>
       </c>
       <c r="F380">
-        <v>22.0</v>
+        <v>1.0</v>
       </c>
       <c r="G380" t="s">
-        <v>849</v>
+        <v>648</v>
       </c>
       <c r="H380" t="s">
-        <v>850</v>
+        <v>648</v>
       </c>
       <c r="I380" t="s">
-        <v>359</v>
+        <v>151</v>
       </c>
     </row>
     <row r="381" spans="1:9">
       <c r="A381" t="s">
-        <v>815</v>
+        <v>844</v>
       </c>
       <c r="B381" t="s">
-        <v>816</v>
+        <v>845</v>
       </c>
       <c r="C381" t="s">
-        <v>404</v>
+        <v>325</v>
       </c>
       <c r="E381" t="s">
         <v>539</v>
@@ -12927,18 +12930,18 @@
         <v>648</v>
       </c>
       <c r="I381" t="s">
-        <v>151</v>
+        <v>549</v>
       </c>
     </row>
     <row r="382" spans="1:9">
       <c r="A382" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
       <c r="B382" t="s">
-        <v>845</v>
+        <v>835</v>
       </c>
       <c r="C382" t="s">
-        <v>325</v>
+        <v>426</v>
       </c>
       <c r="E382" t="s">
         <v>539</v>
@@ -12953,7 +12956,7 @@
         <v>648</v>
       </c>
       <c r="I382" t="s">
-        <v>549</v>
+        <v>151</v>
       </c>
     </row>
     <row r="383" spans="1:9">
@@ -12964,7 +12967,7 @@
         <v>835</v>
       </c>
       <c r="C383" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="E383" t="s">
         <v>539</v>
@@ -12984,10 +12987,10 @@
     </row>
     <row r="384" spans="1:9">
       <c r="A384" t="s">
-        <v>834</v>
+        <v>787</v>
       </c>
       <c r="B384" t="s">
-        <v>835</v>
+        <v>788</v>
       </c>
       <c r="C384" t="s">
         <v>404</v>
@@ -13005,18 +13008,18 @@
         <v>648</v>
       </c>
       <c r="I384" t="s">
-        <v>151</v>
+        <v>549</v>
       </c>
     </row>
     <row r="385" spans="1:9">
       <c r="A385" t="s">
-        <v>787</v>
+        <v>802</v>
       </c>
       <c r="B385" t="s">
-        <v>788</v>
+        <v>803</v>
       </c>
       <c r="C385" t="s">
-        <v>404</v>
+        <v>277</v>
       </c>
       <c r="E385" t="s">
         <v>539</v>
@@ -13036,10 +13039,10 @@
     </row>
     <row r="386" spans="1:9">
       <c r="A386" t="s">
-        <v>802</v>
+        <v>851</v>
       </c>
       <c r="B386" t="s">
-        <v>803</v>
+        <v>852</v>
       </c>
       <c r="C386" t="s">
         <v>277</v>
@@ -13057,7 +13060,7 @@
         <v>648</v>
       </c>
       <c r="I386" t="s">
-        <v>549</v>
+        <v>798</v>
       </c>
     </row>
     <row r="387" spans="1:9">
@@ -13068,7 +13071,7 @@
         <v>852</v>
       </c>
       <c r="C387" t="s">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="E387" t="s">
         <v>539</v>
@@ -13088,71 +13091,68 @@
     </row>
     <row r="388" spans="1:9">
       <c r="A388" t="s">
-        <v>851</v>
+        <v>776</v>
       </c>
       <c r="B388" t="s">
-        <v>852</v>
+        <v>777</v>
       </c>
       <c r="C388" t="s">
-        <v>378</v>
+        <v>104</v>
       </c>
       <c r="E388" t="s">
-        <v>539</v>
+        <v>699</v>
       </c>
       <c r="F388">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G388" t="s">
-        <v>648</v>
+        <v>853</v>
       </c>
       <c r="H388" t="s">
-        <v>648</v>
+        <v>854</v>
       </c>
       <c r="I388" t="s">
-        <v>798</v>
+        <v>855</v>
       </c>
     </row>
     <row r="389" spans="1:9">
       <c r="A389" t="s">
-        <v>776</v>
+        <v>856</v>
       </c>
       <c r="B389" t="s">
-        <v>777</v>
-      </c>
-      <c r="C389" t="s">
-        <v>104</v>
+        <v>857</v>
+      </c>
+      <c r="C389">
+        <v>40</v>
       </c>
       <c r="E389" t="s">
-        <v>699</v>
+        <v>858</v>
       </c>
       <c r="F389">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G389" t="s">
-        <v>853</v>
+        <v>16</v>
       </c>
       <c r="H389" t="s">
-        <v>854</v>
+        <v>16</v>
       </c>
       <c r="I389" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
     </row>
     <row r="390" spans="1:9">
       <c r="A390" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="B390" t="s">
-        <v>857</v>
-      </c>
-      <c r="C390">
-        <v>40</v>
+        <v>861</v>
       </c>
       <c r="E390" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="F390">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G390" t="s">
         <v>16</v>
@@ -13161,21 +13161,21 @@
         <v>16</v>
       </c>
       <c r="I390" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
     </row>
     <row r="391" spans="1:9">
       <c r="A391" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="B391" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="E391" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="F391">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G391" t="s">
         <v>16</v>
@@ -13184,21 +13184,24 @@
         <v>16</v>
       </c>
       <c r="I391" t="s">
-        <v>863</v>
+        <v>755</v>
       </c>
     </row>
     <row r="392" spans="1:9">
       <c r="A392" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B392" t="s">
-        <v>865</v>
+        <v>868</v>
+      </c>
+      <c r="C392" t="s">
+        <v>119</v>
       </c>
       <c r="E392" t="s">
-        <v>866</v>
+        <v>230</v>
       </c>
       <c r="F392">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
       <c r="G392" t="s">
         <v>16</v>
@@ -13207,7 +13210,7 @@
         <v>16</v>
       </c>
       <c r="I392" t="s">
-        <v>755</v>
+        <v>869</v>
       </c>
     </row>
     <row r="393" spans="1:9">
@@ -13218,13 +13221,13 @@
         <v>868</v>
       </c>
       <c r="C393" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="E393" t="s">
         <v>230</v>
       </c>
       <c r="F393">
-        <v>17.0</v>
+        <v>9.0</v>
       </c>
       <c r="G393" t="s">
         <v>16</v>
@@ -13233,24 +13236,24 @@
         <v>16</v>
       </c>
       <c r="I393" t="s">
-        <v>869</v>
+        <v>237</v>
       </c>
     </row>
     <row r="394" spans="1:9">
       <c r="A394" t="s">
-        <v>867</v>
+        <v>847</v>
       </c>
       <c r="B394" t="s">
-        <v>868</v>
+        <v>848</v>
       </c>
       <c r="C394" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="E394" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="F394">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="G394" t="s">
         <v>16</v>
@@ -13259,24 +13262,24 @@
         <v>16</v>
       </c>
       <c r="I394" t="s">
-        <v>237</v>
+        <v>292</v>
       </c>
     </row>
     <row r="395" spans="1:9">
       <c r="A395" t="s">
-        <v>847</v>
+        <v>800</v>
       </c>
       <c r="B395" t="s">
-        <v>848</v>
+        <v>801</v>
       </c>
       <c r="C395" t="s">
         <v>118</v>
       </c>
       <c r="E395" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="F395">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="G395" t="s">
         <v>16</v>
@@ -13285,18 +13288,18 @@
         <v>16</v>
       </c>
       <c r="I395" t="s">
-        <v>292</v>
+        <v>745</v>
       </c>
     </row>
     <row r="396" spans="1:9">
       <c r="A396" t="s">
-        <v>800</v>
+        <v>836</v>
       </c>
       <c r="B396" t="s">
-        <v>801</v>
+        <v>837</v>
       </c>
       <c r="C396" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E396" t="s">
         <v>346</v>
@@ -13316,10 +13319,10 @@
     </row>
     <row r="397" spans="1:9">
       <c r="A397" t="s">
-        <v>836</v>
+        <v>805</v>
       </c>
       <c r="B397" t="s">
-        <v>837</v>
+        <v>806</v>
       </c>
       <c r="C397" t="s">
         <v>108</v>
@@ -13328,7 +13331,7 @@
         <v>346</v>
       </c>
       <c r="F397">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="G397" t="s">
         <v>16</v>
@@ -13337,24 +13340,24 @@
         <v>16</v>
       </c>
       <c r="I397" t="s">
-        <v>745</v>
+        <v>870</v>
       </c>
     </row>
     <row r="398" spans="1:9">
       <c r="A398" t="s">
-        <v>805</v>
+        <v>522</v>
       </c>
       <c r="B398" t="s">
-        <v>806</v>
+        <v>523</v>
       </c>
       <c r="C398" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E398" t="s">
         <v>346</v>
       </c>
       <c r="F398">
-        <v>6.0</v>
+        <v>15.0</v>
       </c>
       <c r="G398" t="s">
         <v>16</v>
@@ -13363,24 +13366,24 @@
         <v>16</v>
       </c>
       <c r="I398" t="s">
-        <v>870</v>
+        <v>395</v>
       </c>
     </row>
     <row r="399" spans="1:9">
       <c r="A399" t="s">
-        <v>522</v>
+        <v>768</v>
       </c>
       <c r="B399" t="s">
-        <v>523</v>
+        <v>769</v>
       </c>
       <c r="C399" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E399" t="s">
         <v>346</v>
       </c>
       <c r="F399">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
       <c r="G399" t="s">
         <v>16</v>
@@ -13389,24 +13392,24 @@
         <v>16</v>
       </c>
       <c r="I399" t="s">
-        <v>395</v>
+        <v>495</v>
       </c>
     </row>
     <row r="400" spans="1:9">
       <c r="A400" t="s">
-        <v>768</v>
+        <v>779</v>
       </c>
       <c r="B400" t="s">
-        <v>769</v>
+        <v>780</v>
       </c>
       <c r="C400" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="E400" t="s">
-        <v>346</v>
+        <v>699</v>
       </c>
       <c r="F400">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="G400" t="s">
         <v>16</v>
@@ -13415,7 +13418,7 @@
         <v>16</v>
       </c>
       <c r="I400" t="s">
-        <v>495</v>
+        <v>759</v>
       </c>
     </row>
     <row r="401" spans="1:9">
@@ -13426,13 +13429,13 @@
         <v>780</v>
       </c>
       <c r="C401" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="E401" t="s">
         <v>699</v>
       </c>
       <c r="F401">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
       <c r="G401" t="s">
         <v>16</v>
@@ -13441,24 +13444,24 @@
         <v>16</v>
       </c>
       <c r="I401" t="s">
-        <v>759</v>
+        <v>871</v>
       </c>
     </row>
     <row r="402" spans="1:9">
       <c r="A402" t="s">
-        <v>779</v>
+        <v>739</v>
       </c>
       <c r="B402" t="s">
-        <v>780</v>
+        <v>740</v>
       </c>
       <c r="C402" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="E402" t="s">
         <v>699</v>
       </c>
       <c r="F402">
-        <v>19.0</v>
+        <v>3.0</v>
       </c>
       <c r="G402" t="s">
         <v>16</v>
@@ -13467,18 +13470,18 @@
         <v>16</v>
       </c>
       <c r="I402" t="s">
-        <v>871</v>
+        <v>479</v>
       </c>
     </row>
     <row r="403" spans="1:9">
       <c r="A403" t="s">
-        <v>739</v>
+        <v>824</v>
       </c>
       <c r="B403" t="s">
-        <v>740</v>
+        <v>825</v>
       </c>
       <c r="C403" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E403" t="s">
         <v>699</v>
@@ -13493,24 +13496,21 @@
         <v>16</v>
       </c>
       <c r="I403" t="s">
-        <v>479</v>
+        <v>756</v>
       </c>
     </row>
     <row r="404" spans="1:9">
       <c r="A404" t="s">
-        <v>824</v>
+        <v>872</v>
       </c>
       <c r="B404" t="s">
-        <v>825</v>
-      </c>
-      <c r="C404" t="s">
-        <v>104</v>
+        <v>873</v>
       </c>
       <c r="E404" t="s">
-        <v>699</v>
+        <v>874</v>
       </c>
       <c r="F404">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G404" t="s">
         <v>16</v>
@@ -13519,15 +13519,15 @@
         <v>16</v>
       </c>
       <c r="I404" t="s">
-        <v>756</v>
+        <v>227</v>
       </c>
     </row>
     <row r="405" spans="1:9">
       <c r="A405" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="B405" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="E405" t="s">
         <v>874</v>
@@ -13542,18 +13542,18 @@
         <v>16</v>
       </c>
       <c r="I405" t="s">
-        <v>227</v>
+        <v>877</v>
       </c>
     </row>
     <row r="406" spans="1:9">
       <c r="A406" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="B406" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E406" t="s">
-        <v>874</v>
+        <v>754</v>
       </c>
       <c r="F406">
         <v>1.0</v>
@@ -13565,21 +13565,24 @@
         <v>16</v>
       </c>
       <c r="I406" t="s">
-        <v>877</v>
+        <v>755</v>
       </c>
     </row>
     <row r="407" spans="1:9">
       <c r="A407" t="s">
-        <v>878</v>
+        <v>565</v>
       </c>
       <c r="B407" t="s">
-        <v>879</v>
+        <v>566</v>
+      </c>
+      <c r="C407" t="s">
+        <v>277</v>
       </c>
       <c r="E407" t="s">
-        <v>754</v>
+        <v>567</v>
       </c>
       <c r="F407">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G407" t="s">
         <v>16</v>
@@ -13588,24 +13591,24 @@
         <v>16</v>
       </c>
       <c r="I407" t="s">
-        <v>755</v>
+        <v>401</v>
       </c>
     </row>
     <row r="408" spans="1:9">
       <c r="A408" t="s">
-        <v>565</v>
+        <v>880</v>
       </c>
       <c r="B408" t="s">
-        <v>566</v>
-      </c>
-      <c r="C408" t="s">
-        <v>277</v>
+        <v>881</v>
+      </c>
+      <c r="C408">
+        <v>44</v>
       </c>
       <c r="E408" t="s">
-        <v>567</v>
+        <v>94</v>
       </c>
       <c r="F408">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G408" t="s">
         <v>16</v>
@@ -13614,24 +13617,24 @@
         <v>16</v>
       </c>
       <c r="I408" t="s">
-        <v>401</v>
+        <v>882</v>
       </c>
     </row>
     <row r="409" spans="1:9">
       <c r="A409" t="s">
-        <v>880</v>
+        <v>770</v>
       </c>
       <c r="B409" t="s">
-        <v>881</v>
-      </c>
-      <c r="C409">
-        <v>44</v>
+        <v>771</v>
+      </c>
+      <c r="C409" t="s">
+        <v>277</v>
       </c>
       <c r="E409" t="s">
-        <v>94</v>
+        <v>772</v>
       </c>
       <c r="F409">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="G409" t="s">
         <v>16</v>
@@ -13640,7 +13643,7 @@
         <v>16</v>
       </c>
       <c r="I409" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="410" spans="1:9">
@@ -13651,13 +13654,13 @@
         <v>771</v>
       </c>
       <c r="C410" t="s">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="E410" t="s">
         <v>772</v>
       </c>
       <c r="F410">
-        <v>8.0</v>
+        <v>15.0</v>
       </c>
       <c r="G410" t="s">
         <v>16</v>
@@ -13666,7 +13669,7 @@
         <v>16</v>
       </c>
       <c r="I410" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="411" spans="1:9">
@@ -13677,13 +13680,13 @@
         <v>771</v>
       </c>
       <c r="C411" t="s">
-        <v>378</v>
+        <v>325</v>
       </c>
       <c r="E411" t="s">
         <v>772</v>
       </c>
       <c r="F411">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="G411" t="s">
         <v>16</v>
@@ -13692,24 +13695,24 @@
         <v>16</v>
       </c>
       <c r="I411" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="412" spans="1:9">
       <c r="A412" t="s">
-        <v>770</v>
+        <v>886</v>
       </c>
       <c r="B412" t="s">
-        <v>771</v>
+        <v>887</v>
       </c>
       <c r="C412" t="s">
-        <v>325</v>
+        <v>277</v>
       </c>
       <c r="E412" t="s">
         <v>772</v>
       </c>
       <c r="F412">
-        <v>11.0</v>
+        <v>7.0</v>
       </c>
       <c r="G412" t="s">
         <v>16</v>
@@ -13718,7 +13721,7 @@
         <v>16</v>
       </c>
       <c r="I412" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
     </row>
     <row r="413" spans="1:9">
@@ -13729,13 +13732,13 @@
         <v>887</v>
       </c>
       <c r="C413" t="s">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="E413" t="s">
         <v>772</v>
       </c>
       <c r="F413">
-        <v>7.0</v>
+        <v>15.0</v>
       </c>
       <c r="G413" t="s">
         <v>16</v>
@@ -13744,7 +13747,7 @@
         <v>16</v>
       </c>
       <c r="I413" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
     </row>
     <row r="414" spans="1:9">
@@ -13755,13 +13758,13 @@
         <v>887</v>
       </c>
       <c r="C414" t="s">
-        <v>378</v>
+        <v>325</v>
       </c>
       <c r="E414" t="s">
         <v>772</v>
       </c>
       <c r="F414">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
       <c r="G414" t="s">
         <v>16</v>
@@ -13770,7 +13773,7 @@
         <v>16</v>
       </c>
       <c r="I414" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
     </row>
     <row r="415" spans="1:9">
@@ -13781,13 +13784,13 @@
         <v>887</v>
       </c>
       <c r="C415" t="s">
-        <v>325</v>
+        <v>426</v>
       </c>
       <c r="E415" t="s">
         <v>772</v>
       </c>
       <c r="F415">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G415" t="s">
         <v>16</v>
@@ -13796,24 +13799,24 @@
         <v>16</v>
       </c>
       <c r="I415" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
     </row>
     <row r="416" spans="1:9">
       <c r="A416" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="B416" t="s">
         <v>887</v>
       </c>
       <c r="C416" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="E416" t="s">
         <v>772</v>
       </c>
       <c r="F416">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="G416" t="s">
         <v>16</v>
@@ -13822,24 +13825,24 @@
         <v>16</v>
       </c>
       <c r="I416" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
     </row>
     <row r="417" spans="1:9">
       <c r="A417" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B417" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="C417" t="s">
-        <v>404</v>
+        <v>277</v>
       </c>
       <c r="E417" t="s">
         <v>772</v>
       </c>
       <c r="F417">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G417" t="s">
         <v>16</v>
@@ -13848,7 +13851,7 @@
         <v>16</v>
       </c>
       <c r="I417" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
     </row>
     <row r="418" spans="1:9">
@@ -13859,13 +13862,13 @@
         <v>892</v>
       </c>
       <c r="C418" t="s">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="E418" t="s">
         <v>772</v>
       </c>
       <c r="F418">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="G418" t="s">
         <v>16</v>
@@ -13874,7 +13877,7 @@
         <v>16</v>
       </c>
       <c r="I418" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="419" spans="1:9">
@@ -13885,13 +13888,13 @@
         <v>892</v>
       </c>
       <c r="C419" t="s">
-        <v>378</v>
+        <v>325</v>
       </c>
       <c r="E419" t="s">
         <v>772</v>
       </c>
       <c r="F419">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="G419" t="s">
         <v>16</v>
@@ -13900,7 +13903,7 @@
         <v>16</v>
       </c>
       <c r="I419" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="420" spans="1:9">
@@ -13911,13 +13914,13 @@
         <v>892</v>
       </c>
       <c r="C420" t="s">
-        <v>325</v>
+        <v>426</v>
       </c>
       <c r="E420" t="s">
         <v>772</v>
       </c>
       <c r="F420">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="G420" t="s">
         <v>16</v>
@@ -13926,24 +13929,24 @@
         <v>16</v>
       </c>
       <c r="I420" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
     </row>
     <row r="421" spans="1:9">
       <c r="A421" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="B421" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="C421" t="s">
-        <v>426</v>
+        <v>277</v>
       </c>
       <c r="E421" t="s">
         <v>772</v>
       </c>
       <c r="F421">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G421" t="s">
         <v>16</v>
@@ -13952,24 +13955,24 @@
         <v>16</v>
       </c>
       <c r="I421" t="s">
-        <v>895</v>
+        <v>804</v>
       </c>
     </row>
     <row r="422" spans="1:9">
       <c r="A422" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B422" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C422" t="s">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="E422" t="s">
         <v>772</v>
       </c>
       <c r="F422">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G422" t="s">
         <v>16</v>
@@ -13978,24 +13981,24 @@
         <v>16</v>
       </c>
       <c r="I422" t="s">
-        <v>789</v>
+        <v>549</v>
       </c>
     </row>
     <row r="423" spans="1:9">
       <c r="A423" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B423" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C423" t="s">
-        <v>378</v>
+        <v>325</v>
       </c>
       <c r="E423" t="s">
         <v>772</v>
       </c>
       <c r="F423">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G423" t="s">
         <v>16</v>
@@ -14004,24 +14007,24 @@
         <v>16</v>
       </c>
       <c r="I423" t="s">
-        <v>549</v>
+        <v>899</v>
       </c>
     </row>
     <row r="424" spans="1:9">
       <c r="A424" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B424" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C424" t="s">
-        <v>325</v>
+        <v>404</v>
       </c>
       <c r="E424" t="s">
         <v>772</v>
       </c>
       <c r="F424">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="G424" t="s">
         <v>16</v>
@@ -14030,24 +14033,24 @@
         <v>16</v>
       </c>
       <c r="I424" t="s">
-        <v>898</v>
+        <v>789</v>
       </c>
     </row>
     <row r="425" spans="1:9">
       <c r="A425" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="B425" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="C425" t="s">
-        <v>404</v>
+        <v>277</v>
       </c>
       <c r="E425" t="s">
         <v>772</v>
       </c>
       <c r="F425">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G425" t="s">
         <v>16</v>
@@ -14056,24 +14059,24 @@
         <v>16</v>
       </c>
       <c r="I425" t="s">
-        <v>789</v>
+        <v>902</v>
       </c>
     </row>
     <row r="426" spans="1:9">
       <c r="A426" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B426" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C426" t="s">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="E426" t="s">
         <v>772</v>
       </c>
       <c r="F426">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G426" t="s">
         <v>16</v>
@@ -14082,24 +14085,24 @@
         <v>16</v>
       </c>
       <c r="I426" t="s">
-        <v>901</v>
+        <v>66</v>
       </c>
     </row>
     <row r="427" spans="1:9">
       <c r="A427" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B427" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C427" t="s">
-        <v>378</v>
+        <v>325</v>
       </c>
       <c r="E427" t="s">
         <v>772</v>
       </c>
       <c r="F427">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G427" t="s">
         <v>16</v>
@@ -14108,24 +14111,24 @@
         <v>16</v>
       </c>
       <c r="I427" t="s">
-        <v>66</v>
+        <v>140</v>
       </c>
     </row>
     <row r="428" spans="1:9">
       <c r="A428" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B428" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C428" t="s">
-        <v>325</v>
+        <v>426</v>
       </c>
       <c r="E428" t="s">
         <v>772</v>
       </c>
       <c r="F428">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G428" t="s">
         <v>16</v>
@@ -14134,24 +14137,24 @@
         <v>16</v>
       </c>
       <c r="I428" t="s">
-        <v>140</v>
+        <v>903</v>
       </c>
     </row>
     <row r="429" spans="1:9">
       <c r="A429" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B429" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C429" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="E429" t="s">
         <v>772</v>
       </c>
       <c r="F429">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G429" t="s">
         <v>16</v>
@@ -14160,24 +14163,24 @@
         <v>16</v>
       </c>
       <c r="I429" t="s">
-        <v>902</v>
+        <v>140</v>
       </c>
     </row>
     <row r="430" spans="1:9">
       <c r="A430" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="B430" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="C430" t="s">
-        <v>404</v>
+        <v>277</v>
       </c>
       <c r="E430" t="s">
         <v>772</v>
       </c>
       <c r="F430">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G430" t="s">
         <v>16</v>
@@ -14186,24 +14189,24 @@
         <v>16</v>
       </c>
       <c r="I430" t="s">
-        <v>140</v>
+        <v>902</v>
       </c>
     </row>
     <row r="431" spans="1:9">
       <c r="A431" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="B431" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C431" t="s">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="E431" t="s">
         <v>772</v>
       </c>
       <c r="F431">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G431" t="s">
         <v>16</v>
@@ -14212,24 +14215,24 @@
         <v>16</v>
       </c>
       <c r="I431" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
     </row>
     <row r="432" spans="1:9">
       <c r="A432" t="s">
+        <v>906</v>
+      </c>
+      <c r="B432" t="s">
         <v>905</v>
       </c>
-      <c r="B432" t="s">
-        <v>904</v>
-      </c>
       <c r="C432" t="s">
-        <v>378</v>
+        <v>325</v>
       </c>
       <c r="E432" t="s">
         <v>772</v>
       </c>
       <c r="F432">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="G432" t="s">
         <v>16</v>
@@ -14238,24 +14241,24 @@
         <v>16</v>
       </c>
       <c r="I432" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="433" spans="1:9">
       <c r="A433" t="s">
+        <v>906</v>
+      </c>
+      <c r="B433" t="s">
         <v>905</v>
       </c>
-      <c r="B433" t="s">
-        <v>904</v>
-      </c>
       <c r="C433" t="s">
-        <v>325</v>
+        <v>426</v>
       </c>
       <c r="E433" t="s">
         <v>772</v>
       </c>
       <c r="F433">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G433" t="s">
         <v>16</v>
@@ -14264,24 +14267,24 @@
         <v>16</v>
       </c>
       <c r="I433" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
     </row>
     <row r="434" spans="1:9">
       <c r="A434" t="s">
+        <v>906</v>
+      </c>
+      <c r="B434" t="s">
         <v>905</v>
       </c>
-      <c r="B434" t="s">
-        <v>904</v>
-      </c>
       <c r="C434" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="E434" t="s">
         <v>772</v>
       </c>
       <c r="F434">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G434" t="s">
         <v>16</v>
@@ -14290,24 +14293,24 @@
         <v>16</v>
       </c>
       <c r="I434" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
     </row>
     <row r="435" spans="1:9">
       <c r="A435" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="B435" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="C435" t="s">
-        <v>404</v>
+        <v>277</v>
       </c>
       <c r="E435" t="s">
         <v>772</v>
       </c>
       <c r="F435">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G435" t="s">
         <v>16</v>
@@ -14316,24 +14319,24 @@
         <v>16</v>
       </c>
       <c r="I435" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
     </row>
     <row r="436" spans="1:9">
       <c r="A436" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B436" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C436" t="s">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="E436" t="s">
         <v>772</v>
       </c>
       <c r="F436">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="G436" t="s">
         <v>16</v>
@@ -14342,18 +14345,18 @@
         <v>16</v>
       </c>
       <c r="I436" t="s">
-        <v>911</v>
+        <v>895</v>
       </c>
     </row>
     <row r="437" spans="1:9">
       <c r="A437" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B437" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C437" t="s">
-        <v>378</v>
+        <v>325</v>
       </c>
       <c r="E437" t="s">
         <v>772</v>
@@ -14368,24 +14371,24 @@
         <v>16</v>
       </c>
       <c r="I437" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="438" spans="1:9">
       <c r="A438" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B438" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C438" t="s">
-        <v>325</v>
+        <v>426</v>
       </c>
       <c r="E438" t="s">
         <v>772</v>
       </c>
       <c r="F438">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="G438" t="s">
         <v>16</v>
@@ -14394,24 +14397,24 @@
         <v>16</v>
       </c>
       <c r="I438" t="s">
-        <v>893</v>
+        <v>913</v>
       </c>
     </row>
     <row r="439" spans="1:9">
       <c r="A439" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B439" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C439" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="E439" t="s">
         <v>772</v>
       </c>
       <c r="F439">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G439" t="s">
         <v>16</v>
@@ -14420,18 +14423,18 @@
         <v>16</v>
       </c>
       <c r="I439" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
     </row>
     <row r="440" spans="1:9">
       <c r="A440" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="B440" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="C440" t="s">
-        <v>404</v>
+        <v>277</v>
       </c>
       <c r="E440" t="s">
         <v>772</v>
@@ -14446,24 +14449,24 @@
         <v>16</v>
       </c>
       <c r="I440" t="s">
-        <v>913</v>
+        <v>66</v>
       </c>
     </row>
     <row r="441" spans="1:9">
       <c r="A441" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B441" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C441" t="s">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="E441" t="s">
         <v>772</v>
       </c>
       <c r="F441">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G441" t="s">
         <v>16</v>
@@ -14472,24 +14475,24 @@
         <v>16</v>
       </c>
       <c r="I441" t="s">
-        <v>66</v>
+        <v>902</v>
       </c>
     </row>
     <row r="442" spans="1:9">
       <c r="A442" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B442" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C442" t="s">
-        <v>378</v>
+        <v>325</v>
       </c>
       <c r="E442" t="s">
         <v>772</v>
       </c>
       <c r="F442">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G442" t="s">
         <v>16</v>
@@ -14498,24 +14501,24 @@
         <v>16</v>
       </c>
       <c r="I442" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
     </row>
     <row r="443" spans="1:9">
       <c r="A443" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B443" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C443" t="s">
-        <v>325</v>
+        <v>426</v>
       </c>
       <c r="E443" t="s">
         <v>772</v>
       </c>
       <c r="F443">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G443" t="s">
         <v>16</v>
@@ -14524,18 +14527,18 @@
         <v>16</v>
       </c>
       <c r="I443" t="s">
-        <v>908</v>
+        <v>140</v>
       </c>
     </row>
     <row r="444" spans="1:9">
       <c r="A444" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B444" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C444" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="E444" t="s">
         <v>772</v>
@@ -14555,19 +14558,19 @@
     </row>
     <row r="445" spans="1:9">
       <c r="A445" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="B445" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="C445" t="s">
-        <v>404</v>
+        <v>277</v>
       </c>
       <c r="E445" t="s">
         <v>772</v>
       </c>
       <c r="F445">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G445" t="s">
         <v>16</v>
@@ -14576,24 +14579,24 @@
         <v>16</v>
       </c>
       <c r="I445" t="s">
-        <v>140</v>
+        <v>704</v>
       </c>
     </row>
     <row r="446" spans="1:9">
       <c r="A446" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B446" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C446" t="s">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="E446" t="s">
         <v>772</v>
       </c>
       <c r="F446">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G446" t="s">
         <v>16</v>
@@ -14602,18 +14605,18 @@
         <v>16</v>
       </c>
       <c r="I446" t="s">
-        <v>704</v>
+        <v>919</v>
       </c>
     </row>
     <row r="447" spans="1:9">
       <c r="A447" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B447" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C447" t="s">
-        <v>378</v>
+        <v>325</v>
       </c>
       <c r="E447" t="s">
         <v>772</v>
@@ -14628,24 +14631,24 @@
         <v>16</v>
       </c>
       <c r="I447" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="448" spans="1:9">
       <c r="A448" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B448" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C448" t="s">
-        <v>325</v>
+        <v>426</v>
       </c>
       <c r="E448" t="s">
         <v>772</v>
       </c>
       <c r="F448">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G448" t="s">
         <v>16</v>
@@ -14654,24 +14657,24 @@
         <v>16</v>
       </c>
       <c r="I448" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="449" spans="1:9">
       <c r="A449" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B449" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C449" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="E449" t="s">
         <v>772</v>
       </c>
       <c r="F449">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G449" t="s">
         <v>16</v>
@@ -14680,24 +14683,24 @@
         <v>16</v>
       </c>
       <c r="I449" t="s">
-        <v>919</v>
+        <v>789</v>
       </c>
     </row>
     <row r="450" spans="1:9">
       <c r="A450" t="s">
-        <v>916</v>
+        <v>867</v>
       </c>
       <c r="B450" t="s">
-        <v>917</v>
+        <v>868</v>
       </c>
       <c r="C450" t="s">
-        <v>404</v>
+        <v>118</v>
       </c>
       <c r="E450" t="s">
-        <v>772</v>
+        <v>230</v>
       </c>
       <c r="F450">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G450" t="s">
         <v>16</v>
@@ -14706,24 +14709,24 @@
         <v>16</v>
       </c>
       <c r="I450" t="s">
-        <v>789</v>
+        <v>284</v>
       </c>
     </row>
     <row r="451" spans="1:9">
       <c r="A451" t="s">
-        <v>867</v>
+        <v>510</v>
       </c>
       <c r="B451" t="s">
-        <v>868</v>
+        <v>511</v>
       </c>
       <c r="C451" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E451" t="s">
-        <v>230</v>
+        <v>346</v>
       </c>
       <c r="F451">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G451" t="s">
         <v>16</v>
@@ -14732,24 +14735,24 @@
         <v>16</v>
       </c>
       <c r="I451" t="s">
-        <v>284</v>
+        <v>529</v>
       </c>
     </row>
     <row r="452" spans="1:9">
       <c r="A452" t="s">
-        <v>510</v>
+        <v>921</v>
       </c>
       <c r="B452" t="s">
-        <v>511</v>
+        <v>922</v>
       </c>
       <c r="C452" t="s">
-        <v>108</v>
+        <v>277</v>
       </c>
       <c r="E452" t="s">
-        <v>346</v>
+        <v>772</v>
       </c>
       <c r="F452">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G452" t="s">
         <v>16</v>
@@ -14758,24 +14761,24 @@
         <v>16</v>
       </c>
       <c r="I452" t="s">
-        <v>529</v>
+        <v>913</v>
       </c>
     </row>
     <row r="453" spans="1:9">
       <c r="A453" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B453" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C453" t="s">
-        <v>277</v>
+        <v>325</v>
       </c>
       <c r="E453" t="s">
         <v>772</v>
       </c>
       <c r="F453">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G453" t="s">
         <v>16</v>
@@ -14784,18 +14787,18 @@
         <v>16</v>
       </c>
       <c r="I453" t="s">
-        <v>912</v>
+        <v>923</v>
       </c>
     </row>
     <row r="454" spans="1:9">
       <c r="A454" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B454" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C454" t="s">
-        <v>325</v>
+        <v>404</v>
       </c>
       <c r="E454" t="s">
         <v>772</v>
@@ -14810,24 +14813,24 @@
         <v>16</v>
       </c>
       <c r="I454" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="455" spans="1:9">
       <c r="A455" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B455" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C455" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="E455" t="s">
         <v>772</v>
       </c>
       <c r="F455">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G455" t="s">
         <v>16</v>
@@ -14836,24 +14839,24 @@
         <v>16</v>
       </c>
       <c r="I455" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
     </row>
     <row r="456" spans="1:9">
       <c r="A456" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B456" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C456" t="s">
-        <v>426</v>
+        <v>378</v>
       </c>
       <c r="E456" t="s">
         <v>772</v>
       </c>
       <c r="F456">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G456" t="s">
         <v>16</v>
@@ -14862,59 +14865,33 @@
         <v>16</v>
       </c>
       <c r="I456" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="457" spans="1:9">
       <c r="A457" t="s">
-        <v>920</v>
+        <v>770</v>
       </c>
       <c r="B457" t="s">
-        <v>921</v>
+        <v>771</v>
       </c>
       <c r="C457" t="s">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="E457" t="s">
         <v>772</v>
       </c>
       <c r="F457">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G457" t="s">
-        <v>16</v>
+        <v>924</v>
       </c>
       <c r="H457" t="s">
-        <v>16</v>
+        <v>924</v>
       </c>
       <c r="I457" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="458" spans="1:9">
-      <c r="A458" t="s">
-        <v>770</v>
-      </c>
-      <c r="B458" t="s">
-        <v>771</v>
-      </c>
-      <c r="C458" t="s">
-        <v>404</v>
-      </c>
-      <c r="E458" t="s">
-        <v>772</v>
-      </c>
-      <c r="F458">
-        <v>1.0</v>
-      </c>
-      <c r="G458" t="s">
-        <v>923</v>
-      </c>
-      <c r="H458" t="s">
-        <v>923</v>
-      </c>
-      <c r="I458" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
   </sheetData>

--- a/src/inventory/Cum.xlsx
+++ b/src/inventory/Cum.xlsx
@@ -1250,93 +1250,90 @@
     <t>৳274.96</t>
   </si>
   <si>
-    <t>৳1,924.71</t>
-  </si>
-  <si>
-    <t>৳2,443.00</t>
+    <t>৳1,649.75</t>
   </si>
   <si>
     <t>৳332.72</t>
   </si>
   <si>
-    <t>৳1,996.30</t>
+    <t>৳1,330.86</t>
+  </si>
+  <si>
+    <t>109-0103-001</t>
+  </si>
+  <si>
+    <t>৳5,943.00</t>
+  </si>
+  <si>
+    <t>105-0301-004</t>
+  </si>
+  <si>
+    <t>Drop Shoulder T-Shirt 004</t>
+  </si>
+  <si>
+    <t>2XL</t>
+  </si>
+  <si>
+    <t>Men / T-SHIRT,Drop Shoulder</t>
+  </si>
+  <si>
+    <t>৳350.00</t>
+  </si>
+  <si>
+    <t>৳194.81</t>
+  </si>
+  <si>
+    <t>৳1,168.84</t>
+  </si>
+  <si>
+    <t>৳5,928.00</t>
+  </si>
+  <si>
+    <t>105-0301-008</t>
+  </si>
+  <si>
+    <t>Crew Graphic Drop Shoulder T-Shirt</t>
+  </si>
+  <si>
+    <t>৳345.83</t>
+  </si>
+  <si>
+    <t>৳2,766.67</t>
+  </si>
+  <si>
+    <t>৳6,320.00</t>
+  </si>
+  <si>
+    <t>৳202.80</t>
+  </si>
+  <si>
+    <t>৳1,216.79</t>
+  </si>
+  <si>
+    <t>105-0301-005</t>
+  </si>
+  <si>
+    <t>Drop Shoulder T-Shirt 05</t>
+  </si>
+  <si>
+    <t>৳305.56</t>
+  </si>
+  <si>
+    <t>৳790.00</t>
+  </si>
+  <si>
+    <t>৳322.50</t>
+  </si>
+  <si>
+    <t>৳229.24</t>
+  </si>
+  <si>
+    <t>৳1,375.42</t>
   </si>
   <si>
     <t>৳4,740.00</t>
   </si>
   <si>
-    <t>109-0103-001</t>
-  </si>
-  <si>
-    <t>৳5,943.00</t>
-  </si>
-  <si>
-    <t>105-0301-004</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt 004</t>
-  </si>
-  <si>
-    <t>2XL</t>
-  </si>
-  <si>
-    <t>Men / T-SHIRT,Drop Shoulder</t>
-  </si>
-  <si>
-    <t>৳350.00</t>
-  </si>
-  <si>
-    <t>৳194.81</t>
-  </si>
-  <si>
-    <t>৳1,168.84</t>
-  </si>
-  <si>
-    <t>৳5,928.00</t>
-  </si>
-  <si>
-    <t>105-0301-008</t>
-  </si>
-  <si>
-    <t>Crew Graphic Drop Shoulder T-Shirt</t>
-  </si>
-  <si>
-    <t>৳345.83</t>
-  </si>
-  <si>
-    <t>৳2,766.67</t>
-  </si>
-  <si>
-    <t>৳6,320.00</t>
-  </si>
-  <si>
-    <t>৳202.80</t>
-  </si>
-  <si>
-    <t>৳1,216.79</t>
-  </si>
-  <si>
-    <t>105-0301-005</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt 05</t>
-  </si>
-  <si>
-    <t>৳305.56</t>
-  </si>
-  <si>
-    <t>৳790.00</t>
-  </si>
-  <si>
-    <t>৳322.50</t>
-  </si>
-  <si>
-    <t>৳229.24</t>
-  </si>
-  <si>
-    <t>৳1,375.42</t>
-  </si>
-  <si>
     <t>105-0201-035</t>
   </si>
   <si>
@@ -1400,10 +1397,10 @@
     <t>৳403.79</t>
   </si>
   <si>
-    <t>৳7,671.97</t>
-  </si>
-  <si>
-    <t>৳15,010.00</t>
+    <t>৳7,268.19</t>
+  </si>
+  <si>
+    <t>৳14,220.00</t>
   </si>
   <si>
     <t>109-0104-002</t>
@@ -1826,6 +1823,21 @@
     <t>৳5,180.00</t>
   </si>
   <si>
+    <t>102-0302-006</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 006</t>
+  </si>
+  <si>
+    <t>৳650.00</t>
+  </si>
+  <si>
+    <t>৳3,250.00</t>
+  </si>
+  <si>
+    <t>৳6,625.00</t>
+  </si>
+  <si>
     <t>৳171.46</t>
   </si>
   <si>
@@ -1919,21 +1931,6 @@
     <t>৳6,495.00</t>
   </si>
   <si>
-    <t>102-0302-006</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 006</t>
-  </si>
-  <si>
-    <t>৳650.00</t>
-  </si>
-  <si>
-    <t>৳3,250.00</t>
-  </si>
-  <si>
-    <t>৳6,625.00</t>
-  </si>
-  <si>
     <t>102-0301-002</t>
   </si>
   <si>
@@ -2033,6 +2030,9 @@
     <t>৳3,000.00</t>
   </si>
   <si>
+    <t>৳2,600.00</t>
+  </si>
+  <si>
     <t>101-0100-135</t>
   </si>
   <si>
@@ -2090,9 +2090,6 @@
     <t>৳744.44</t>
   </si>
   <si>
-    <t>৳2,600.00</t>
-  </si>
-  <si>
     <t>৳3,900.00</t>
   </si>
   <si>
@@ -2168,6 +2165,12 @@
     <t>৳4,720.00</t>
   </si>
   <si>
+    <t>৳1,300.00</t>
+  </si>
+  <si>
+    <t>৳2,650.00</t>
+  </si>
+  <si>
     <t>105-0401-008</t>
   </si>
   <si>
@@ -2237,12 +2240,6 @@
     <t>৳3,540.00</t>
   </si>
   <si>
-    <t>৳1,300.00</t>
-  </si>
-  <si>
-    <t>৳2,650.00</t>
-  </si>
-  <si>
     <t>৳4,550.00</t>
   </si>
   <si>
@@ -2261,6 +2258,18 @@
     <t>৳1,299.00</t>
   </si>
   <si>
+    <t>105-0101-372</t>
+  </si>
+  <si>
+    <t>Deep Harbor T-shirt</t>
+  </si>
+  <si>
+    <t>৳127.27</t>
+  </si>
+  <si>
+    <t>৳636.36</t>
+  </si>
+  <si>
     <t>৳1,920.00</t>
   </si>
   <si>
@@ -2294,6 +2303,9 @@
     <t>Ivory Floral Semi Formal Panjabi</t>
   </si>
   <si>
+    <t>৳420.00</t>
+  </si>
+  <si>
     <t>105-0201-034</t>
   </si>
   <si>
@@ -2318,18 +2330,6 @@
     <t>৳11,900.00</t>
   </si>
   <si>
-    <t>105-0101-372</t>
-  </si>
-  <si>
-    <t>Deep Harbor T-shirt</t>
-  </si>
-  <si>
-    <t>৳127.27</t>
-  </si>
-  <si>
-    <t>৳636.36</t>
-  </si>
-  <si>
     <t>105-0101-371</t>
   </si>
   <si>
@@ -2384,9 +2384,6 @@
     <t>৳4,320.00</t>
   </si>
   <si>
-    <t>৳420.00</t>
-  </si>
-  <si>
     <t>৳1,283.33</t>
   </si>
   <si>
@@ -2438,6 +2435,15 @@
     <t>Mocha Rock T-shirt</t>
   </si>
   <si>
+    <t>105-0101-379</t>
+  </si>
+  <si>
+    <t>Essential White T-shirt</t>
+  </si>
+  <si>
+    <t>৳5,120.00</t>
+  </si>
+  <si>
     <t>৳82.03</t>
   </si>
   <si>
@@ -2474,12 +2480,6 @@
     <t>৳20.15</t>
   </si>
   <si>
-    <t>105-0101-379</t>
-  </si>
-  <si>
-    <t>Essential White T-shirt</t>
-  </si>
-  <si>
     <t>৳735.00</t>
   </si>
   <si>
@@ -2495,6 +2495,12 @@
     <t>৳115.34</t>
   </si>
   <si>
+    <t>৳10,030.00</t>
+  </si>
+  <si>
+    <t>৳10,620.00</t>
+  </si>
+  <si>
     <t>102-0301-001</t>
   </si>
   <si>
@@ -2519,18 +2525,9 @@
     <t>৳24.60</t>
   </si>
   <si>
-    <t>৳5,120.00</t>
-  </si>
-  <si>
     <t>৳1,180.00</t>
   </si>
   <si>
-    <t>৳10,030.00</t>
-  </si>
-  <si>
-    <t>৳10,620.00</t>
-  </si>
-  <si>
     <t>102-0301-006</t>
   </si>
   <si>
@@ -2682,6 +2679,9 @@
   </si>
   <si>
     <t>৳5,960.00</t>
+  </si>
+  <si>
+    <t>৳7,450.00</t>
   </si>
   <si>
     <t>৳14,900.00</t>
@@ -6856,7 +6856,7 @@
         <v>382</v>
       </c>
       <c r="F146">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="G146" t="s">
         <v>410</v>
@@ -6865,7 +6865,7 @@
         <v>411</v>
       </c>
       <c r="I146" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -6882,21 +6882,21 @@
         <v>376</v>
       </c>
       <c r="F147">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G147" t="s">
+        <v>412</v>
+      </c>
+      <c r="H147" t="s">
         <v>413</v>
       </c>
-      <c r="H147" t="s">
-        <v>414</v>
-      </c>
       <c r="I147" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
     </row>
     <row r="148" spans="1:9">
       <c r="A148" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B148" t="s">
         <v>309</v>
@@ -6914,30 +6914,30 @@
         <v>16</v>
       </c>
       <c r="I148" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:9">
       <c r="A149" t="s">
+        <v>416</v>
+      </c>
+      <c r="B149" t="s">
+        <v>417</v>
+      </c>
+      <c r="C149" t="s">
         <v>418</v>
       </c>
-      <c r="B149" t="s">
+      <c r="E149" t="s">
         <v>419</v>
-      </c>
-      <c r="C149" t="s">
-        <v>420</v>
-      </c>
-      <c r="E149" t="s">
-        <v>421</v>
       </c>
       <c r="F149">
         <v>1.0</v>
       </c>
       <c r="G149" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H149" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I149" t="s">
         <v>405</v>
@@ -6960,13 +6960,13 @@
         <v>6.0</v>
       </c>
       <c r="G150" t="s">
+        <v>421</v>
+      </c>
+      <c r="H150" t="s">
+        <v>422</v>
+      </c>
+      <c r="I150" t="s">
         <v>423</v>
-      </c>
-      <c r="H150" t="s">
-        <v>424</v>
-      </c>
-      <c r="I150" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -6997,10 +6997,10 @@
     </row>
     <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B152" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C152" t="s">
         <v>398</v>
@@ -7012,13 +7012,13 @@
         <v>8.0</v>
       </c>
       <c r="G152" t="s">
+        <v>426</v>
+      </c>
+      <c r="H152" t="s">
+        <v>427</v>
+      </c>
+      <c r="I152" t="s">
         <v>428</v>
-      </c>
-      <c r="H152" t="s">
-        <v>429</v>
-      </c>
-      <c r="I152" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -7038,21 +7038,21 @@
         <v>6.0</v>
       </c>
       <c r="G153" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H153" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I153" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B154" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C154" t="s">
         <v>325</v>
@@ -7064,13 +7064,13 @@
         <v>1.0</v>
       </c>
       <c r="G154" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H154" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="I154" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -7090,21 +7090,21 @@
         <v>1.0</v>
       </c>
       <c r="G155" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H155" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="I155" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B156" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C156" t="s">
         <v>375</v>
@@ -7116,21 +7116,21 @@
         <v>6.0</v>
       </c>
       <c r="G156" t="s">
+        <v>436</v>
+      </c>
+      <c r="H156" t="s">
+        <v>437</v>
+      </c>
+      <c r="I156" t="s">
         <v>438</v>
-      </c>
-      <c r="H156" t="s">
-        <v>439</v>
-      </c>
-      <c r="I156" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="157" spans="1:9">
       <c r="A157" t="s">
+        <v>439</v>
+      </c>
+      <c r="B157" t="s">
         <v>440</v>
-      </c>
-      <c r="B157" t="s">
-        <v>441</v>
       </c>
       <c r="C157" t="s">
         <v>240</v>
@@ -7142,27 +7142,27 @@
         <v>2.0</v>
       </c>
       <c r="G157" t="s">
+        <v>441</v>
+      </c>
+      <c r="H157" t="s">
         <v>442</v>
       </c>
-      <c r="H157" t="s">
+      <c r="I157" t="s">
         <v>443</v>
-      </c>
-      <c r="I157" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="158" spans="1:9">
       <c r="A158" t="s">
+        <v>444</v>
+      </c>
+      <c r="B158" t="s">
         <v>445</v>
-      </c>
-      <c r="B158" t="s">
-        <v>446</v>
       </c>
       <c r="C158" t="s">
         <v>107</v>
       </c>
       <c r="E158" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F158">
         <v>2.0</v>
@@ -7174,15 +7174,15 @@
         <v>16</v>
       </c>
       <c r="I158" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="159" spans="1:9">
       <c r="A159" t="s">
+        <v>448</v>
+      </c>
+      <c r="B159" t="s">
         <v>449</v>
-      </c>
-      <c r="B159" t="s">
-        <v>450</v>
       </c>
       <c r="E159" t="s">
         <v>247</v>
@@ -7194,18 +7194,18 @@
         <v>126</v>
       </c>
       <c r="H159" t="s">
+        <v>450</v>
+      </c>
+      <c r="I159" t="s">
         <v>451</v>
-      </c>
-      <c r="I159" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="160" spans="1:9">
       <c r="A160" t="s">
+        <v>452</v>
+      </c>
+      <c r="B160" t="s">
         <v>453</v>
-      </c>
-      <c r="B160" t="s">
-        <v>454</v>
       </c>
       <c r="E160" t="s">
         <v>247</v>
@@ -7217,18 +7217,18 @@
         <v>126</v>
       </c>
       <c r="H160" t="s">
+        <v>450</v>
+      </c>
+      <c r="I160" t="s">
         <v>451</v>
-      </c>
-      <c r="I160" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="161" spans="1:9">
       <c r="A161" t="s">
+        <v>454</v>
+      </c>
+      <c r="B161" t="s">
         <v>455</v>
-      </c>
-      <c r="B161" t="s">
-        <v>456</v>
       </c>
       <c r="E161" t="s">
         <v>247</v>
@@ -7243,7 +7243,7 @@
         <v>273</v>
       </c>
       <c r="I161" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -7263,10 +7263,10 @@
         <v>2.0</v>
       </c>
       <c r="G162" t="s">
+        <v>457</v>
+      </c>
+      <c r="H162" t="s">
         <v>458</v>
-      </c>
-      <c r="H162" t="s">
-        <v>459</v>
       </c>
       <c r="I162" t="s">
         <v>370</v>
@@ -7286,24 +7286,24 @@
         <v>278</v>
       </c>
       <c r="F163">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="G163" t="s">
+        <v>459</v>
+      </c>
+      <c r="H163" t="s">
         <v>460</v>
       </c>
-      <c r="H163" t="s">
+      <c r="I163" t="s">
         <v>461</v>
-      </c>
-      <c r="I163" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="164" spans="1:9">
       <c r="A164" t="s">
+        <v>462</v>
+      </c>
+      <c r="B164" t="s">
         <v>463</v>
-      </c>
-      <c r="B164" t="s">
-        <v>464</v>
       </c>
       <c r="E164" t="s">
         <v>225</v>
@@ -7323,10 +7323,10 @@
     </row>
     <row r="165" spans="1:9">
       <c r="A165" t="s">
+        <v>464</v>
+      </c>
+      <c r="B165" t="s">
         <v>465</v>
-      </c>
-      <c r="B165" t="s">
-        <v>466</v>
       </c>
       <c r="E165" t="s">
         <v>225</v>
@@ -7341,21 +7341,21 @@
         <v>287</v>
       </c>
       <c r="I165" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="166" spans="1:9">
       <c r="A166" t="s">
+        <v>467</v>
+      </c>
+      <c r="B166" t="s">
         <v>468</v>
-      </c>
-      <c r="B166" t="s">
-        <v>469</v>
       </c>
       <c r="C166" t="s">
         <v>107</v>
       </c>
       <c r="E166" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F166">
         <v>1.0</v>
@@ -7367,7 +7367,7 @@
         <v>16</v>
       </c>
       <c r="I166" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -7387,10 +7387,10 @@
         <v>3.0</v>
       </c>
       <c r="G167" t="s">
+        <v>471</v>
+      </c>
+      <c r="H167" t="s">
         <v>472</v>
-      </c>
-      <c r="H167" t="s">
-        <v>473</v>
       </c>
       <c r="I167" t="s">
         <v>392</v>
@@ -7398,10 +7398,10 @@
     </row>
     <row r="168" spans="1:9">
       <c r="A168" t="s">
+        <v>473</v>
+      </c>
+      <c r="B168" t="s">
         <v>474</v>
-      </c>
-      <c r="B168" t="s">
-        <v>475</v>
       </c>
       <c r="E168" t="s">
         <v>225</v>
@@ -7416,12 +7416,12 @@
         <v>287</v>
       </c>
       <c r="I168" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="169" spans="1:9">
       <c r="A169" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B169" t="s">
         <v>386</v>
@@ -7436,21 +7436,21 @@
         <v>6.0</v>
       </c>
       <c r="G169" t="s">
+        <v>476</v>
+      </c>
+      <c r="H169" t="s">
         <v>477</v>
       </c>
-      <c r="H169" t="s">
+      <c r="I169" t="s">
         <v>478</v>
-      </c>
-      <c r="I169" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="170" spans="1:9">
       <c r="A170" t="s">
+        <v>439</v>
+      </c>
+      <c r="B170" t="s">
         <v>440</v>
-      </c>
-      <c r="B170" t="s">
-        <v>441</v>
       </c>
       <c r="C170" t="s">
         <v>107</v>
@@ -7462,21 +7462,21 @@
         <v>9.0</v>
       </c>
       <c r="G170" t="s">
+        <v>479</v>
+      </c>
+      <c r="H170" t="s">
         <v>480</v>
       </c>
-      <c r="H170" t="s">
+      <c r="I170" t="s">
         <v>481</v>
-      </c>
-      <c r="I170" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="171" spans="1:9">
       <c r="A171" t="s">
+        <v>482</v>
+      </c>
+      <c r="B171" t="s">
         <v>483</v>
-      </c>
-      <c r="B171" t="s">
-        <v>484</v>
       </c>
       <c r="E171" t="s">
         <v>247</v>
@@ -7488,10 +7488,10 @@
         <v>126</v>
       </c>
       <c r="H171" t="s">
+        <v>484</v>
+      </c>
+      <c r="I171" t="s">
         <v>485</v>
-      </c>
-      <c r="I171" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -7502,7 +7502,7 @@
         <v>276</v>
       </c>
       <c r="C172" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E172" t="s">
         <v>278</v>
@@ -7511,24 +7511,24 @@
         <v>5.0</v>
       </c>
       <c r="G172" t="s">
+        <v>486</v>
+      </c>
+      <c r="H172" t="s">
         <v>487</v>
       </c>
-      <c r="H172" t="s">
+      <c r="I172" t="s">
         <v>488</v>
-      </c>
-      <c r="I172" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="173" spans="1:9">
       <c r="A173" t="s">
+        <v>489</v>
+      </c>
+      <c r="B173" t="s">
         <v>490</v>
       </c>
-      <c r="B173" t="s">
+      <c r="E173" t="s">
         <v>491</v>
-      </c>
-      <c r="E173" t="s">
-        <v>492</v>
       </c>
       <c r="F173">
         <v>4.0</v>
@@ -7537,10 +7537,10 @@
         <v>226</v>
       </c>
       <c r="H173" t="s">
+        <v>492</v>
+      </c>
+      <c r="I173" t="s">
         <v>493</v>
-      </c>
-      <c r="I173" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -7560,10 +7560,10 @@
         <v>2.0</v>
       </c>
       <c r="G174" t="s">
+        <v>494</v>
+      </c>
+      <c r="H174" t="s">
         <v>495</v>
-      </c>
-      <c r="H174" t="s">
-        <v>496</v>
       </c>
       <c r="I174" t="s">
         <v>370</v>
@@ -7586,21 +7586,21 @@
         <v>1.0</v>
       </c>
       <c r="G175" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H175" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I175" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="176" spans="1:9">
       <c r="A176" t="s">
+        <v>497</v>
+      </c>
+      <c r="B176" t="s">
         <v>498</v>
-      </c>
-      <c r="B176" t="s">
-        <v>499</v>
       </c>
       <c r="C176" t="s">
         <v>120</v>
@@ -7612,24 +7612,24 @@
         <v>3.0</v>
       </c>
       <c r="G176" t="s">
+        <v>499</v>
+      </c>
+      <c r="H176" t="s">
         <v>500</v>
       </c>
-      <c r="H176" t="s">
+      <c r="I176" t="s">
         <v>501</v>
-      </c>
-      <c r="I176" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="177" spans="1:9">
       <c r="A177" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B177" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C177" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E177" t="s">
         <v>376</v>
@@ -7638,44 +7638,44 @@
         <v>6.0</v>
       </c>
       <c r="G177" t="s">
+        <v>502</v>
+      </c>
+      <c r="H177" t="s">
         <v>503</v>
       </c>
-      <c r="H177" t="s">
-        <v>504</v>
-      </c>
       <c r="I177" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
     </row>
     <row r="178" spans="1:9">
       <c r="A178" t="s">
+        <v>504</v>
+      </c>
+      <c r="B178" t="s">
         <v>505</v>
       </c>
-      <c r="B178" t="s">
+      <c r="E178" t="s">
         <v>506</v>
-      </c>
-      <c r="E178" t="s">
-        <v>507</v>
       </c>
       <c r="F178">
         <v>20.0</v>
       </c>
       <c r="G178" t="s">
+        <v>507</v>
+      </c>
+      <c r="H178" t="s">
         <v>508</v>
       </c>
-      <c r="H178" t="s">
+      <c r="I178" t="s">
         <v>509</v>
-      </c>
-      <c r="I178" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="179" spans="1:9">
       <c r="A179" t="s">
+        <v>510</v>
+      </c>
+      <c r="B179" t="s">
         <v>511</v>
-      </c>
-      <c r="B179" t="s">
-        <v>512</v>
       </c>
       <c r="C179" t="s">
         <v>117</v>
@@ -7687,21 +7687,21 @@
         <v>19.0</v>
       </c>
       <c r="G179" t="s">
+        <v>512</v>
+      </c>
+      <c r="H179" t="s">
         <v>513</v>
       </c>
-      <c r="H179" t="s">
+      <c r="I179" t="s">
         <v>514</v>
-      </c>
-      <c r="I179" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="180" spans="1:9">
       <c r="A180" t="s">
+        <v>439</v>
+      </c>
+      <c r="B180" t="s">
         <v>440</v>
-      </c>
-      <c r="B180" t="s">
-        <v>441</v>
       </c>
       <c r="C180" t="s">
         <v>120</v>
@@ -7713,21 +7713,21 @@
         <v>4.0</v>
       </c>
       <c r="G180" t="s">
+        <v>515</v>
+      </c>
+      <c r="H180" t="s">
         <v>516</v>
       </c>
-      <c r="H180" t="s">
+      <c r="I180" t="s">
         <v>517</v>
-      </c>
-      <c r="I180" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="181" spans="1:9">
       <c r="A181" t="s">
+        <v>518</v>
+      </c>
+      <c r="B181" t="s">
         <v>519</v>
-      </c>
-      <c r="B181" t="s">
-        <v>520</v>
       </c>
       <c r="E181" t="s">
         <v>247</v>
@@ -7747,10 +7747,10 @@
     </row>
     <row r="182" spans="1:9">
       <c r="A182" t="s">
+        <v>520</v>
+      </c>
+      <c r="B182" t="s">
         <v>521</v>
-      </c>
-      <c r="B182" t="s">
-        <v>522</v>
       </c>
       <c r="E182" t="s">
         <v>247</v>
@@ -7762,21 +7762,21 @@
         <v>126</v>
       </c>
       <c r="H182" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I182" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="183" spans="1:9">
       <c r="A183" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B183" t="s">
         <v>386</v>
       </c>
       <c r="C183" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E183" t="s">
         <v>376</v>
@@ -7788,36 +7788,36 @@
         <v>286</v>
       </c>
       <c r="H183" t="s">
+        <v>523</v>
+      </c>
+      <c r="I183" t="s">
         <v>524</v>
-      </c>
-      <c r="I183" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="184" spans="1:9">
       <c r="A184" t="s">
+        <v>525</v>
+      </c>
+      <c r="B184" t="s">
         <v>526</v>
-      </c>
-      <c r="B184" t="s">
-        <v>527</v>
       </c>
       <c r="C184" t="s">
         <v>375</v>
       </c>
       <c r="E184" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F184">
         <v>15.0</v>
       </c>
       <c r="G184" t="s">
+        <v>528</v>
+      </c>
+      <c r="H184" t="s">
         <v>529</v>
       </c>
-      <c r="H184" t="s">
+      <c r="I184" t="s">
         <v>530</v>
-      </c>
-      <c r="I184" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -7828,7 +7828,7 @@
         <v>374</v>
       </c>
       <c r="C185" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E185" t="s">
         <v>376</v>
@@ -7837,10 +7837,10 @@
         <v>4.0</v>
       </c>
       <c r="G185" t="s">
+        <v>531</v>
+      </c>
+      <c r="H185" t="s">
         <v>532</v>
-      </c>
-      <c r="H185" t="s">
-        <v>533</v>
       </c>
       <c r="I185" t="s">
         <v>401</v>
@@ -7848,10 +7848,10 @@
     </row>
     <row r="186" spans="1:9">
       <c r="A186" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B186" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C186" t="s">
         <v>277</v>
@@ -7863,21 +7863,21 @@
         <v>2.0</v>
       </c>
       <c r="G186" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H186" t="s">
+        <v>533</v>
+      </c>
+      <c r="I186" t="s">
         <v>534</v>
-      </c>
-      <c r="I186" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="187" spans="1:9">
       <c r="A187" t="s">
+        <v>535</v>
+      </c>
+      <c r="B187" t="s">
         <v>536</v>
-      </c>
-      <c r="B187" t="s">
-        <v>537</v>
       </c>
       <c r="C187">
         <v>28</v>
@@ -7895,7 +7895,7 @@
         <v>16</v>
       </c>
       <c r="I187" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -7915,39 +7915,39 @@
         <v>1.0</v>
       </c>
       <c r="G188" t="s">
+        <v>538</v>
+      </c>
+      <c r="H188" t="s">
+        <v>538</v>
+      </c>
+      <c r="I188" t="s">
         <v>539</v>
-      </c>
-      <c r="H188" t="s">
-        <v>539</v>
-      </c>
-      <c r="I188" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="189" spans="1:9">
       <c r="A189" t="s">
+        <v>540</v>
+      </c>
+      <c r="B189" t="s">
         <v>541</v>
-      </c>
-      <c r="B189" t="s">
-        <v>542</v>
       </c>
       <c r="C189" t="s">
         <v>375</v>
       </c>
       <c r="E189" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F189">
         <v>13.0</v>
       </c>
       <c r="G189" t="s">
+        <v>542</v>
+      </c>
+      <c r="H189" t="s">
         <v>543</v>
       </c>
-      <c r="H189" t="s">
+      <c r="I189" t="s">
         <v>544</v>
-      </c>
-      <c r="I189" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -7978,13 +7978,13 @@
     </row>
     <row r="191" spans="1:9">
       <c r="A191" t="s">
+        <v>545</v>
+      </c>
+      <c r="B191" t="s">
         <v>546</v>
       </c>
-      <c r="B191" t="s">
+      <c r="E191" t="s">
         <v>547</v>
-      </c>
-      <c r="E191" t="s">
-        <v>548</v>
       </c>
       <c r="F191">
         <v>1.0</v>
@@ -7996,33 +7996,33 @@
         <v>16</v>
       </c>
       <c r="I191" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="192" spans="1:9">
       <c r="A192" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B192" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C192" t="s">
         <v>375</v>
       </c>
       <c r="E192" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F192">
         <v>2.0</v>
       </c>
       <c r="G192" t="s">
+        <v>549</v>
+      </c>
+      <c r="H192" t="s">
         <v>550</v>
       </c>
-      <c r="H192" t="s">
-        <v>551</v>
-      </c>
       <c r="I192" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -8042,47 +8042,47 @@
         <v>16.0</v>
       </c>
       <c r="G193" t="s">
+        <v>551</v>
+      </c>
+      <c r="H193" t="s">
         <v>552</v>
       </c>
-      <c r="H193" t="s">
+      <c r="I193" t="s">
         <v>553</v>
-      </c>
-      <c r="I193" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="194" spans="1:9">
       <c r="A194" t="s">
+        <v>554</v>
+      </c>
+      <c r="B194" t="s">
         <v>555</v>
-      </c>
-      <c r="B194" t="s">
-        <v>556</v>
       </c>
       <c r="C194" t="s">
         <v>398</v>
       </c>
       <c r="E194" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F194">
         <v>1.0</v>
       </c>
       <c r="G194" t="s">
+        <v>557</v>
+      </c>
+      <c r="H194" t="s">
+        <v>557</v>
+      </c>
+      <c r="I194" t="s">
         <v>558</v>
-      </c>
-      <c r="H194" t="s">
-        <v>558</v>
-      </c>
-      <c r="I194" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="195" spans="1:9">
       <c r="A195" t="s">
+        <v>559</v>
+      </c>
+      <c r="B195" t="s">
         <v>560</v>
-      </c>
-      <c r="B195" t="s">
-        <v>561</v>
       </c>
       <c r="E195" t="s">
         <v>247</v>
@@ -8097,7 +8097,7 @@
         <v>141</v>
       </c>
       <c r="I195" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -8117,21 +8117,21 @@
         <v>16.0</v>
       </c>
       <c r="G196" t="s">
+        <v>562</v>
+      </c>
+      <c r="H196" t="s">
         <v>563</v>
       </c>
-      <c r="H196" t="s">
-        <v>564</v>
-      </c>
       <c r="I196" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="197" spans="1:9">
       <c r="A197" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B197" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C197" t="s">
         <v>277</v>
@@ -8143,13 +8143,13 @@
         <v>9.0</v>
       </c>
       <c r="G197" t="s">
+        <v>564</v>
+      </c>
+      <c r="H197" t="s">
         <v>565</v>
       </c>
-      <c r="H197" t="s">
+      <c r="I197" t="s">
         <v>566</v>
-      </c>
-      <c r="I197" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -8160,7 +8160,7 @@
         <v>397</v>
       </c>
       <c r="C198" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E198" t="s">
         <v>278</v>
@@ -8169,21 +8169,21 @@
         <v>8.0</v>
       </c>
       <c r="G198" t="s">
+        <v>567</v>
+      </c>
+      <c r="H198" t="s">
         <v>568</v>
       </c>
-      <c r="H198" t="s">
-        <v>569</v>
-      </c>
       <c r="I198" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="199" spans="1:9">
       <c r="A199" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B199" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C199" t="s">
         <v>325</v>
@@ -8195,47 +8195,47 @@
         <v>20.0</v>
       </c>
       <c r="G199" t="s">
+        <v>569</v>
+      </c>
+      <c r="H199" t="s">
         <v>570</v>
       </c>
-      <c r="H199" t="s">
+      <c r="I199" t="s">
         <v>571</v>
-      </c>
-      <c r="I199" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="200" spans="1:9">
       <c r="A200" t="s">
+        <v>525</v>
+      </c>
+      <c r="B200" t="s">
         <v>526</v>
-      </c>
-      <c r="B200" t="s">
-        <v>527</v>
       </c>
       <c r="C200" t="s">
         <v>325</v>
       </c>
       <c r="E200" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F200">
         <v>10.0</v>
       </c>
       <c r="G200" t="s">
+        <v>572</v>
+      </c>
+      <c r="H200" t="s">
+        <v>509</v>
+      </c>
+      <c r="I200" t="s">
         <v>573</v>
-      </c>
-      <c r="H200" t="s">
-        <v>510</v>
-      </c>
-      <c r="I200" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="201" spans="1:9">
       <c r="A201" t="s">
+        <v>574</v>
+      </c>
+      <c r="B201" t="s">
         <v>575</v>
-      </c>
-      <c r="B201" t="s">
-        <v>576</v>
       </c>
       <c r="C201" t="s">
         <v>107</v>
@@ -8247,21 +8247,21 @@
         <v>1.0</v>
       </c>
       <c r="G201" t="s">
+        <v>576</v>
+      </c>
+      <c r="H201" t="s">
+        <v>576</v>
+      </c>
+      <c r="I201" t="s">
         <v>577</v>
-      </c>
-      <c r="H201" t="s">
-        <v>577</v>
-      </c>
-      <c r="I201" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="202" spans="1:9">
       <c r="A202" t="s">
+        <v>510</v>
+      </c>
+      <c r="B202" t="s">
         <v>511</v>
-      </c>
-      <c r="B202" t="s">
-        <v>512</v>
       </c>
       <c r="C202" t="s">
         <v>107</v>
@@ -8273,10 +8273,10 @@
         <v>15.0</v>
       </c>
       <c r="G202" t="s">
+        <v>578</v>
+      </c>
+      <c r="H202" t="s">
         <v>579</v>
-      </c>
-      <c r="H202" t="s">
-        <v>580</v>
       </c>
       <c r="I202" t="s">
         <v>389</v>
@@ -8284,13 +8284,13 @@
     </row>
     <row r="203" spans="1:9">
       <c r="A203" t="s">
+        <v>580</v>
+      </c>
+      <c r="B203" t="s">
         <v>581</v>
       </c>
-      <c r="B203" t="s">
+      <c r="E203" t="s">
         <v>582</v>
-      </c>
-      <c r="E203" t="s">
-        <v>583</v>
       </c>
       <c r="F203">
         <v>3.0</v>
@@ -8302,15 +8302,15 @@
         <v>65</v>
       </c>
       <c r="I203" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="204" spans="1:9">
       <c r="A204" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B204" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C204" t="s">
         <v>375</v>
@@ -8322,64 +8322,64 @@
         <v>11.0</v>
       </c>
       <c r="G204" t="s">
+        <v>584</v>
+      </c>
+      <c r="H204" t="s">
         <v>585</v>
       </c>
-      <c r="H204" t="s">
+      <c r="I204" t="s">
         <v>586</v>
-      </c>
-      <c r="I204" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="205" spans="1:9">
       <c r="A205" t="s">
+        <v>587</v>
+      </c>
+      <c r="B205" t="s">
         <v>588</v>
       </c>
-      <c r="B205" t="s">
+      <c r="E205" t="s">
         <v>589</v>
-      </c>
-      <c r="E205" t="s">
-        <v>590</v>
       </c>
       <c r="F205">
         <v>4.0</v>
       </c>
       <c r="G205" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H205" t="s">
         <v>161</v>
       </c>
       <c r="I205" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="206" spans="1:9">
       <c r="A206" t="s">
+        <v>591</v>
+      </c>
+      <c r="B206" t="s">
         <v>592</v>
       </c>
-      <c r="B206" t="s">
-        <v>593</v>
-      </c>
       <c r="E206" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F206">
         <v>1.0</v>
       </c>
       <c r="G206" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H206" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I206" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="207" spans="1:9">
       <c r="A207" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B207" t="s">
         <v>386</v>
@@ -8394,13 +8394,13 @@
         <v>4.0</v>
       </c>
       <c r="G207" t="s">
+        <v>594</v>
+      </c>
+      <c r="H207" t="s">
         <v>595</v>
       </c>
-      <c r="H207" t="s">
+      <c r="I207" t="s">
         <v>596</v>
-      </c>
-      <c r="I207" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -8420,10 +8420,10 @@
         <v>3.0</v>
       </c>
       <c r="G208" t="s">
+        <v>597</v>
+      </c>
+      <c r="H208" t="s">
         <v>598</v>
-      </c>
-      <c r="H208" t="s">
-        <v>599</v>
       </c>
       <c r="I208" t="s">
         <v>281</v>
@@ -8446,111 +8446,111 @@
         <v>2.0</v>
       </c>
       <c r="G209" t="s">
+        <v>599</v>
+      </c>
+      <c r="H209" t="s">
         <v>600</v>
       </c>
-      <c r="H209" t="s">
+      <c r="I209" t="s">
         <v>601</v>
-      </c>
-      <c r="I209" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="210" spans="1:9">
       <c r="A210" t="s">
-        <v>426</v>
+        <v>602</v>
       </c>
       <c r="B210" t="s">
-        <v>427</v>
+        <v>603</v>
       </c>
       <c r="C210" t="s">
-        <v>420</v>
+        <v>375</v>
       </c>
       <c r="E210" t="s">
-        <v>278</v>
+        <v>527</v>
       </c>
       <c r="F210">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="G210" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H210" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="I210" t="s">
-        <v>430</v>
+        <v>606</v>
       </c>
     </row>
     <row r="211" spans="1:9">
       <c r="A211" t="s">
-        <v>498</v>
+        <v>424</v>
       </c>
       <c r="B211" t="s">
-        <v>499</v>
+        <v>425</v>
       </c>
       <c r="C211" t="s">
-        <v>117</v>
+        <v>418</v>
       </c>
       <c r="E211" t="s">
-        <v>346</v>
+        <v>278</v>
       </c>
       <c r="F211">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="G211" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="H211" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="I211" t="s">
-        <v>518</v>
+        <v>428</v>
       </c>
     </row>
     <row r="212" spans="1:9">
       <c r="A212" t="s">
-        <v>555</v>
+        <v>497</v>
       </c>
       <c r="B212" t="s">
-        <v>556</v>
+        <v>498</v>
       </c>
       <c r="C212" t="s">
-        <v>375</v>
+        <v>117</v>
       </c>
       <c r="E212" t="s">
-        <v>557</v>
+        <v>346</v>
       </c>
       <c r="F212">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="G212" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="H212" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="I212" t="s">
-        <v>609</v>
+        <v>517</v>
       </c>
     </row>
     <row r="213" spans="1:9">
       <c r="A213" t="s">
-        <v>610</v>
+        <v>554</v>
       </c>
       <c r="B213" t="s">
-        <v>611</v>
+        <v>555</v>
       </c>
       <c r="C213" t="s">
         <v>375</v>
       </c>
       <c r="E213" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F213">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G213" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H213" t="s">
         <v>612</v>
@@ -8561,126 +8561,126 @@
     </row>
     <row r="214" spans="1:9">
       <c r="A214" t="s">
-        <v>541</v>
+        <v>614</v>
       </c>
       <c r="B214" t="s">
-        <v>542</v>
+        <v>615</v>
       </c>
       <c r="C214" t="s">
-        <v>325</v>
+        <v>375</v>
       </c>
       <c r="E214" t="s">
-        <v>528</v>
+        <v>556</v>
       </c>
       <c r="F214">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G214" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H214" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="I214" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="215" spans="1:9">
       <c r="A215" t="s">
-        <v>610</v>
+        <v>540</v>
       </c>
       <c r="B215" t="s">
-        <v>611</v>
+        <v>541</v>
       </c>
       <c r="C215" t="s">
-        <v>398</v>
+        <v>325</v>
       </c>
       <c r="E215" t="s">
-        <v>557</v>
+        <v>527</v>
       </c>
       <c r="F215">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G215" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H215" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="I215" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
     </row>
     <row r="216" spans="1:9">
       <c r="A216" t="s">
-        <v>350</v>
+        <v>614</v>
       </c>
       <c r="B216" t="s">
-        <v>351</v>
+        <v>615</v>
       </c>
       <c r="C216" t="s">
-        <v>117</v>
+        <v>398</v>
       </c>
       <c r="E216" t="s">
-        <v>340</v>
+        <v>556</v>
       </c>
       <c r="F216">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G216" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="H216" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="I216" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="217" spans="1:9">
       <c r="A217" t="s">
-        <v>621</v>
+        <v>350</v>
       </c>
       <c r="B217" t="s">
-        <v>622</v>
+        <v>351</v>
+      </c>
+      <c r="C217" t="s">
+        <v>117</v>
       </c>
       <c r="E217" t="s">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="F217">
         <v>4.0</v>
       </c>
       <c r="G217" t="s">
-        <v>16</v>
+        <v>622</v>
       </c>
       <c r="H217" t="s">
-        <v>16</v>
+        <v>623</v>
       </c>
       <c r="I217" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="218" spans="1:9">
       <c r="A218" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B218" t="s">
-        <v>625</v>
-      </c>
-      <c r="C218" t="s">
-        <v>107</v>
+        <v>626</v>
       </c>
       <c r="E218" t="s">
-        <v>364</v>
+        <v>310</v>
       </c>
       <c r="F218">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G218" t="s">
-        <v>626</v>
+        <v>16</v>
       </c>
       <c r="H218" t="s">
-        <v>256</v>
+        <v>16</v>
       </c>
       <c r="I218" t="s">
         <v>627</v>
@@ -8694,137 +8694,137 @@
         <v>629</v>
       </c>
       <c r="C219" t="s">
-        <v>375</v>
+        <v>107</v>
       </c>
       <c r="E219" t="s">
-        <v>528</v>
+        <v>364</v>
       </c>
       <c r="F219">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G219" t="s">
-        <v>524</v>
+        <v>630</v>
       </c>
       <c r="H219" t="s">
-        <v>74</v>
+        <v>256</v>
       </c>
       <c r="I219" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="220" spans="1:9">
       <c r="A220" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B220" t="s">
-        <v>632</v>
+        <v>633</v>
+      </c>
+      <c r="C220" t="s">
+        <v>375</v>
       </c>
       <c r="E220" t="s">
-        <v>583</v>
+        <v>527</v>
       </c>
       <c r="F220">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G220" t="s">
-        <v>226</v>
+        <v>523</v>
       </c>
       <c r="H220" t="s">
-        <v>257</v>
+        <v>74</v>
       </c>
       <c r="I220" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="221" spans="1:9">
       <c r="A221" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B221" t="s">
-        <v>635</v>
-      </c>
-      <c r="C221" t="s">
-        <v>375</v>
+        <v>636</v>
       </c>
       <c r="E221" t="s">
-        <v>528</v>
+        <v>582</v>
       </c>
       <c r="F221">
         <v>5.0</v>
       </c>
       <c r="G221" t="s">
-        <v>636</v>
+        <v>226</v>
       </c>
       <c r="H221" t="s">
+        <v>257</v>
+      </c>
+      <c r="I221" t="s">
         <v>637</v>
-      </c>
-      <c r="I221" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="222" spans="1:9">
       <c r="A222" t="s">
+        <v>638</v>
+      </c>
+      <c r="B222" t="s">
         <v>639</v>
-      </c>
-      <c r="B222" t="s">
-        <v>640</v>
       </c>
       <c r="C222" t="s">
         <v>375</v>
       </c>
       <c r="E222" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F222">
         <v>10.0</v>
       </c>
       <c r="G222" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H222" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="I222" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="223" spans="1:9">
       <c r="A223" t="s">
+        <v>641</v>
+      </c>
+      <c r="B223" t="s">
         <v>642</v>
-      </c>
-      <c r="B223" t="s">
-        <v>643</v>
       </c>
       <c r="C223" t="s">
         <v>375</v>
       </c>
       <c r="E223" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F223">
         <v>14.0</v>
       </c>
       <c r="G223" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H223" t="s">
+        <v>643</v>
+      </c>
+      <c r="I223" t="s">
         <v>644</v>
-      </c>
-      <c r="I223" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="224" spans="1:9">
       <c r="A224" t="s">
+        <v>645</v>
+      </c>
+      <c r="B224" t="s">
         <v>646</v>
-      </c>
-      <c r="B224" t="s">
-        <v>647</v>
       </c>
       <c r="C224" t="s">
         <v>277</v>
       </c>
       <c r="E224" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="F224">
         <v>2.0</v>
@@ -8836,30 +8836,30 @@
         <v>16</v>
       </c>
       <c r="I224" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="225" spans="1:9">
       <c r="A225" t="s">
+        <v>649</v>
+      </c>
+      <c r="B225" t="s">
         <v>650</v>
       </c>
-      <c r="B225" t="s">
-        <v>651</v>
-      </c>
       <c r="C225" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E225" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F225">
         <v>5.0</v>
       </c>
       <c r="G225" t="s">
+        <v>651</v>
+      </c>
+      <c r="H225" t="s">
         <v>652</v>
-      </c>
-      <c r="H225" t="s">
-        <v>653</v>
       </c>
       <c r="I225" t="s">
         <v>141</v>
@@ -8867,62 +8867,62 @@
     </row>
     <row r="226" spans="1:9">
       <c r="A226" t="s">
+        <v>653</v>
+      </c>
+      <c r="B226" t="s">
         <v>654</v>
-      </c>
-      <c r="B226" t="s">
-        <v>655</v>
       </c>
       <c r="C226" t="s">
         <v>375</v>
       </c>
       <c r="E226" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F226">
         <v>1.0</v>
       </c>
       <c r="G226" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H226" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="I226" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="227" spans="1:9">
       <c r="A227" t="s">
+        <v>649</v>
+      </c>
+      <c r="B227" t="s">
         <v>650</v>
-      </c>
-      <c r="B227" t="s">
-        <v>651</v>
       </c>
       <c r="C227" t="s">
         <v>325</v>
       </c>
       <c r="E227" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F227">
         <v>3.0</v>
       </c>
       <c r="G227" t="s">
+        <v>656</v>
+      </c>
+      <c r="H227" t="s">
         <v>657</v>
       </c>
-      <c r="H227" t="s">
+      <c r="I227" t="s">
         <v>658</v>
-      </c>
-      <c r="I227" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="228" spans="1:9">
       <c r="A228" t="s">
+        <v>659</v>
+      </c>
+      <c r="B228" t="s">
         <v>660</v>
-      </c>
-      <c r="B228" t="s">
-        <v>661</v>
       </c>
       <c r="E228" t="s">
         <v>247</v>
@@ -8937,15 +8937,15 @@
         <v>257</v>
       </c>
       <c r="I228" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="229" spans="1:9">
       <c r="A229" t="s">
+        <v>497</v>
+      </c>
+      <c r="B229" t="s">
         <v>498</v>
-      </c>
-      <c r="B229" t="s">
-        <v>499</v>
       </c>
       <c r="C229" t="s">
         <v>240</v>
@@ -8957,489 +8957,489 @@
         <v>1.0</v>
       </c>
       <c r="G229" t="s">
+        <v>661</v>
+      </c>
+      <c r="H229" t="s">
+        <v>661</v>
+      </c>
+      <c r="I229" t="s">
         <v>662</v>
-      </c>
-      <c r="H229" t="s">
-        <v>662</v>
-      </c>
-      <c r="I229" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="230" spans="1:9">
       <c r="A230" t="s">
+        <v>540</v>
+      </c>
+      <c r="B230" t="s">
         <v>541</v>
-      </c>
-      <c r="B230" t="s">
-        <v>542</v>
       </c>
       <c r="C230" t="s">
         <v>277</v>
       </c>
       <c r="E230" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F230">
         <v>8.0</v>
       </c>
       <c r="G230" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="H230" t="s">
+        <v>663</v>
+      </c>
+      <c r="I230" t="s">
         <v>664</v>
-      </c>
-      <c r="I230" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="231" spans="1:9">
       <c r="A231" t="s">
+        <v>525</v>
+      </c>
+      <c r="B231" t="s">
         <v>526</v>
       </c>
-      <c r="B231" t="s">
+      <c r="C231" t="s">
+        <v>418</v>
+      </c>
+      <c r="E231" t="s">
         <v>527</v>
-      </c>
-      <c r="C231" t="s">
-        <v>420</v>
-      </c>
-      <c r="E231" t="s">
-        <v>528</v>
       </c>
       <c r="F231">
         <v>6.0</v>
       </c>
       <c r="G231" t="s">
+        <v>665</v>
+      </c>
+      <c r="H231" t="s">
         <v>666</v>
       </c>
-      <c r="H231" t="s">
+      <c r="I231" t="s">
         <v>667</v>
-      </c>
-      <c r="I231" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="232" spans="1:9">
       <c r="A232" t="s">
+        <v>668</v>
+      </c>
+      <c r="B232" t="s">
         <v>669</v>
-      </c>
-      <c r="B232" t="s">
-        <v>670</v>
       </c>
       <c r="C232" t="s">
         <v>375</v>
       </c>
       <c r="E232" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F232">
         <v>6.0</v>
       </c>
       <c r="G232" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H232" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="I232" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="233" spans="1:9">
       <c r="A233" t="s">
-        <v>672</v>
+        <v>602</v>
       </c>
       <c r="B233" t="s">
-        <v>222</v>
-      </c>
-      <c r="C233">
-        <v>28</v>
+        <v>603</v>
+      </c>
+      <c r="C233" t="s">
+        <v>325</v>
       </c>
       <c r="E233" t="s">
-        <v>157</v>
+        <v>527</v>
       </c>
       <c r="F233">
         <v>4.0</v>
       </c>
       <c r="G233" t="s">
-        <v>16</v>
+        <v>604</v>
       </c>
       <c r="H233" t="s">
-        <v>16</v>
+        <v>671</v>
       </c>
       <c r="I233" t="s">
-        <v>673</v>
+        <v>215</v>
       </c>
     </row>
     <row r="234" spans="1:9">
       <c r="A234" t="s">
-        <v>541</v>
+        <v>672</v>
       </c>
       <c r="B234" t="s">
-        <v>542</v>
-      </c>
-      <c r="C234" t="s">
-        <v>420</v>
+        <v>222</v>
+      </c>
+      <c r="C234">
+        <v>28</v>
       </c>
       <c r="E234" t="s">
-        <v>528</v>
+        <v>157</v>
       </c>
       <c r="F234">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="G234" t="s">
-        <v>666</v>
+        <v>16</v>
       </c>
       <c r="H234" t="s">
-        <v>489</v>
+        <v>16</v>
       </c>
       <c r="I234" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="235" spans="1:9">
       <c r="A235" t="s">
-        <v>650</v>
+        <v>540</v>
       </c>
       <c r="B235" t="s">
-        <v>651</v>
+        <v>541</v>
       </c>
       <c r="C235" t="s">
-        <v>375</v>
+        <v>418</v>
       </c>
       <c r="E235" t="s">
-        <v>557</v>
+        <v>527</v>
       </c>
       <c r="F235">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G235" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="H235" t="s">
-        <v>676</v>
+        <v>488</v>
       </c>
       <c r="I235" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="236" spans="1:9">
       <c r="A236" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B236" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C236" t="s">
         <v>375</v>
       </c>
       <c r="E236" t="s">
-        <v>648</v>
+        <v>556</v>
       </c>
       <c r="F236">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="G236" t="s">
-        <v>16</v>
+        <v>675</v>
       </c>
       <c r="H236" t="s">
-        <v>16</v>
+        <v>676</v>
       </c>
       <c r="I236" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="237" spans="1:9">
       <c r="A237" t="s">
-        <v>610</v>
+        <v>645</v>
       </c>
       <c r="B237" t="s">
-        <v>611</v>
+        <v>646</v>
       </c>
       <c r="C237" t="s">
-        <v>325</v>
+        <v>375</v>
       </c>
       <c r="E237" t="s">
-        <v>557</v>
+        <v>647</v>
       </c>
       <c r="F237">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="G237" t="s">
-        <v>679</v>
+        <v>16</v>
       </c>
       <c r="H237" t="s">
-        <v>680</v>
+        <v>16</v>
       </c>
       <c r="I237" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="238" spans="1:9">
       <c r="A238" t="s">
-        <v>555</v>
+        <v>602</v>
       </c>
       <c r="B238" t="s">
-        <v>556</v>
+        <v>603</v>
       </c>
       <c r="C238" t="s">
-        <v>325</v>
+        <v>277</v>
       </c>
       <c r="E238" t="s">
-        <v>557</v>
+        <v>527</v>
       </c>
       <c r="F238">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G238" t="s">
-        <v>682</v>
+        <v>604</v>
       </c>
       <c r="H238" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="I238" t="s">
-        <v>467</v>
+        <v>215</v>
       </c>
     </row>
     <row r="239" spans="1:9">
       <c r="A239" t="s">
-        <v>684</v>
+        <v>614</v>
       </c>
       <c r="B239" t="s">
-        <v>685</v>
-      </c>
-      <c r="C239">
-        <v>38</v>
+        <v>615</v>
+      </c>
+      <c r="C239" t="s">
+        <v>325</v>
       </c>
       <c r="E239" t="s">
-        <v>93</v>
+        <v>556</v>
       </c>
       <c r="F239">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G239" t="s">
-        <v>42</v>
+        <v>679</v>
       </c>
       <c r="H239" t="s">
-        <v>46</v>
+        <v>680</v>
       </c>
       <c r="I239" t="s">
-        <v>602</v>
+        <v>681</v>
       </c>
     </row>
     <row r="240" spans="1:9">
       <c r="A240" t="s">
-        <v>686</v>
+        <v>554</v>
       </c>
       <c r="B240" t="s">
-        <v>687</v>
+        <v>555</v>
       </c>
       <c r="C240" t="s">
-        <v>117</v>
+        <v>325</v>
       </c>
       <c r="E240" t="s">
-        <v>688</v>
+        <v>556</v>
       </c>
       <c r="F240">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G240" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="H240" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="I240" t="s">
-        <v>306</v>
+        <v>466</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="A241" t="s">
-        <v>646</v>
+        <v>684</v>
       </c>
       <c r="B241" t="s">
-        <v>647</v>
-      </c>
-      <c r="C241" t="s">
-        <v>398</v>
+        <v>685</v>
+      </c>
+      <c r="C241">
+        <v>38</v>
       </c>
       <c r="E241" t="s">
-        <v>648</v>
+        <v>93</v>
       </c>
       <c r="F241">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G241" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="H241" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="I241" t="s">
-        <v>517</v>
+        <v>601</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" t="s">
-        <v>634</v>
+        <v>686</v>
       </c>
       <c r="B242" t="s">
-        <v>635</v>
+        <v>687</v>
       </c>
       <c r="C242" t="s">
-        <v>277</v>
+        <v>117</v>
       </c>
       <c r="E242" t="s">
-        <v>528</v>
+        <v>688</v>
       </c>
       <c r="F242">
         <v>4.0</v>
       </c>
       <c r="G242" t="s">
-        <v>636</v>
+        <v>689</v>
       </c>
       <c r="H242" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="I242" t="s">
-        <v>215</v>
+        <v>306</v>
       </c>
     </row>
     <row r="243" spans="1:9">
       <c r="A243" t="s">
-        <v>634</v>
+        <v>645</v>
       </c>
       <c r="B243" t="s">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="C243" t="s">
-        <v>325</v>
+        <v>398</v>
       </c>
       <c r="E243" t="s">
-        <v>528</v>
+        <v>647</v>
       </c>
       <c r="F243">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G243" t="s">
-        <v>636</v>
+        <v>16</v>
       </c>
       <c r="H243" t="s">
-        <v>691</v>
+        <v>16</v>
       </c>
       <c r="I243" t="s">
-        <v>215</v>
+        <v>516</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" t="s">
+        <v>638</v>
+      </c>
+      <c r="B244" t="s">
         <v>639</v>
-      </c>
-      <c r="B244" t="s">
-        <v>640</v>
       </c>
       <c r="C244" t="s">
         <v>325</v>
       </c>
       <c r="E244" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F244">
         <v>6.0</v>
       </c>
       <c r="G244" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H244" t="s">
+        <v>691</v>
+      </c>
+      <c r="I244" t="s">
         <v>692</v>
-      </c>
-      <c r="I244" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="245" spans="1:9">
       <c r="A245" t="s">
+        <v>641</v>
+      </c>
+      <c r="B245" t="s">
         <v>642</v>
-      </c>
-      <c r="B245" t="s">
-        <v>643</v>
       </c>
       <c r="C245" t="s">
         <v>325</v>
       </c>
       <c r="E245" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F245">
         <v>8.0</v>
       </c>
       <c r="G245" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H245" t="s">
+        <v>693</v>
+      </c>
+      <c r="I245" t="s">
         <v>694</v>
-      </c>
-      <c r="I245" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="246" spans="1:9">
       <c r="A246" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B246" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C246" t="s">
         <v>277</v>
       </c>
       <c r="E246" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F246">
         <v>2.0</v>
       </c>
       <c r="G246" t="s">
+        <v>695</v>
+      </c>
+      <c r="H246" t="s">
+        <v>572</v>
+      </c>
+      <c r="I246" t="s">
         <v>696</v>
-      </c>
-      <c r="H246" t="s">
-        <v>573</v>
-      </c>
-      <c r="I246" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="247" spans="1:9">
       <c r="A247" t="s">
+        <v>668</v>
+      </c>
+      <c r="B247" t="s">
         <v>669</v>
-      </c>
-      <c r="B247" t="s">
-        <v>670</v>
       </c>
       <c r="C247" t="s">
         <v>325</v>
       </c>
       <c r="E247" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F247">
         <v>5.0</v>
       </c>
       <c r="G247" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H247" t="s">
         <v>84</v>
       </c>
       <c r="I247" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="248" spans="1:9">
       <c r="A248" t="s">
+        <v>698</v>
+      </c>
+      <c r="B248" t="s">
         <v>699</v>
-      </c>
-      <c r="B248" t="s">
-        <v>700</v>
       </c>
       <c r="E248" t="s">
         <v>247</v>
@@ -9459,10 +9459,10 @@
     </row>
     <row r="249" spans="1:9">
       <c r="A249" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B249" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C249" t="s">
         <v>398</v>
@@ -9474,21 +9474,21 @@
         <v>1.0</v>
       </c>
       <c r="G249" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H249" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="I249" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="250" spans="1:9">
       <c r="A250" t="s">
+        <v>701</v>
+      </c>
+      <c r="B250" t="s">
         <v>702</v>
-      </c>
-      <c r="B250" t="s">
-        <v>703</v>
       </c>
       <c r="C250" t="s">
         <v>240</v>
@@ -9506,15 +9506,15 @@
         <v>16</v>
       </c>
       <c r="I250" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="251" spans="1:9">
       <c r="A251" t="s">
+        <v>704</v>
+      </c>
+      <c r="B251" t="s">
         <v>705</v>
-      </c>
-      <c r="B251" t="s">
-        <v>706</v>
       </c>
       <c r="C251" t="s">
         <v>103</v>
@@ -9526,27 +9526,27 @@
         <v>1.0</v>
       </c>
       <c r="G251" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H251" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="I251" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:9">
       <c r="A252" t="s">
+        <v>707</v>
+      </c>
+      <c r="B252" t="s">
         <v>708</v>
       </c>
-      <c r="B252" t="s">
-        <v>709</v>
-      </c>
       <c r="C252" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E252" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="F252">
         <v>2.0</v>
@@ -9558,47 +9558,47 @@
         <v>16</v>
       </c>
       <c r="I252" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="253" spans="1:9">
       <c r="A253" t="s">
+        <v>525</v>
+      </c>
+      <c r="B253" t="s">
         <v>526</v>
-      </c>
-      <c r="B253" t="s">
-        <v>527</v>
       </c>
       <c r="C253" t="s">
         <v>277</v>
       </c>
       <c r="E253" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F253">
         <v>5.0</v>
       </c>
       <c r="G253" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H253" t="s">
         <v>22</v>
       </c>
       <c r="I253" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="254" spans="1:9">
       <c r="A254" t="s">
+        <v>710</v>
+      </c>
+      <c r="B254" t="s">
         <v>711</v>
       </c>
-      <c r="B254" t="s">
-        <v>712</v>
-      </c>
       <c r="C254" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E254" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="F254">
         <v>4.0</v>
@@ -9610,382 +9610,382 @@
         <v>16</v>
       </c>
       <c r="I254" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="255" spans="1:9">
       <c r="A255" t="s">
+        <v>713</v>
+      </c>
+      <c r="B255" t="s">
         <v>714</v>
-      </c>
-      <c r="B255" t="s">
-        <v>715</v>
       </c>
       <c r="C255" t="s">
         <v>375</v>
       </c>
       <c r="E255" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F255">
         <v>4.0</v>
       </c>
       <c r="G255" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H255" t="s">
         <v>74</v>
       </c>
       <c r="I255" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="256" spans="1:9">
       <c r="A256" t="s">
-        <v>717</v>
+        <v>602</v>
       </c>
       <c r="B256" t="s">
-        <v>718</v>
+        <v>603</v>
       </c>
       <c r="C256" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E256" t="s">
-        <v>648</v>
+        <v>527</v>
       </c>
       <c r="F256">
         <v>2.0</v>
       </c>
       <c r="G256" t="s">
-        <v>16</v>
+        <v>604</v>
       </c>
       <c r="H256" t="s">
-        <v>16</v>
+        <v>716</v>
       </c>
       <c r="I256" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
     </row>
     <row r="257" spans="1:9">
       <c r="A257" t="s">
+        <v>718</v>
+      </c>
+      <c r="B257" t="s">
         <v>719</v>
       </c>
-      <c r="B257" t="s">
-        <v>720</v>
-      </c>
       <c r="C257" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="E257" t="s">
-        <v>528</v>
+        <v>647</v>
       </c>
       <c r="F257">
         <v>2.0</v>
       </c>
       <c r="G257" t="s">
-        <v>524</v>
+        <v>16</v>
       </c>
       <c r="H257" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I257" t="s">
-        <v>721</v>
+        <v>696</v>
       </c>
     </row>
     <row r="258" spans="1:9">
       <c r="A258" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B258" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C258" t="s">
         <v>375</v>
       </c>
       <c r="E258" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F258">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G258" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H258" t="s">
-        <v>724</v>
+        <v>73</v>
       </c>
       <c r="I258" t="s">
-        <v>153</v>
+        <v>722</v>
       </c>
     </row>
     <row r="259" spans="1:9">
       <c r="A259" t="s">
-        <v>628</v>
+        <v>723</v>
       </c>
       <c r="B259" t="s">
-        <v>629</v>
+        <v>724</v>
       </c>
       <c r="C259" t="s">
-        <v>325</v>
+        <v>375</v>
       </c>
       <c r="E259" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F259">
         <v>3.0</v>
       </c>
       <c r="G259" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H259" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="I259" t="s">
-        <v>725</v>
+        <v>153</v>
       </c>
     </row>
     <row r="260" spans="1:9">
       <c r="A260" t="s">
+        <v>632</v>
+      </c>
+      <c r="B260" t="s">
+        <v>633</v>
+      </c>
+      <c r="C260" t="s">
+        <v>325</v>
+      </c>
+      <c r="E260" t="s">
+        <v>527</v>
+      </c>
+      <c r="F260">
+        <v>3.0</v>
+      </c>
+      <c r="G260" t="s">
+        <v>523</v>
+      </c>
+      <c r="H260" t="s">
+        <v>725</v>
+      </c>
+      <c r="I260" t="s">
         <v>726</v>
-      </c>
-      <c r="B260" t="s">
-        <v>727</v>
-      </c>
-      <c r="C260" t="s">
-        <v>117</v>
-      </c>
-      <c r="E260" t="s">
-        <v>688</v>
-      </c>
-      <c r="F260">
-        <v>4.0</v>
-      </c>
-      <c r="G260" t="s">
-        <v>728</v>
-      </c>
-      <c r="H260" t="s">
-        <v>729</v>
-      </c>
-      <c r="I260" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="261" spans="1:9">
       <c r="A261" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B261" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C261" t="s">
-        <v>240</v>
+        <v>117</v>
       </c>
       <c r="E261" t="s">
         <v>688</v>
       </c>
       <c r="F261">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="G261" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="H261" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="I261" t="s">
-        <v>609</v>
+        <v>306</v>
       </c>
     </row>
     <row r="262" spans="1:9">
       <c r="A262" t="s">
-        <v>440</v>
+        <v>731</v>
       </c>
       <c r="B262" t="s">
-        <v>441</v>
+        <v>732</v>
       </c>
       <c r="C262" t="s">
-        <v>117</v>
+        <v>240</v>
       </c>
       <c r="E262" t="s">
-        <v>346</v>
+        <v>688</v>
       </c>
       <c r="F262">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G262" t="s">
+        <v>733</v>
+      </c>
+      <c r="H262" t="s">
         <v>734</v>
       </c>
-      <c r="H262" t="s">
-        <v>735</v>
-      </c>
       <c r="I262" t="s">
-        <v>736</v>
+        <v>613</v>
       </c>
     </row>
     <row r="263" spans="1:9">
       <c r="A263" t="s">
-        <v>610</v>
+        <v>439</v>
       </c>
       <c r="B263" t="s">
-        <v>611</v>
+        <v>440</v>
       </c>
       <c r="C263" t="s">
-        <v>420</v>
+        <v>117</v>
       </c>
       <c r="E263" t="s">
-        <v>557</v>
+        <v>346</v>
       </c>
       <c r="F263">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G263" t="s">
+        <v>735</v>
+      </c>
+      <c r="H263" t="s">
+        <v>736</v>
+      </c>
+      <c r="I263" t="s">
         <v>737</v>
-      </c>
-      <c r="H263" t="s">
-        <v>738</v>
-      </c>
-      <c r="I263" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="264" spans="1:9">
       <c r="A264" t="s">
-        <v>714</v>
+        <v>614</v>
       </c>
       <c r="B264" t="s">
-        <v>715</v>
+        <v>615</v>
       </c>
       <c r="C264" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="E264" t="s">
-        <v>528</v>
+        <v>556</v>
       </c>
       <c r="F264">
         <v>3.0</v>
       </c>
       <c r="G264" t="s">
-        <v>524</v>
+        <v>738</v>
       </c>
       <c r="H264" t="s">
-        <v>724</v>
+        <v>739</v>
       </c>
       <c r="I264" t="s">
-        <v>739</v>
+        <v>658</v>
       </c>
     </row>
     <row r="265" spans="1:9">
       <c r="A265" t="s">
-        <v>634</v>
+        <v>713</v>
       </c>
       <c r="B265" t="s">
-        <v>635</v>
+        <v>714</v>
       </c>
       <c r="C265" t="s">
-        <v>420</v>
+        <v>325</v>
       </c>
       <c r="E265" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F265">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G265" t="s">
-        <v>636</v>
+        <v>523</v>
       </c>
       <c r="H265" t="s">
+        <v>725</v>
+      </c>
+      <c r="I265" t="s">
         <v>740</v>
-      </c>
-      <c r="I265" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="266" spans="1:9">
       <c r="A266" t="s">
+        <v>641</v>
+      </c>
+      <c r="B266" t="s">
         <v>642</v>
-      </c>
-      <c r="B266" t="s">
-        <v>643</v>
       </c>
       <c r="C266" t="s">
         <v>277</v>
       </c>
       <c r="E266" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F266">
         <v>7.0</v>
       </c>
       <c r="G266" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H266" t="s">
+        <v>741</v>
+      </c>
+      <c r="I266" t="s">
         <v>742</v>
-      </c>
-      <c r="I266" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="267" spans="1:9">
       <c r="A267" t="s">
+        <v>668</v>
+      </c>
+      <c r="B267" t="s">
         <v>669</v>
-      </c>
-      <c r="B267" t="s">
-        <v>670</v>
       </c>
       <c r="C267" t="s">
         <v>277</v>
       </c>
       <c r="E267" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F267">
         <v>4.0</v>
       </c>
       <c r="G267" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H267" t="s">
         <v>74</v>
       </c>
       <c r="I267" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="268" spans="1:9">
       <c r="A268" t="s">
+        <v>668</v>
+      </c>
+      <c r="B268" t="s">
         <v>669</v>
       </c>
-      <c r="B268" t="s">
-        <v>670</v>
-      </c>
       <c r="C268" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E268" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F268">
         <v>4.0</v>
       </c>
       <c r="G268" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H268" t="s">
         <v>74</v>
       </c>
       <c r="I268" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="269" spans="1:9">
       <c r="A269" t="s">
+        <v>743</v>
+      </c>
+      <c r="B269" t="s">
         <v>744</v>
       </c>
-      <c r="B269" t="s">
+      <c r="E269" t="s">
         <v>745</v>
-      </c>
-      <c r="E269" t="s">
-        <v>746</v>
       </c>
       <c r="F269">
         <v>1.0</v>
@@ -9997,278 +9997,278 @@
         <v>16</v>
       </c>
       <c r="I269" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="270" spans="1:9">
       <c r="A270" t="s">
-        <v>708</v>
+        <v>747</v>
       </c>
       <c r="B270" t="s">
-        <v>709</v>
+        <v>748</v>
       </c>
       <c r="C270" t="s">
-        <v>277</v>
+        <v>107</v>
       </c>
       <c r="E270" t="s">
-        <v>648</v>
+        <v>688</v>
       </c>
       <c r="F270">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G270" t="s">
-        <v>16</v>
+        <v>749</v>
       </c>
       <c r="H270" t="s">
-        <v>16</v>
+        <v>750</v>
       </c>
       <c r="I270" t="s">
-        <v>748</v>
+        <v>354</v>
       </c>
     </row>
     <row r="271" spans="1:9">
       <c r="A271" t="s">
-        <v>730</v>
+        <v>707</v>
       </c>
       <c r="B271" t="s">
-        <v>731</v>
+        <v>708</v>
       </c>
       <c r="C271" t="s">
-        <v>107</v>
+        <v>277</v>
       </c>
       <c r="E271" t="s">
-        <v>688</v>
+        <v>647</v>
       </c>
       <c r="F271">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="G271" t="s">
-        <v>749</v>
+        <v>16</v>
       </c>
       <c r="H271" t="s">
-        <v>750</v>
+        <v>16</v>
       </c>
       <c r="I271" t="s">
-        <v>668</v>
+        <v>751</v>
       </c>
     </row>
     <row r="272" spans="1:9">
       <c r="A272" t="s">
-        <v>541</v>
+        <v>731</v>
       </c>
       <c r="B272" t="s">
-        <v>542</v>
+        <v>732</v>
       </c>
       <c r="C272" t="s">
-        <v>398</v>
+        <v>107</v>
       </c>
       <c r="E272" t="s">
-        <v>528</v>
+        <v>688</v>
       </c>
       <c r="F272">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
       <c r="G272" t="s">
-        <v>614</v>
+        <v>752</v>
       </c>
       <c r="H272" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="I272" t="s">
-        <v>215</v>
+        <v>667</v>
       </c>
     </row>
     <row r="273" spans="1:9">
       <c r="A273" t="s">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="B273" t="s">
-        <v>556</v>
+        <v>541</v>
       </c>
       <c r="C273" t="s">
-        <v>420</v>
+        <v>398</v>
       </c>
       <c r="E273" t="s">
-        <v>557</v>
+        <v>527</v>
       </c>
       <c r="F273">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G273" t="s">
-        <v>707</v>
+        <v>618</v>
       </c>
       <c r="H273" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="I273" t="s">
-        <v>467</v>
+        <v>215</v>
       </c>
     </row>
     <row r="274" spans="1:9">
       <c r="A274" t="s">
-        <v>646</v>
+        <v>554</v>
       </c>
       <c r="B274" t="s">
-        <v>647</v>
+        <v>555</v>
       </c>
       <c r="C274" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="E274" t="s">
-        <v>648</v>
+        <v>556</v>
       </c>
       <c r="F274">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G274" t="s">
-        <v>753</v>
+        <v>706</v>
       </c>
       <c r="H274" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I274" t="s">
-        <v>649</v>
+        <v>466</v>
       </c>
     </row>
     <row r="275" spans="1:9">
       <c r="A275" t="s">
-        <v>711</v>
+        <v>645</v>
       </c>
       <c r="B275" t="s">
-        <v>712</v>
+        <v>646</v>
       </c>
       <c r="C275" t="s">
         <v>325</v>
       </c>
       <c r="E275" t="s">
+        <v>647</v>
+      </c>
+      <c r="F275">
+        <v>2.0</v>
+      </c>
+      <c r="G275" t="s">
+        <v>756</v>
+      </c>
+      <c r="H275" t="s">
+        <v>757</v>
+      </c>
+      <c r="I275" t="s">
         <v>648</v>
-      </c>
-      <c r="F275">
-        <v>4.0</v>
-      </c>
-      <c r="G275" t="s">
-        <v>16</v>
-      </c>
-      <c r="H275" t="s">
-        <v>16</v>
-      </c>
-      <c r="I275" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="276" spans="1:9">
       <c r="A276" t="s">
-        <v>755</v>
+        <v>710</v>
       </c>
       <c r="B276" t="s">
-        <v>756</v>
+        <v>711</v>
       </c>
       <c r="C276" t="s">
         <v>325</v>
       </c>
       <c r="E276" t="s">
-        <v>528</v>
+        <v>647</v>
       </c>
       <c r="F276">
         <v>4.0</v>
       </c>
       <c r="G276" t="s">
-        <v>524</v>
+        <v>16</v>
       </c>
       <c r="H276" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="I276" t="s">
-        <v>630</v>
+        <v>712</v>
       </c>
     </row>
     <row r="277" spans="1:9">
       <c r="A277" t="s">
-        <v>722</v>
+        <v>758</v>
       </c>
       <c r="B277" t="s">
-        <v>723</v>
+        <v>759</v>
       </c>
       <c r="C277" t="s">
-        <v>277</v>
+        <v>325</v>
       </c>
       <c r="E277" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F277">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G277" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H277" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I277" t="s">
-        <v>741</v>
+        <v>634</v>
       </c>
     </row>
     <row r="278" spans="1:9">
       <c r="A278" t="s">
-        <v>708</v>
+        <v>723</v>
       </c>
       <c r="B278" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="C278" t="s">
-        <v>325</v>
+        <v>277</v>
       </c>
       <c r="E278" t="s">
-        <v>648</v>
+        <v>527</v>
       </c>
       <c r="F278">
         <v>2.0</v>
       </c>
       <c r="G278" t="s">
-        <v>16</v>
+        <v>523</v>
       </c>
       <c r="H278" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="I278" t="s">
-        <v>649</v>
+        <v>717</v>
       </c>
     </row>
     <row r="279" spans="1:9">
       <c r="A279" t="s">
-        <v>757</v>
+        <v>707</v>
       </c>
       <c r="B279" t="s">
-        <v>758</v>
-      </c>
-      <c r="C279">
-        <v>40</v>
+        <v>708</v>
+      </c>
+      <c r="C279" t="s">
+        <v>325</v>
       </c>
       <c r="E279" t="s">
-        <v>93</v>
+        <v>647</v>
       </c>
       <c r="F279">
         <v>2.0</v>
       </c>
       <c r="G279" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="H279" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="I279" t="s">
-        <v>53</v>
+        <v>648</v>
       </c>
     </row>
     <row r="280" spans="1:9">
       <c r="A280" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B280" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C280">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E280" t="s">
         <v>93</v>
@@ -10288,221 +10288,221 @@
     </row>
     <row r="281" spans="1:9">
       <c r="A281" t="s">
-        <v>639</v>
+        <v>760</v>
       </c>
       <c r="B281" t="s">
-        <v>640</v>
-      </c>
-      <c r="C281" t="s">
-        <v>420</v>
+        <v>761</v>
+      </c>
+      <c r="C281">
+        <v>44</v>
       </c>
       <c r="E281" t="s">
-        <v>528</v>
+        <v>93</v>
       </c>
       <c r="F281">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G281" t="s">
-        <v>636</v>
+        <v>42</v>
       </c>
       <c r="H281" t="s">
-        <v>691</v>
+        <v>46</v>
       </c>
       <c r="I281" t="s">
-        <v>215</v>
+        <v>53</v>
       </c>
     </row>
     <row r="282" spans="1:9">
       <c r="A282" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B282" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C282" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E282" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F282">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G282" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H282" t="s">
-        <v>637</v>
+        <v>671</v>
       </c>
       <c r="I282" t="s">
-        <v>710</v>
+        <v>215</v>
       </c>
     </row>
     <row r="283" spans="1:9">
       <c r="A283" t="s">
-        <v>755</v>
+        <v>641</v>
       </c>
       <c r="B283" t="s">
-        <v>756</v>
+        <v>642</v>
       </c>
       <c r="C283" t="s">
-        <v>375</v>
+        <v>418</v>
       </c>
       <c r="E283" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F283">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G283" t="s">
-        <v>524</v>
+        <v>604</v>
       </c>
       <c r="H283" t="s">
-        <v>73</v>
+        <v>605</v>
       </c>
       <c r="I283" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
     </row>
     <row r="284" spans="1:9">
       <c r="A284" t="s">
-        <v>686</v>
+        <v>758</v>
       </c>
       <c r="B284" t="s">
-        <v>687</v>
+        <v>759</v>
       </c>
       <c r="C284" t="s">
-        <v>107</v>
+        <v>375</v>
       </c>
       <c r="E284" t="s">
-        <v>688</v>
+        <v>527</v>
       </c>
       <c r="F284">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G284" t="s">
-        <v>656</v>
+        <v>523</v>
       </c>
       <c r="H284" t="s">
-        <v>656</v>
+        <v>73</v>
       </c>
       <c r="I284" t="s">
-        <v>517</v>
+        <v>722</v>
       </c>
     </row>
     <row r="285" spans="1:9">
       <c r="A285" t="s">
-        <v>759</v>
+        <v>727</v>
       </c>
       <c r="B285" t="s">
-        <v>760</v>
+        <v>728</v>
       </c>
       <c r="C285" t="s">
-        <v>240</v>
+        <v>107</v>
       </c>
       <c r="E285" t="s">
-        <v>346</v>
+        <v>688</v>
       </c>
       <c r="F285">
         <v>4.0</v>
       </c>
       <c r="G285" t="s">
-        <v>16</v>
+        <v>655</v>
       </c>
       <c r="H285" t="s">
-        <v>16</v>
+        <v>762</v>
       </c>
       <c r="I285" t="s">
-        <v>518</v>
+        <v>306</v>
       </c>
     </row>
     <row r="286" spans="1:9">
       <c r="A286" t="s">
-        <v>761</v>
+        <v>686</v>
       </c>
       <c r="B286" t="s">
-        <v>762</v>
+        <v>687</v>
       </c>
       <c r="C286" t="s">
-        <v>420</v>
+        <v>107</v>
       </c>
       <c r="E286" t="s">
-        <v>763</v>
+        <v>688</v>
       </c>
       <c r="F286">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G286" t="s">
-        <v>764</v>
+        <v>655</v>
       </c>
       <c r="H286" t="s">
-        <v>765</v>
+        <v>655</v>
       </c>
       <c r="I286" t="s">
-        <v>766</v>
+        <v>516</v>
       </c>
     </row>
     <row r="287" spans="1:9">
       <c r="A287" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="B287" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="C287" t="s">
-        <v>107</v>
+        <v>240</v>
       </c>
       <c r="E287" t="s">
-        <v>688</v>
+        <v>346</v>
       </c>
       <c r="F287">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G287" t="s">
-        <v>769</v>
+        <v>16</v>
       </c>
       <c r="H287" t="s">
-        <v>770</v>
+        <v>16</v>
       </c>
       <c r="I287" t="s">
-        <v>354</v>
+        <v>517</v>
       </c>
     </row>
     <row r="288" spans="1:9">
       <c r="A288" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="B288" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="C288" t="s">
-        <v>117</v>
+        <v>418</v>
       </c>
       <c r="E288" t="s">
-        <v>688</v>
+        <v>767</v>
       </c>
       <c r="F288">
         <v>10.0</v>
       </c>
       <c r="G288" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="H288" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="I288" t="s">
-        <v>710</v>
+        <v>770</v>
       </c>
     </row>
     <row r="289" spans="1:9">
       <c r="A289" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B289" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="C289" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E289" t="s">
         <v>688</v>
@@ -10511,238 +10511,238 @@
         <v>10.0</v>
       </c>
       <c r="G289" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="H289" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="I289" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="290" spans="1:9">
       <c r="A290" t="s">
-        <v>717</v>
+        <v>775</v>
       </c>
       <c r="B290" t="s">
-        <v>718</v>
+        <v>776</v>
       </c>
       <c r="C290" t="s">
-        <v>420</v>
+        <v>107</v>
       </c>
       <c r="E290" t="s">
-        <v>648</v>
+        <v>688</v>
       </c>
       <c r="F290">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="G290" t="s">
-        <v>16</v>
+        <v>777</v>
       </c>
       <c r="H290" t="s">
-        <v>16</v>
+        <v>778</v>
       </c>
       <c r="I290" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
     </row>
     <row r="291" spans="1:9">
       <c r="A291" t="s">
-        <v>639</v>
+        <v>718</v>
       </c>
       <c r="B291" t="s">
-        <v>640</v>
+        <v>719</v>
       </c>
       <c r="C291" t="s">
-        <v>277</v>
+        <v>418</v>
       </c>
       <c r="E291" t="s">
-        <v>528</v>
+        <v>647</v>
       </c>
       <c r="F291">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G291" t="s">
-        <v>636</v>
+        <v>16</v>
       </c>
       <c r="H291" t="s">
-        <v>779</v>
+        <v>16</v>
       </c>
       <c r="I291" t="s">
-        <v>153</v>
+        <v>696</v>
       </c>
     </row>
     <row r="292" spans="1:9">
       <c r="A292" t="s">
-        <v>780</v>
+        <v>638</v>
       </c>
       <c r="B292" t="s">
-        <v>781</v>
+        <v>639</v>
       </c>
       <c r="C292" t="s">
-        <v>375</v>
+        <v>277</v>
       </c>
       <c r="E292" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F292">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G292" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H292" t="s">
-        <v>691</v>
+        <v>779</v>
       </c>
       <c r="I292" t="s">
-        <v>782</v>
+        <v>153</v>
       </c>
     </row>
     <row r="293" spans="1:9">
       <c r="A293" t="s">
-        <v>628</v>
+        <v>780</v>
       </c>
       <c r="B293" t="s">
-        <v>629</v>
+        <v>781</v>
       </c>
       <c r="C293" t="s">
-        <v>277</v>
+        <v>375</v>
       </c>
       <c r="E293" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F293">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G293" t="s">
-        <v>524</v>
+        <v>604</v>
       </c>
       <c r="H293" t="s">
-        <v>73</v>
+        <v>671</v>
       </c>
       <c r="I293" t="s">
-        <v>721</v>
+        <v>782</v>
       </c>
     </row>
     <row r="294" spans="1:9">
       <c r="A294" t="s">
-        <v>511</v>
+        <v>632</v>
       </c>
       <c r="B294" t="s">
-        <v>512</v>
+        <v>633</v>
       </c>
       <c r="C294" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="E294" t="s">
-        <v>346</v>
+        <v>527</v>
       </c>
       <c r="F294">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G294" t="s">
-        <v>783</v>
+        <v>523</v>
       </c>
       <c r="H294" t="s">
-        <v>784</v>
+        <v>73</v>
       </c>
       <c r="I294" t="s">
-        <v>785</v>
+        <v>722</v>
       </c>
     </row>
     <row r="295" spans="1:9">
       <c r="A295" t="s">
-        <v>717</v>
+        <v>510</v>
       </c>
       <c r="B295" t="s">
-        <v>718</v>
+        <v>511</v>
       </c>
       <c r="C295" t="s">
-        <v>325</v>
+        <v>240</v>
       </c>
       <c r="E295" t="s">
-        <v>648</v>
+        <v>346</v>
       </c>
       <c r="F295">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G295" t="s">
-        <v>16</v>
+        <v>783</v>
       </c>
       <c r="H295" t="s">
-        <v>16</v>
+        <v>784</v>
       </c>
       <c r="I295" t="s">
-        <v>659</v>
+        <v>785</v>
       </c>
     </row>
     <row r="296" spans="1:9">
       <c r="A296" t="s">
-        <v>786</v>
+        <v>718</v>
       </c>
       <c r="B296" t="s">
-        <v>787</v>
+        <v>719</v>
       </c>
       <c r="C296" t="s">
-        <v>107</v>
+        <v>325</v>
       </c>
       <c r="E296" t="s">
-        <v>688</v>
+        <v>647</v>
       </c>
       <c r="F296">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G296" t="s">
-        <v>777</v>
+        <v>16</v>
       </c>
       <c r="H296" t="s">
-        <v>778</v>
+        <v>16</v>
       </c>
       <c r="I296" t="s">
-        <v>710</v>
+        <v>658</v>
       </c>
     </row>
     <row r="297" spans="1:9">
       <c r="A297" t="s">
-        <v>717</v>
+        <v>786</v>
       </c>
       <c r="B297" t="s">
-        <v>718</v>
+        <v>787</v>
       </c>
       <c r="C297" t="s">
-        <v>375</v>
+        <v>107</v>
       </c>
       <c r="E297" t="s">
-        <v>648</v>
+        <v>688</v>
       </c>
       <c r="F297">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="G297" t="s">
-        <v>16</v>
+        <v>777</v>
       </c>
       <c r="H297" t="s">
-        <v>16</v>
+        <v>778</v>
       </c>
       <c r="I297" t="s">
-        <v>788</v>
+        <v>709</v>
       </c>
     </row>
     <row r="298" spans="1:9">
       <c r="A298" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B298" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C298" t="s">
-        <v>277</v>
+        <v>375</v>
       </c>
       <c r="E298" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="F298">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="G298" t="s">
         <v>16</v>
@@ -10751,388 +10751,388 @@
         <v>16</v>
       </c>
       <c r="I298" t="s">
-        <v>659</v>
+        <v>788</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="A299" t="s">
-        <v>767</v>
+        <v>718</v>
       </c>
       <c r="B299" t="s">
-        <v>768</v>
+        <v>719</v>
       </c>
       <c r="C299" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="E299" t="s">
-        <v>688</v>
+        <v>647</v>
       </c>
       <c r="F299">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G299" t="s">
-        <v>777</v>
+        <v>16</v>
       </c>
       <c r="H299" t="s">
-        <v>777</v>
+        <v>16</v>
       </c>
       <c r="I299" t="s">
-        <v>517</v>
+        <v>658</v>
       </c>
     </row>
     <row r="300" spans="1:9">
       <c r="A300" t="s">
-        <v>714</v>
+        <v>747</v>
       </c>
       <c r="B300" t="s">
-        <v>715</v>
+        <v>748</v>
       </c>
       <c r="C300" t="s">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="E300" t="s">
-        <v>528</v>
+        <v>688</v>
       </c>
       <c r="F300">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G300" t="s">
-        <v>524</v>
+        <v>777</v>
       </c>
       <c r="H300" t="s">
-        <v>73</v>
+        <v>777</v>
       </c>
       <c r="I300" t="s">
-        <v>713</v>
+        <v>516</v>
       </c>
     </row>
     <row r="301" spans="1:9">
       <c r="A301" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="B301" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="C301" t="s">
-        <v>107</v>
+        <v>418</v>
       </c>
       <c r="E301" t="s">
-        <v>688</v>
+        <v>527</v>
       </c>
       <c r="F301">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G301" t="s">
-        <v>656</v>
+        <v>523</v>
       </c>
       <c r="H301" t="s">
-        <v>789</v>
+        <v>73</v>
       </c>
       <c r="I301" t="s">
-        <v>306</v>
+        <v>712</v>
       </c>
     </row>
     <row r="302" spans="1:9">
       <c r="A302" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="B302" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="C302" t="s">
-        <v>375</v>
+        <v>107</v>
       </c>
       <c r="E302" t="s">
-        <v>648</v>
+        <v>688</v>
       </c>
       <c r="F302">
         <v>4.0</v>
       </c>
       <c r="G302" t="s">
-        <v>16</v>
+        <v>655</v>
       </c>
       <c r="H302" t="s">
-        <v>16</v>
+        <v>762</v>
       </c>
       <c r="I302" t="s">
-        <v>713</v>
+        <v>306</v>
       </c>
     </row>
     <row r="303" spans="1:9">
       <c r="A303" t="s">
-        <v>771</v>
+        <v>710</v>
       </c>
       <c r="B303" t="s">
-        <v>772</v>
+        <v>711</v>
       </c>
       <c r="C303" t="s">
-        <v>107</v>
+        <v>375</v>
       </c>
       <c r="E303" t="s">
-        <v>688</v>
+        <v>647</v>
       </c>
       <c r="F303">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="G303" t="s">
-        <v>773</v>
+        <v>16</v>
       </c>
       <c r="H303" t="s">
-        <v>790</v>
+        <v>16</v>
       </c>
       <c r="I303" t="s">
-        <v>791</v>
+        <v>712</v>
       </c>
     </row>
     <row r="304" spans="1:9">
       <c r="A304" t="s">
-        <v>628</v>
+        <v>771</v>
       </c>
       <c r="B304" t="s">
-        <v>629</v>
+        <v>772</v>
       </c>
       <c r="C304" t="s">
-        <v>420</v>
+        <v>107</v>
       </c>
       <c r="E304" t="s">
-        <v>528</v>
+        <v>688</v>
       </c>
       <c r="F304">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="G304" t="s">
-        <v>524</v>
+        <v>773</v>
       </c>
       <c r="H304" t="s">
-        <v>524</v>
+        <v>789</v>
       </c>
       <c r="I304" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305" t="s">
-        <v>755</v>
+        <v>632</v>
       </c>
       <c r="B305" t="s">
-        <v>756</v>
+        <v>633</v>
       </c>
       <c r="C305" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E305" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F305">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G305" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H305" t="s">
-        <v>724</v>
+        <v>523</v>
       </c>
       <c r="I305" t="s">
-        <v>725</v>
+        <v>791</v>
       </c>
     </row>
     <row r="306" spans="1:9">
       <c r="A306" t="s">
-        <v>719</v>
+        <v>758</v>
       </c>
       <c r="B306" t="s">
-        <v>720</v>
+        <v>759</v>
       </c>
       <c r="C306" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="E306" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F306">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G306" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H306" t="s">
-        <v>73</v>
+        <v>725</v>
       </c>
       <c r="I306" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
     </row>
     <row r="307" spans="1:9">
       <c r="A307" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B307" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C307" t="s">
         <v>325</v>
       </c>
       <c r="E307" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F307">
         <v>2.0</v>
       </c>
       <c r="G307" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H307" t="s">
         <v>73</v>
       </c>
       <c r="I307" t="s">
-        <v>741</v>
+        <v>722</v>
       </c>
     </row>
     <row r="308" spans="1:9">
       <c r="A308" t="s">
-        <v>775</v>
+        <v>723</v>
       </c>
       <c r="B308" t="s">
-        <v>776</v>
+        <v>724</v>
       </c>
       <c r="C308" t="s">
-        <v>240</v>
+        <v>325</v>
       </c>
       <c r="E308" t="s">
-        <v>688</v>
+        <v>527</v>
       </c>
       <c r="F308">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G308" t="s">
-        <v>777</v>
+        <v>523</v>
       </c>
       <c r="H308" t="s">
-        <v>793</v>
+        <v>73</v>
       </c>
       <c r="I308" t="s">
-        <v>739</v>
+        <v>717</v>
       </c>
     </row>
     <row r="309" spans="1:9">
       <c r="A309" t="s">
-        <v>794</v>
+        <v>775</v>
       </c>
       <c r="B309" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="C309" t="s">
-        <v>103</v>
+        <v>240</v>
       </c>
       <c r="E309" t="s">
-        <v>346</v>
+        <v>688</v>
       </c>
       <c r="F309">
         <v>6.0</v>
       </c>
       <c r="G309" t="s">
-        <v>16</v>
+        <v>777</v>
       </c>
       <c r="H309" t="s">
-        <v>16</v>
+        <v>792</v>
       </c>
       <c r="I309" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
     </row>
     <row r="310" spans="1:9">
       <c r="A310" t="s">
-        <v>714</v>
+        <v>793</v>
       </c>
       <c r="B310" t="s">
-        <v>715</v>
+        <v>794</v>
       </c>
       <c r="C310" t="s">
-        <v>277</v>
+        <v>103</v>
       </c>
       <c r="E310" t="s">
-        <v>528</v>
+        <v>346</v>
       </c>
       <c r="F310">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G310" t="s">
-        <v>524</v>
+        <v>16</v>
       </c>
       <c r="H310" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I310" t="s">
-        <v>713</v>
+        <v>737</v>
       </c>
     </row>
     <row r="311" spans="1:9">
       <c r="A311" t="s">
-        <v>796</v>
+        <v>713</v>
       </c>
       <c r="B311" t="s">
-        <v>797</v>
+        <v>714</v>
       </c>
       <c r="C311" t="s">
-        <v>375</v>
+        <v>277</v>
       </c>
       <c r="E311" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F311">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G311" t="s">
-        <v>636</v>
+        <v>523</v>
       </c>
       <c r="H311" t="s">
-        <v>779</v>
+        <v>73</v>
       </c>
       <c r="I311" t="s">
-        <v>798</v>
+        <v>712</v>
       </c>
     </row>
     <row r="312" spans="1:9">
       <c r="A312" t="s">
-        <v>786</v>
+        <v>795</v>
       </c>
       <c r="B312" t="s">
-        <v>787</v>
+        <v>796</v>
       </c>
       <c r="C312" t="s">
-        <v>103</v>
+        <v>375</v>
       </c>
       <c r="E312" t="s">
-        <v>688</v>
+        <v>527</v>
       </c>
       <c r="F312">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G312" t="s">
-        <v>16</v>
+        <v>604</v>
       </c>
       <c r="H312" t="s">
-        <v>16</v>
+        <v>779</v>
       </c>
       <c r="I312" t="s">
-        <v>710</v>
+        <v>797</v>
       </c>
     </row>
     <row r="313" spans="1:9">
       <c r="A313" t="s">
-        <v>759</v>
+        <v>786</v>
       </c>
       <c r="B313" t="s">
-        <v>760</v>
+        <v>787</v>
       </c>
       <c r="C313" t="s">
         <v>103</v>
       </c>
       <c r="E313" t="s">
-        <v>346</v>
+        <v>688</v>
       </c>
       <c r="F313">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="G313" t="s">
         <v>16</v>
@@ -11141,108 +11141,108 @@
         <v>16</v>
       </c>
       <c r="I313" t="s">
-        <v>799</v>
+        <v>709</v>
       </c>
     </row>
     <row r="314" spans="1:9">
       <c r="A314" t="s">
-        <v>726</v>
+        <v>763</v>
       </c>
       <c r="B314" t="s">
-        <v>727</v>
+        <v>764</v>
       </c>
       <c r="C314" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E314" t="s">
-        <v>688</v>
+        <v>346</v>
       </c>
       <c r="F314">
-        <v>4.0</v>
+        <v>11.0</v>
       </c>
       <c r="G314" t="s">
-        <v>656</v>
+        <v>16</v>
       </c>
       <c r="H314" t="s">
-        <v>789</v>
+        <v>16</v>
       </c>
       <c r="I314" t="s">
-        <v>306</v>
+        <v>798</v>
       </c>
     </row>
     <row r="315" spans="1:9">
       <c r="A315" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="B315" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C315" t="s">
         <v>277</v>
       </c>
       <c r="E315" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F315">
         <v>2.0</v>
       </c>
       <c r="G315" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H315" t="s">
         <v>73</v>
       </c>
       <c r="I315" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="A316" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B316" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C316" t="s">
         <v>277</v>
       </c>
       <c r="E316" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F316">
         <v>2.0</v>
       </c>
       <c r="G316" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H316" t="s">
         <v>73</v>
       </c>
       <c r="I316" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="317" spans="1:9">
       <c r="A317" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B317" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C317" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E317" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F317">
         <v>1.0</v>
       </c>
       <c r="G317" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H317" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I317" t="s">
         <v>152</v>
@@ -11259,53 +11259,53 @@
         <v>325</v>
       </c>
       <c r="E318" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F318">
         <v>3.0</v>
       </c>
       <c r="G318" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H318" t="s">
         <v>779</v>
       </c>
       <c r="I318" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="319" spans="1:9">
       <c r="A319" t="s">
+        <v>795</v>
+      </c>
+      <c r="B319" t="s">
         <v>796</v>
-      </c>
-      <c r="B319" t="s">
-        <v>797</v>
       </c>
       <c r="C319" t="s">
         <v>325</v>
       </c>
       <c r="E319" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F319">
         <v>3.0</v>
       </c>
       <c r="G319" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H319" t="s">
         <v>779</v>
       </c>
       <c r="I319" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="A320" t="s">
+        <v>799</v>
+      </c>
+      <c r="B320" t="s">
         <v>800</v>
-      </c>
-      <c r="B320" t="s">
-        <v>801</v>
       </c>
       <c r="C320" t="s">
         <v>103</v>
@@ -11317,21 +11317,21 @@
         <v>8.0</v>
       </c>
       <c r="G320" t="s">
+        <v>801</v>
+      </c>
+      <c r="H320" t="s">
         <v>802</v>
       </c>
-      <c r="H320" t="s">
+      <c r="I320" t="s">
         <v>803</v>
-      </c>
-      <c r="I320" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="A321" t="s">
+        <v>804</v>
+      </c>
+      <c r="B321" t="s">
         <v>805</v>
-      </c>
-      <c r="B321" t="s">
-        <v>806</v>
       </c>
       <c r="C321" t="s">
         <v>107</v>
@@ -11349,111 +11349,111 @@
         <v>679</v>
       </c>
       <c r="I321" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="A322" t="s">
-        <v>767</v>
+        <v>806</v>
       </c>
       <c r="B322" t="s">
-        <v>768</v>
+        <v>807</v>
       </c>
       <c r="C322" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="E322" t="s">
         <v>688</v>
       </c>
       <c r="F322">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G322" t="s">
-        <v>807</v>
+        <v>777</v>
       </c>
       <c r="H322" t="s">
-        <v>807</v>
+        <v>680</v>
       </c>
       <c r="I322" t="s">
-        <v>517</v>
+        <v>808</v>
       </c>
     </row>
     <row r="323" spans="1:9">
       <c r="A323" t="s">
-        <v>730</v>
+        <v>747</v>
       </c>
       <c r="B323" t="s">
-        <v>731</v>
+        <v>748</v>
       </c>
       <c r="C323" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="E323" t="s">
         <v>688</v>
       </c>
       <c r="F323">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G323" t="s">
-        <v>16</v>
+        <v>809</v>
       </c>
       <c r="H323" t="s">
-        <v>16</v>
+        <v>809</v>
       </c>
       <c r="I323" t="s">
-        <v>609</v>
+        <v>516</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="A324" t="s">
-        <v>642</v>
+        <v>731</v>
       </c>
       <c r="B324" t="s">
-        <v>643</v>
+        <v>732</v>
       </c>
       <c r="C324" t="s">
-        <v>398</v>
+        <v>103</v>
       </c>
       <c r="E324" t="s">
-        <v>528</v>
+        <v>688</v>
       </c>
       <c r="F324">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="G324" t="s">
-        <v>636</v>
+        <v>16</v>
       </c>
       <c r="H324" t="s">
-        <v>779</v>
+        <v>16</v>
       </c>
       <c r="I324" t="s">
-        <v>739</v>
+        <v>613</v>
       </c>
     </row>
     <row r="325" spans="1:9">
       <c r="A325" t="s">
-        <v>808</v>
+        <v>641</v>
       </c>
       <c r="B325" t="s">
-        <v>809</v>
+        <v>642</v>
       </c>
       <c r="C325" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="E325" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F325">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G325" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H325" t="s">
+        <v>779</v>
+      </c>
+      <c r="I325" t="s">
         <v>740</v>
-      </c>
-      <c r="I325" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="326" spans="1:9">
@@ -11467,45 +11467,45 @@
         <v>375</v>
       </c>
       <c r="E326" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F326">
         <v>2.0</v>
       </c>
       <c r="G326" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H326" t="s">
-        <v>740</v>
+        <v>716</v>
       </c>
       <c r="I326" t="s">
-        <v>741</v>
+        <v>712</v>
       </c>
     </row>
     <row r="327" spans="1:9">
       <c r="A327" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B327" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C327" t="s">
-        <v>325</v>
+        <v>375</v>
       </c>
       <c r="E327" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F327">
         <v>2.0</v>
       </c>
       <c r="G327" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H327" t="s">
-        <v>740</v>
+        <v>716</v>
       </c>
       <c r="I327" t="s">
-        <v>741</v>
+        <v>717</v>
       </c>
     </row>
     <row r="328" spans="1:9">
@@ -11516,85 +11516,85 @@
         <v>813</v>
       </c>
       <c r="C328" t="s">
-        <v>375</v>
+        <v>325</v>
       </c>
       <c r="E328" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F328">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G328" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H328" t="s">
-        <v>779</v>
+        <v>716</v>
       </c>
       <c r="I328" t="s">
-        <v>798</v>
+        <v>717</v>
       </c>
     </row>
     <row r="329" spans="1:9">
       <c r="A329" t="s">
-        <v>209</v>
+        <v>814</v>
       </c>
       <c r="B329" t="s">
-        <v>210</v>
-      </c>
-      <c r="C329">
-        <v>46</v>
+        <v>815</v>
+      </c>
+      <c r="C329" t="s">
+        <v>375</v>
       </c>
       <c r="E329" t="s">
-        <v>52</v>
+        <v>527</v>
       </c>
       <c r="F329">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G329" t="s">
-        <v>42</v>
+        <v>604</v>
       </c>
       <c r="H329" t="s">
-        <v>42</v>
+        <v>779</v>
       </c>
       <c r="I329" t="s">
-        <v>66</v>
+        <v>797</v>
       </c>
     </row>
     <row r="330" spans="1:9">
       <c r="A330" t="s">
-        <v>814</v>
+        <v>209</v>
       </c>
       <c r="B330" t="s">
-        <v>815</v>
+        <v>210</v>
       </c>
       <c r="C330">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E330" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="F330">
         <v>1.0</v>
       </c>
       <c r="G330" t="s">
-        <v>816</v>
+        <v>42</v>
       </c>
       <c r="H330" t="s">
-        <v>816</v>
+        <v>42</v>
       </c>
       <c r="I330" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="331" spans="1:9">
       <c r="A331" t="s">
-        <v>684</v>
+        <v>816</v>
       </c>
       <c r="B331" t="s">
-        <v>685</v>
+        <v>817</v>
       </c>
       <c r="C331">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E331" t="s">
         <v>93</v>
@@ -11603,10 +11603,10 @@
         <v>1.0</v>
       </c>
       <c r="G331" t="s">
-        <v>42</v>
+        <v>818</v>
       </c>
       <c r="H331" t="s">
-        <v>42</v>
+        <v>818</v>
       </c>
       <c r="I331" t="s">
         <v>70</v>
@@ -11614,88 +11614,88 @@
     </row>
     <row r="332" spans="1:9">
       <c r="A332" t="s">
-        <v>800</v>
+        <v>684</v>
       </c>
       <c r="B332" t="s">
-        <v>801</v>
-      </c>
-      <c r="C332" t="s">
-        <v>117</v>
+        <v>685</v>
+      </c>
+      <c r="C332">
+        <v>46</v>
       </c>
       <c r="E332" t="s">
-        <v>346</v>
+        <v>93</v>
       </c>
       <c r="F332">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G332" t="s">
-        <v>817</v>
+        <v>42</v>
       </c>
       <c r="H332" t="s">
-        <v>818</v>
+        <v>42</v>
       </c>
       <c r="I332" t="s">
-        <v>444</v>
+        <v>70</v>
       </c>
     </row>
     <row r="333" spans="1:9">
       <c r="A333" t="s">
-        <v>819</v>
+        <v>731</v>
       </c>
       <c r="B333" t="s">
-        <v>820</v>
+        <v>732</v>
       </c>
       <c r="C333" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E333" t="s">
         <v>688</v>
       </c>
       <c r="F333">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G333" t="s">
-        <v>656</v>
+        <v>16</v>
       </c>
       <c r="H333" t="s">
-        <v>821</v>
+        <v>16</v>
       </c>
       <c r="I333" t="s">
-        <v>678</v>
+        <v>558</v>
       </c>
     </row>
     <row r="334" spans="1:9">
       <c r="A334" t="s">
-        <v>771</v>
+        <v>799</v>
       </c>
       <c r="B334" t="s">
-        <v>772</v>
+        <v>800</v>
       </c>
       <c r="C334" t="s">
-        <v>240</v>
+        <v>117</v>
       </c>
       <c r="E334" t="s">
-        <v>688</v>
+        <v>346</v>
       </c>
       <c r="F334">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G334" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="H334" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="I334" t="s">
-        <v>710</v>
+        <v>443</v>
       </c>
     </row>
     <row r="335" spans="1:9">
       <c r="A335" t="s">
-        <v>786</v>
+        <v>806</v>
       </c>
       <c r="B335" t="s">
-        <v>787</v>
+        <v>807</v>
       </c>
       <c r="C335" t="s">
         <v>117</v>
@@ -11704,397 +11704,397 @@
         <v>688</v>
       </c>
       <c r="F335">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G335" t="s">
-        <v>16</v>
+        <v>655</v>
       </c>
       <c r="H335" t="s">
-        <v>16</v>
+        <v>821</v>
       </c>
       <c r="I335" t="s">
-        <v>739</v>
+        <v>678</v>
       </c>
     </row>
     <row r="336" spans="1:9">
       <c r="A336" t="s">
-        <v>755</v>
+        <v>771</v>
       </c>
       <c r="B336" t="s">
-        <v>756</v>
+        <v>772</v>
       </c>
       <c r="C336" t="s">
-        <v>398</v>
+        <v>240</v>
       </c>
       <c r="E336" t="s">
-        <v>528</v>
+        <v>688</v>
       </c>
       <c r="F336">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="G336" t="s">
-        <v>524</v>
+        <v>822</v>
       </c>
       <c r="H336" t="s">
-        <v>73</v>
+        <v>823</v>
       </c>
       <c r="I336" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
     </row>
     <row r="337" spans="1:9">
       <c r="A337" t="s">
-        <v>722</v>
+        <v>786</v>
       </c>
       <c r="B337" t="s">
-        <v>723</v>
+        <v>787</v>
       </c>
       <c r="C337" t="s">
-        <v>398</v>
+        <v>117</v>
       </c>
       <c r="E337" t="s">
-        <v>528</v>
+        <v>688</v>
       </c>
       <c r="F337">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G337" t="s">
-        <v>524</v>
+        <v>16</v>
       </c>
       <c r="H337" t="s">
-        <v>524</v>
+        <v>16</v>
       </c>
       <c r="I337" t="s">
-        <v>152</v>
+        <v>740</v>
       </c>
     </row>
     <row r="338" spans="1:9">
       <c r="A338" t="s">
-        <v>440</v>
+        <v>758</v>
       </c>
       <c r="B338" t="s">
-        <v>441</v>
+        <v>759</v>
       </c>
       <c r="C338" t="s">
-        <v>103</v>
+        <v>398</v>
       </c>
       <c r="E338" t="s">
-        <v>346</v>
+        <v>527</v>
       </c>
       <c r="F338">
         <v>2.0</v>
       </c>
       <c r="G338" t="s">
-        <v>824</v>
+        <v>523</v>
       </c>
       <c r="H338" t="s">
-        <v>825</v>
+        <v>73</v>
       </c>
       <c r="I338" t="s">
-        <v>444</v>
+        <v>722</v>
       </c>
     </row>
     <row r="339" spans="1:9">
       <c r="A339" t="s">
-        <v>759</v>
+        <v>723</v>
       </c>
       <c r="B339" t="s">
-        <v>760</v>
+        <v>724</v>
       </c>
       <c r="C339" t="s">
-        <v>120</v>
+        <v>398</v>
       </c>
       <c r="E339" t="s">
-        <v>346</v>
+        <v>527</v>
       </c>
       <c r="F339">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
       <c r="G339" t="s">
-        <v>16</v>
+        <v>523</v>
       </c>
       <c r="H339" t="s">
-        <v>16</v>
+        <v>523</v>
       </c>
       <c r="I339" t="s">
-        <v>482</v>
+        <v>152</v>
       </c>
     </row>
     <row r="340" spans="1:9">
       <c r="A340" t="s">
-        <v>775</v>
+        <v>439</v>
       </c>
       <c r="B340" t="s">
-        <v>776</v>
+        <v>440</v>
       </c>
       <c r="C340" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="E340" t="s">
-        <v>688</v>
+        <v>346</v>
       </c>
       <c r="F340">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="G340" t="s">
-        <v>777</v>
+        <v>824</v>
       </c>
       <c r="H340" t="s">
-        <v>680</v>
+        <v>825</v>
       </c>
       <c r="I340" t="s">
-        <v>716</v>
+        <v>443</v>
       </c>
     </row>
     <row r="341" spans="1:9">
       <c r="A341" t="s">
-        <v>826</v>
+        <v>763</v>
       </c>
       <c r="B341" t="s">
-        <v>827</v>
+        <v>764</v>
       </c>
       <c r="C341" t="s">
-        <v>375</v>
+        <v>120</v>
       </c>
       <c r="E341" t="s">
-        <v>528</v>
+        <v>346</v>
       </c>
       <c r="F341">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="G341" t="s">
-        <v>636</v>
+        <v>16</v>
       </c>
       <c r="H341" t="s">
-        <v>740</v>
+        <v>16</v>
       </c>
       <c r="I341" t="s">
-        <v>721</v>
+        <v>481</v>
       </c>
     </row>
     <row r="342" spans="1:9">
       <c r="A342" t="s">
-        <v>639</v>
+        <v>775</v>
       </c>
       <c r="B342" t="s">
-        <v>640</v>
+        <v>776</v>
       </c>
       <c r="C342" t="s">
-        <v>398</v>
+        <v>120</v>
       </c>
       <c r="E342" t="s">
-        <v>528</v>
+        <v>688</v>
       </c>
       <c r="F342">
-        <v>2.0</v>
+        <v>17.0</v>
       </c>
       <c r="G342" t="s">
-        <v>636</v>
+        <v>16</v>
       </c>
       <c r="H342" t="s">
-        <v>740</v>
+        <v>16</v>
       </c>
       <c r="I342" t="s">
-        <v>741</v>
+        <v>826</v>
       </c>
     </row>
     <row r="343" spans="1:9">
       <c r="A343" t="s">
-        <v>828</v>
+        <v>775</v>
       </c>
       <c r="B343" t="s">
-        <v>829</v>
+        <v>776</v>
       </c>
       <c r="C343" t="s">
-        <v>375</v>
+        <v>117</v>
       </c>
       <c r="E343" t="s">
-        <v>528</v>
+        <v>688</v>
       </c>
       <c r="F343">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="G343" t="s">
-        <v>636</v>
+        <v>777</v>
       </c>
       <c r="H343" t="s">
-        <v>740</v>
+        <v>680</v>
       </c>
       <c r="I343" t="s">
-        <v>741</v>
+        <v>715</v>
       </c>
     </row>
     <row r="344" spans="1:9">
       <c r="A344" t="s">
-        <v>796</v>
+        <v>775</v>
       </c>
       <c r="B344" t="s">
-        <v>797</v>
+        <v>776</v>
       </c>
       <c r="C344" t="s">
-        <v>420</v>
+        <v>103</v>
       </c>
       <c r="E344" t="s">
-        <v>528</v>
+        <v>688</v>
       </c>
       <c r="F344">
-        <v>2.0</v>
+        <v>18.0</v>
       </c>
       <c r="G344" t="s">
-        <v>636</v>
+        <v>16</v>
       </c>
       <c r="H344" t="s">
-        <v>740</v>
+        <v>16</v>
       </c>
       <c r="I344" t="s">
-        <v>160</v>
+        <v>827</v>
       </c>
     </row>
     <row r="345" spans="1:9">
       <c r="A345" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B345" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C345" t="s">
-        <v>117</v>
+        <v>375</v>
       </c>
       <c r="E345" t="s">
-        <v>346</v>
+        <v>527</v>
       </c>
       <c r="F345">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="G345" t="s">
-        <v>832</v>
+        <v>604</v>
       </c>
       <c r="H345" t="s">
-        <v>833</v>
+        <v>716</v>
       </c>
       <c r="I345" t="s">
-        <v>804</v>
+        <v>722</v>
       </c>
     </row>
     <row r="346" spans="1:9">
       <c r="A346" t="s">
-        <v>819</v>
+        <v>638</v>
       </c>
       <c r="B346" t="s">
-        <v>820</v>
+        <v>639</v>
       </c>
       <c r="C346" t="s">
-        <v>107</v>
+        <v>398</v>
       </c>
       <c r="E346" t="s">
-        <v>688</v>
+        <v>527</v>
       </c>
       <c r="F346">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="G346" t="s">
-        <v>777</v>
+        <v>604</v>
       </c>
       <c r="H346" t="s">
-        <v>680</v>
+        <v>716</v>
       </c>
       <c r="I346" t="s">
-        <v>834</v>
+        <v>717</v>
       </c>
     </row>
     <row r="347" spans="1:9">
       <c r="A347" t="s">
-        <v>702</v>
+        <v>830</v>
       </c>
       <c r="B347" t="s">
-        <v>703</v>
+        <v>831</v>
       </c>
       <c r="C347" t="s">
-        <v>107</v>
+        <v>375</v>
       </c>
       <c r="E347" t="s">
-        <v>241</v>
+        <v>527</v>
       </c>
       <c r="F347">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G347" t="s">
-        <v>16</v>
+        <v>604</v>
       </c>
       <c r="H347" t="s">
-        <v>16</v>
+        <v>716</v>
       </c>
       <c r="I347" t="s">
-        <v>392</v>
+        <v>717</v>
       </c>
     </row>
     <row r="348" spans="1:9">
       <c r="A348" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B348" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C348" t="s">
-        <v>120</v>
+        <v>418</v>
       </c>
       <c r="E348" t="s">
-        <v>346</v>
+        <v>527</v>
       </c>
       <c r="F348">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G348" t="s">
-        <v>16</v>
+        <v>604</v>
       </c>
       <c r="H348" t="s">
-        <v>16</v>
+        <v>716</v>
       </c>
       <c r="I348" t="s">
-        <v>518</v>
+        <v>160</v>
       </c>
     </row>
     <row r="349" spans="1:9">
       <c r="A349" t="s">
-        <v>702</v>
+        <v>832</v>
       </c>
       <c r="B349" t="s">
-        <v>703</v>
+        <v>833</v>
       </c>
       <c r="C349" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E349" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="F349">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="G349" t="s">
-        <v>16</v>
+        <v>834</v>
       </c>
       <c r="H349" t="s">
-        <v>16</v>
+        <v>835</v>
       </c>
       <c r="I349" t="s">
-        <v>392</v>
+        <v>803</v>
       </c>
     </row>
     <row r="350" spans="1:9">
       <c r="A350" t="s">
-        <v>786</v>
+        <v>701</v>
       </c>
       <c r="B350" t="s">
-        <v>787</v>
+        <v>702</v>
       </c>
       <c r="C350" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="E350" t="s">
-        <v>688</v>
+        <v>241</v>
       </c>
       <c r="F350">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G350" t="s">
         <v>16</v>
@@ -12103,24 +12103,24 @@
         <v>16</v>
       </c>
       <c r="I350" t="s">
-        <v>710</v>
+        <v>392</v>
       </c>
     </row>
     <row r="351" spans="1:9">
       <c r="A351" t="s">
-        <v>759</v>
+        <v>793</v>
       </c>
       <c r="B351" t="s">
-        <v>760</v>
+        <v>794</v>
       </c>
       <c r="C351" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E351" t="s">
         <v>346</v>
       </c>
       <c r="F351">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G351" t="s">
         <v>16</v>
@@ -12129,41 +12129,41 @@
         <v>16</v>
       </c>
       <c r="I351" t="s">
-        <v>502</v>
+        <v>517</v>
       </c>
     </row>
     <row r="352" spans="1:9">
       <c r="A352" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="B352" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="C352" t="s">
-        <v>398</v>
+        <v>120</v>
       </c>
       <c r="E352" t="s">
-        <v>528</v>
+        <v>241</v>
       </c>
       <c r="F352">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G352" t="s">
-        <v>524</v>
+        <v>16</v>
       </c>
       <c r="H352" t="s">
-        <v>524</v>
+        <v>16</v>
       </c>
       <c r="I352" t="s">
-        <v>835</v>
+        <v>392</v>
       </c>
     </row>
     <row r="353" spans="1:9">
       <c r="A353" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
       <c r="B353" t="s">
-        <v>776</v>
+        <v>787</v>
       </c>
       <c r="C353" t="s">
         <v>120</v>
@@ -12172,7 +12172,7 @@
         <v>688</v>
       </c>
       <c r="F353">
-        <v>17.0</v>
+        <v>10.0</v>
       </c>
       <c r="G353" t="s">
         <v>16</v>
@@ -12181,24 +12181,24 @@
         <v>16</v>
       </c>
       <c r="I353" t="s">
-        <v>836</v>
+        <v>709</v>
       </c>
     </row>
     <row r="354" spans="1:9">
       <c r="A354" t="s">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="B354" t="s">
-        <v>776</v>
+        <v>764</v>
       </c>
       <c r="C354" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="E354" t="s">
-        <v>688</v>
+        <v>346</v>
       </c>
       <c r="F354">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="G354" t="s">
         <v>16</v>
@@ -12207,111 +12207,111 @@
         <v>16</v>
       </c>
       <c r="I354" t="s">
-        <v>837</v>
+        <v>501</v>
       </c>
     </row>
     <row r="355" spans="1:9">
       <c r="A355" t="s">
-        <v>628</v>
+        <v>713</v>
       </c>
       <c r="B355" t="s">
-        <v>629</v>
+        <v>714</v>
       </c>
       <c r="C355" t="s">
         <v>398</v>
       </c>
       <c r="E355" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F355">
         <v>1.0</v>
       </c>
       <c r="G355" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H355" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I355" t="s">
-        <v>792</v>
+        <v>836</v>
       </c>
     </row>
     <row r="356" spans="1:9">
       <c r="A356" t="s">
-        <v>719</v>
+        <v>632</v>
       </c>
       <c r="B356" t="s">
-        <v>720</v>
+        <v>633</v>
       </c>
       <c r="C356" t="s">
         <v>398</v>
       </c>
       <c r="E356" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F356">
         <v>1.0</v>
       </c>
       <c r="G356" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H356" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I356" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="357" spans="1:9">
       <c r="A357" t="s">
-        <v>838</v>
+        <v>720</v>
       </c>
       <c r="B357" t="s">
-        <v>839</v>
+        <v>721</v>
       </c>
       <c r="C357" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="E357" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F357">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G357" t="s">
-        <v>636</v>
+        <v>523</v>
       </c>
       <c r="H357" t="s">
-        <v>740</v>
+        <v>523</v>
       </c>
       <c r="I357" t="s">
-        <v>160</v>
+        <v>791</v>
       </c>
     </row>
     <row r="358" spans="1:9">
       <c r="A358" t="s">
-        <v>780</v>
+        <v>837</v>
       </c>
       <c r="B358" t="s">
-        <v>781</v>
+        <v>838</v>
       </c>
       <c r="C358" t="s">
-        <v>277</v>
+        <v>375</v>
       </c>
       <c r="E358" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F358">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G358" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H358" t="s">
-        <v>636</v>
+        <v>716</v>
       </c>
       <c r="I358" t="s">
-        <v>540</v>
+        <v>160</v>
       </c>
     </row>
     <row r="359" spans="1:9">
@@ -12322,45 +12322,45 @@
         <v>781</v>
       </c>
       <c r="C359" t="s">
-        <v>420</v>
+        <v>277</v>
       </c>
       <c r="E359" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F359">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G359" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H359" t="s">
-        <v>740</v>
+        <v>604</v>
       </c>
       <c r="I359" t="s">
-        <v>160</v>
+        <v>539</v>
       </c>
     </row>
     <row r="360" spans="1:9">
       <c r="A360" t="s">
-        <v>812</v>
+        <v>780</v>
       </c>
       <c r="B360" t="s">
-        <v>813</v>
+        <v>781</v>
       </c>
       <c r="C360" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="E360" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F360">
         <v>2.0</v>
       </c>
       <c r="G360" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H360" t="s">
-        <v>740</v>
+        <v>716</v>
       </c>
       <c r="I360" t="s">
         <v>160</v>
@@ -12368,25 +12368,25 @@
     </row>
     <row r="361" spans="1:9">
       <c r="A361" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B361" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C361" t="s">
-        <v>420</v>
+        <v>325</v>
       </c>
       <c r="E361" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F361">
         <v>2.0</v>
       </c>
       <c r="G361" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H361" t="s">
-        <v>740</v>
+        <v>716</v>
       </c>
       <c r="I361" t="s">
         <v>160</v>
@@ -12394,97 +12394,97 @@
     </row>
     <row r="362" spans="1:9">
       <c r="A362" t="s">
-        <v>794</v>
+        <v>814</v>
       </c>
       <c r="B362" t="s">
-        <v>795</v>
+        <v>815</v>
       </c>
       <c r="C362" t="s">
-        <v>107</v>
+        <v>418</v>
       </c>
       <c r="E362" t="s">
-        <v>346</v>
+        <v>527</v>
       </c>
       <c r="F362">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="G362" t="s">
-        <v>16</v>
+        <v>604</v>
       </c>
       <c r="H362" t="s">
-        <v>16</v>
+        <v>716</v>
       </c>
       <c r="I362" t="s">
-        <v>840</v>
+        <v>160</v>
       </c>
     </row>
     <row r="363" spans="1:9">
       <c r="A363" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="B363" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="C363" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="E363" t="s">
         <v>346</v>
       </c>
       <c r="F363">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G363" t="s">
-        <v>841</v>
+        <v>16</v>
       </c>
       <c r="H363" t="s">
-        <v>841</v>
+        <v>16</v>
       </c>
       <c r="I363" t="s">
-        <v>663</v>
+        <v>839</v>
       </c>
     </row>
     <row r="364" spans="1:9">
       <c r="A364" t="s">
-        <v>830</v>
+        <v>799</v>
       </c>
       <c r="B364" t="s">
-        <v>831</v>
+        <v>800</v>
       </c>
       <c r="C364" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="E364" t="s">
         <v>346</v>
       </c>
       <c r="F364">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G364" t="s">
-        <v>16</v>
+        <v>840</v>
       </c>
       <c r="H364" t="s">
-        <v>16</v>
+        <v>840</v>
       </c>
       <c r="I364" t="s">
-        <v>804</v>
+        <v>662</v>
       </c>
     </row>
     <row r="365" spans="1:9">
       <c r="A365" t="s">
-        <v>842</v>
+        <v>832</v>
       </c>
       <c r="B365" t="s">
-        <v>843</v>
+        <v>833</v>
       </c>
       <c r="C365" t="s">
-        <v>240</v>
+        <v>103</v>
       </c>
       <c r="E365" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="F365">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="G365" t="s">
         <v>16</v>
@@ -12493,24 +12493,24 @@
         <v>16</v>
       </c>
       <c r="I365" t="s">
-        <v>293</v>
+        <v>803</v>
       </c>
     </row>
     <row r="366" spans="1:9">
       <c r="A366" t="s">
-        <v>830</v>
+        <v>841</v>
       </c>
       <c r="B366" t="s">
-        <v>831</v>
+        <v>842</v>
       </c>
       <c r="C366" t="s">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="E366" t="s">
-        <v>346</v>
+        <v>241</v>
       </c>
       <c r="F366">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G366" t="s">
         <v>16</v>
@@ -12519,24 +12519,24 @@
         <v>16</v>
       </c>
       <c r="I366" t="s">
-        <v>355</v>
+        <v>293</v>
       </c>
     </row>
     <row r="367" spans="1:9">
       <c r="A367" t="s">
-        <v>730</v>
+        <v>832</v>
       </c>
       <c r="B367" t="s">
-        <v>731</v>
+        <v>833</v>
       </c>
       <c r="C367" t="s">
         <v>120</v>
       </c>
       <c r="E367" t="s">
-        <v>688</v>
+        <v>346</v>
       </c>
       <c r="F367">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G367" t="s">
         <v>16</v>
@@ -12545,56 +12545,56 @@
         <v>16</v>
       </c>
       <c r="I367" t="s">
-        <v>559</v>
+        <v>355</v>
       </c>
     </row>
     <row r="368" spans="1:9">
       <c r="A368" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B368" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C368" t="s">
         <v>277</v>
       </c>
       <c r="E368" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F368">
         <v>1.0</v>
       </c>
       <c r="G368" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H368" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="I368" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="369" spans="1:9">
       <c r="A369" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B369" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C369" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E369" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F369">
         <v>1.0</v>
       </c>
       <c r="G369" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H369" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="I369" t="s">
         <v>152</v>
@@ -12602,25 +12602,25 @@
     </row>
     <row r="370" spans="1:9">
       <c r="A370" t="s">
+        <v>837</v>
+      </c>
+      <c r="B370" t="s">
         <v>838</v>
       </c>
-      <c r="B370" t="s">
-        <v>839</v>
-      </c>
       <c r="C370" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E370" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F370">
         <v>2.0</v>
       </c>
       <c r="G370" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H370" t="s">
-        <v>740</v>
+        <v>716</v>
       </c>
       <c r="I370" t="s">
         <v>160</v>
@@ -12628,36 +12628,36 @@
     </row>
     <row r="371" spans="1:9">
       <c r="A371" t="s">
+        <v>795</v>
+      </c>
+      <c r="B371" t="s">
         <v>796</v>
-      </c>
-      <c r="B371" t="s">
-        <v>797</v>
       </c>
       <c r="C371" t="s">
         <v>398</v>
       </c>
       <c r="E371" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F371">
         <v>1.0</v>
       </c>
       <c r="G371" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H371" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="I371" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="372" spans="1:9">
       <c r="A372" t="s">
+        <v>510</v>
+      </c>
+      <c r="B372" t="s">
         <v>511</v>
-      </c>
-      <c r="B372" t="s">
-        <v>512</v>
       </c>
       <c r="C372" t="s">
         <v>120</v>
@@ -12669,10 +12669,10 @@
         <v>22.0</v>
       </c>
       <c r="G372" t="s">
+        <v>843</v>
+      </c>
+      <c r="H372" t="s">
         <v>844</v>
-      </c>
-      <c r="H372" t="s">
-        <v>845</v>
       </c>
       <c r="I372" t="s">
         <v>359</v>
@@ -12680,25 +12680,25 @@
     </row>
     <row r="373" spans="1:9">
       <c r="A373" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B373" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C373" t="s">
         <v>398</v>
       </c>
       <c r="E373" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F373">
         <v>1.0</v>
       </c>
       <c r="G373" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H373" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="I373" t="s">
         <v>152</v>
@@ -12706,51 +12706,51 @@
     </row>
     <row r="374" spans="1:9">
       <c r="A374" t="s">
+        <v>837</v>
+      </c>
+      <c r="B374" t="s">
         <v>838</v>
-      </c>
-      <c r="B374" t="s">
-        <v>839</v>
       </c>
       <c r="C374" t="s">
         <v>325</v>
       </c>
       <c r="E374" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F374">
         <v>1.0</v>
       </c>
       <c r="G374" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H374" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="I374" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="375" spans="1:9">
       <c r="A375" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B375" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C375" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E375" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F375">
         <v>1.0</v>
       </c>
       <c r="G375" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H375" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="I375" t="s">
         <v>152</v>
@@ -12758,25 +12758,25 @@
     </row>
     <row r="376" spans="1:9">
       <c r="A376" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B376" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C376" t="s">
         <v>398</v>
       </c>
       <c r="E376" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F376">
         <v>1.0</v>
       </c>
       <c r="G376" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H376" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="I376" t="s">
         <v>152</v>
@@ -12793,163 +12793,166 @@
         <v>398</v>
       </c>
       <c r="E377" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F377">
         <v>1.0</v>
       </c>
       <c r="G377" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H377" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="I377" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="378" spans="1:9">
       <c r="A378" t="s">
+        <v>795</v>
+      </c>
+      <c r="B378" t="s">
         <v>796</v>
-      </c>
-      <c r="B378" t="s">
-        <v>797</v>
       </c>
       <c r="C378" t="s">
         <v>277</v>
       </c>
       <c r="E378" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F378">
         <v>1.0</v>
       </c>
       <c r="G378" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H378" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="I378" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="379" spans="1:9">
       <c r="A379" t="s">
+        <v>845</v>
+      </c>
+      <c r="B379" t="s">
         <v>846</v>
-      </c>
-      <c r="B379" t="s">
-        <v>847</v>
       </c>
       <c r="C379" t="s">
         <v>277</v>
       </c>
       <c r="E379" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F379">
         <v>1.0</v>
       </c>
       <c r="G379" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H379" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="I379" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="380" spans="1:9">
       <c r="A380" t="s">
+        <v>845</v>
+      </c>
+      <c r="B380" t="s">
         <v>846</v>
-      </c>
-      <c r="B380" t="s">
-        <v>847</v>
       </c>
       <c r="C380" t="s">
         <v>375</v>
       </c>
       <c r="E380" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F380">
         <v>1.0</v>
       </c>
       <c r="G380" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="H380" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="I380" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="381" spans="1:9">
       <c r="A381" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="B381" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="C381" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="E381" t="s">
         <v>688</v>
       </c>
       <c r="F381">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="G381" t="s">
-        <v>848</v>
+        <v>16</v>
       </c>
       <c r="H381" t="s">
-        <v>849</v>
+        <v>16</v>
       </c>
       <c r="I381" t="s">
-        <v>354</v>
+        <v>667</v>
       </c>
     </row>
     <row r="382" spans="1:9">
       <c r="A382" t="s">
-        <v>850</v>
+        <v>747</v>
       </c>
       <c r="B382" t="s">
-        <v>851</v>
-      </c>
-      <c r="C382">
-        <v>40</v>
+        <v>748</v>
+      </c>
+      <c r="C382" t="s">
+        <v>103</v>
       </c>
       <c r="E382" t="s">
-        <v>852</v>
+        <v>688</v>
       </c>
       <c r="F382">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G382" t="s">
-        <v>16</v>
+        <v>847</v>
       </c>
       <c r="H382" t="s">
-        <v>16</v>
+        <v>848</v>
       </c>
       <c r="I382" t="s">
-        <v>853</v>
+        <v>354</v>
       </c>
     </row>
     <row r="383" spans="1:9">
       <c r="A383" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="B383" t="s">
-        <v>855</v>
+        <v>850</v>
+      </c>
+      <c r="C383">
+        <v>40</v>
       </c>
       <c r="E383" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="F383">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G383" t="s">
         <v>16</v>
@@ -12958,21 +12961,21 @@
         <v>16</v>
       </c>
       <c r="I383" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
     </row>
     <row r="384" spans="1:9">
       <c r="A384" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="B384" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="E384" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="F384">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G384" t="s">
         <v>16</v>
@@ -12981,24 +12984,21 @@
         <v>16</v>
       </c>
       <c r="I384" t="s">
-        <v>747</v>
+        <v>856</v>
       </c>
     </row>
     <row r="385" spans="1:9">
       <c r="A385" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="B385" t="s">
-        <v>862</v>
-      </c>
-      <c r="C385" t="s">
-        <v>120</v>
+        <v>858</v>
       </c>
       <c r="E385" t="s">
-        <v>230</v>
+        <v>859</v>
       </c>
       <c r="F385">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="G385" t="s">
         <v>16</v>
@@ -13007,24 +13007,24 @@
         <v>16</v>
       </c>
       <c r="I385" t="s">
-        <v>863</v>
+        <v>746</v>
       </c>
     </row>
     <row r="386" spans="1:9">
       <c r="A386" t="s">
+        <v>860</v>
+      </c>
+      <c r="B386" t="s">
         <v>861</v>
       </c>
-      <c r="B386" t="s">
-        <v>862</v>
-      </c>
       <c r="C386" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="E386" t="s">
         <v>230</v>
       </c>
       <c r="F386">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
       <c r="G386" t="s">
         <v>16</v>
@@ -13033,24 +13033,24 @@
         <v>16</v>
       </c>
       <c r="I386" t="s">
-        <v>237</v>
+        <v>862</v>
       </c>
     </row>
     <row r="387" spans="1:9">
       <c r="A387" t="s">
-        <v>842</v>
+        <v>860</v>
       </c>
       <c r="B387" t="s">
-        <v>843</v>
+        <v>861</v>
       </c>
       <c r="C387" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="E387" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="F387">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="G387" t="s">
         <v>16</v>
@@ -13059,24 +13059,24 @@
         <v>16</v>
       </c>
       <c r="I387" t="s">
-        <v>293</v>
+        <v>237</v>
       </c>
     </row>
     <row r="388" spans="1:9">
       <c r="A388" t="s">
-        <v>794</v>
+        <v>841</v>
       </c>
       <c r="B388" t="s">
-        <v>795</v>
+        <v>842</v>
       </c>
       <c r="C388" t="s">
         <v>117</v>
       </c>
       <c r="E388" t="s">
-        <v>346</v>
+        <v>241</v>
       </c>
       <c r="F388">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G388" t="s">
         <v>16</v>
@@ -13085,24 +13085,24 @@
         <v>16</v>
       </c>
       <c r="I388" t="s">
-        <v>736</v>
+        <v>293</v>
       </c>
     </row>
     <row r="389" spans="1:9">
       <c r="A389" t="s">
-        <v>830</v>
+        <v>793</v>
       </c>
       <c r="B389" t="s">
-        <v>831</v>
+        <v>794</v>
       </c>
       <c r="C389" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E389" t="s">
         <v>346</v>
       </c>
       <c r="F389">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="G389" t="s">
         <v>16</v>
@@ -13111,15 +13111,15 @@
         <v>16</v>
       </c>
       <c r="I389" t="s">
-        <v>840</v>
+        <v>737</v>
       </c>
     </row>
     <row r="390" spans="1:9">
       <c r="A390" t="s">
-        <v>800</v>
+        <v>832</v>
       </c>
       <c r="B390" t="s">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="C390" t="s">
         <v>107</v>
@@ -13128,7 +13128,7 @@
         <v>346</v>
       </c>
       <c r="F390">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="G390" t="s">
         <v>16</v>
@@ -13137,24 +13137,24 @@
         <v>16</v>
       </c>
       <c r="I390" t="s">
-        <v>785</v>
+        <v>839</v>
       </c>
     </row>
     <row r="391" spans="1:9">
       <c r="A391" t="s">
-        <v>511</v>
+        <v>799</v>
       </c>
       <c r="B391" t="s">
-        <v>512</v>
+        <v>800</v>
       </c>
       <c r="C391" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E391" t="s">
         <v>346</v>
       </c>
       <c r="F391">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="G391" t="s">
         <v>16</v>
@@ -13163,24 +13163,24 @@
         <v>16</v>
       </c>
       <c r="I391" t="s">
-        <v>389</v>
+        <v>785</v>
       </c>
     </row>
     <row r="392" spans="1:9">
       <c r="A392" t="s">
-        <v>759</v>
+        <v>510</v>
       </c>
       <c r="B392" t="s">
-        <v>760</v>
+        <v>511</v>
       </c>
       <c r="C392" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E392" t="s">
         <v>346</v>
       </c>
       <c r="F392">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
       <c r="G392" t="s">
         <v>16</v>
@@ -13189,24 +13189,24 @@
         <v>16</v>
       </c>
       <c r="I392" t="s">
-        <v>482</v>
+        <v>389</v>
       </c>
     </row>
     <row r="393" spans="1:9">
       <c r="A393" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="B393" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="C393" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="E393" t="s">
-        <v>688</v>
+        <v>346</v>
       </c>
       <c r="F393">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
       <c r="G393" t="s">
         <v>16</v>
@@ -13215,7 +13215,7 @@
         <v>16</v>
       </c>
       <c r="I393" t="s">
-        <v>668</v>
+        <v>481</v>
       </c>
     </row>
     <row r="394" spans="1:9">
@@ -13241,15 +13241,15 @@
         <v>16</v>
       </c>
       <c r="I394" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="395" spans="1:9">
       <c r="A395" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B395" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C395" t="s">
         <v>117</v>
@@ -13267,15 +13267,15 @@
         <v>16</v>
       </c>
       <c r="I395" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="396" spans="1:9">
       <c r="A396" t="s">
-        <v>819</v>
+        <v>806</v>
       </c>
       <c r="B396" t="s">
-        <v>820</v>
+        <v>807</v>
       </c>
       <c r="C396" t="s">
         <v>103</v>
@@ -13293,18 +13293,18 @@
         <v>16</v>
       </c>
       <c r="I396" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
     <row r="397" spans="1:9">
       <c r="A397" t="s">
+        <v>864</v>
+      </c>
+      <c r="B397" t="s">
         <v>865</v>
       </c>
-      <c r="B397" t="s">
+      <c r="E397" t="s">
         <v>866</v>
-      </c>
-      <c r="E397" t="s">
-        <v>867</v>
       </c>
       <c r="F397">
         <v>1.0</v>
@@ -13321,13 +13321,13 @@
     </row>
     <row r="398" spans="1:9">
       <c r="A398" t="s">
+        <v>867</v>
+      </c>
+      <c r="B398" t="s">
         <v>868</v>
       </c>
-      <c r="B398" t="s">
-        <v>869</v>
-      </c>
       <c r="E398" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F398">
         <v>1.0</v>
@@ -13339,18 +13339,18 @@
         <v>16</v>
       </c>
       <c r="I398" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="399" spans="1:9">
       <c r="A399" t="s">
+        <v>870</v>
+      </c>
+      <c r="B399" t="s">
         <v>871</v>
       </c>
-      <c r="B399" t="s">
-        <v>872</v>
-      </c>
       <c r="E399" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F399">
         <v>1.0</v>
@@ -13362,21 +13362,21 @@
         <v>16</v>
       </c>
       <c r="I399" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="400" spans="1:9">
       <c r="A400" t="s">
+        <v>554</v>
+      </c>
+      <c r="B400" t="s">
         <v>555</v>
-      </c>
-      <c r="B400" t="s">
-        <v>556</v>
       </c>
       <c r="C400" t="s">
         <v>277</v>
       </c>
       <c r="E400" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F400">
         <v>5.0</v>
@@ -13393,10 +13393,10 @@
     </row>
     <row r="401" spans="1:9">
       <c r="A401" t="s">
+        <v>872</v>
+      </c>
+      <c r="B401" t="s">
         <v>873</v>
-      </c>
-      <c r="B401" t="s">
-        <v>874</v>
       </c>
       <c r="C401">
         <v>44</v>
@@ -13414,21 +13414,21 @@
         <v>16</v>
       </c>
       <c r="I401" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="402" spans="1:9">
       <c r="A402" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B402" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C402" t="s">
         <v>277</v>
       </c>
       <c r="E402" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F402">
         <v>8.0</v>
@@ -13440,21 +13440,21 @@
         <v>16</v>
       </c>
       <c r="I402" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="403" spans="1:9">
       <c r="A403" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B403" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C403" t="s">
         <v>375</v>
       </c>
       <c r="E403" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F403">
         <v>14.0</v>
@@ -13466,21 +13466,21 @@
         <v>16</v>
       </c>
       <c r="I403" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="404" spans="1:9">
       <c r="A404" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B404" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C404" t="s">
         <v>325</v>
       </c>
       <c r="E404" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F404">
         <v>11.0</v>
@@ -13492,21 +13492,21 @@
         <v>16</v>
       </c>
       <c r="I404" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="405" spans="1:9">
       <c r="A405" t="s">
+        <v>878</v>
+      </c>
+      <c r="B405" t="s">
         <v>879</v>
-      </c>
-      <c r="B405" t="s">
-        <v>880</v>
       </c>
       <c r="C405" t="s">
         <v>277</v>
       </c>
       <c r="E405" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F405">
         <v>7.0</v>
@@ -13518,21 +13518,21 @@
         <v>16</v>
       </c>
       <c r="I405" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="406" spans="1:9">
       <c r="A406" t="s">
+        <v>878</v>
+      </c>
+      <c r="B406" t="s">
         <v>879</v>
-      </c>
-      <c r="B406" t="s">
-        <v>880</v>
       </c>
       <c r="C406" t="s">
         <v>375</v>
       </c>
       <c r="E406" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F406">
         <v>15.0</v>
@@ -13544,21 +13544,21 @@
         <v>16</v>
       </c>
       <c r="I406" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="407" spans="1:9">
       <c r="A407" t="s">
+        <v>878</v>
+      </c>
+      <c r="B407" t="s">
         <v>879</v>
-      </c>
-      <c r="B407" t="s">
-        <v>880</v>
       </c>
       <c r="C407" t="s">
         <v>325</v>
       </c>
       <c r="E407" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F407">
         <v>7.0</v>
@@ -13570,21 +13570,21 @@
         <v>16</v>
       </c>
       <c r="I407" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="408" spans="1:9">
       <c r="A408" t="s">
+        <v>878</v>
+      </c>
+      <c r="B408" t="s">
         <v>879</v>
       </c>
-      <c r="B408" t="s">
-        <v>880</v>
-      </c>
       <c r="C408" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E408" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F408">
         <v>8.0</v>
@@ -13596,21 +13596,21 @@
         <v>16</v>
       </c>
       <c r="I408" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="409" spans="1:9">
       <c r="A409" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B409" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C409" t="s">
         <v>398</v>
       </c>
       <c r="E409" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F409">
         <v>4.0</v>
@@ -13622,21 +13622,21 @@
         <v>16</v>
       </c>
       <c r="I409" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="410" spans="1:9">
       <c r="A410" t="s">
+        <v>884</v>
+      </c>
+      <c r="B410" t="s">
         <v>885</v>
-      </c>
-      <c r="B410" t="s">
-        <v>886</v>
       </c>
       <c r="C410" t="s">
         <v>277</v>
       </c>
       <c r="E410" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F410">
         <v>6.0</v>
@@ -13648,21 +13648,21 @@
         <v>16</v>
       </c>
       <c r="I410" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="411" spans="1:9">
       <c r="A411" t="s">
+        <v>884</v>
+      </c>
+      <c r="B411" t="s">
         <v>885</v>
-      </c>
-      <c r="B411" t="s">
-        <v>886</v>
       </c>
       <c r="C411" t="s">
         <v>375</v>
       </c>
       <c r="E411" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F411">
         <v>4.0</v>
@@ -13674,24 +13674,24 @@
         <v>16</v>
       </c>
       <c r="I411" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="412" spans="1:9">
       <c r="A412" t="s">
+        <v>884</v>
+      </c>
+      <c r="B412" t="s">
         <v>885</v>
-      </c>
-      <c r="B412" t="s">
-        <v>886</v>
       </c>
       <c r="C412" t="s">
         <v>325</v>
       </c>
       <c r="E412" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F412">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G412" t="s">
         <v>16</v>
@@ -13700,21 +13700,21 @@
         <v>16</v>
       </c>
       <c r="I412" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="413" spans="1:9">
       <c r="A413" t="s">
+        <v>884</v>
+      </c>
+      <c r="B413" t="s">
         <v>885</v>
       </c>
-      <c r="B413" t="s">
-        <v>886</v>
-      </c>
       <c r="C413" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E413" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F413">
         <v>10.0</v>
@@ -13740,7 +13740,7 @@
         <v>277</v>
       </c>
       <c r="E414" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F414">
         <v>3.0</v>
@@ -13752,7 +13752,7 @@
         <v>16</v>
       </c>
       <c r="I414" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="415" spans="1:9">
@@ -13766,7 +13766,7 @@
         <v>325</v>
       </c>
       <c r="E415" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F415">
         <v>7.0</v>
@@ -13792,7 +13792,7 @@
         <v>398</v>
       </c>
       <c r="E416" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F416">
         <v>4.0</v>
@@ -13818,7 +13818,7 @@
         <v>277</v>
       </c>
       <c r="E417" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F417">
         <v>4.0</v>
@@ -13844,7 +13844,7 @@
         <v>325</v>
       </c>
       <c r="E418" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F418">
         <v>3.0</v>
@@ -13867,10 +13867,10 @@
         <v>894</v>
       </c>
       <c r="C419" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E419" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F419">
         <v>4.0</v>
@@ -13896,7 +13896,7 @@
         <v>398</v>
       </c>
       <c r="E420" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F420">
         <v>2.0</v>
@@ -13922,7 +13922,7 @@
         <v>277</v>
       </c>
       <c r="E421" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F421">
         <v>4.0</v>
@@ -13948,7 +13948,7 @@
         <v>375</v>
       </c>
       <c r="E422" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F422">
         <v>7.0</v>
@@ -13974,7 +13974,7 @@
         <v>325</v>
       </c>
       <c r="E423" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F423">
         <v>6.0</v>
@@ -13997,10 +13997,10 @@
         <v>898</v>
       </c>
       <c r="C424" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E424" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F424">
         <v>4.0</v>
@@ -14026,7 +14026,7 @@
         <v>398</v>
       </c>
       <c r="E425" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F425">
         <v>3.0</v>
@@ -14052,7 +14052,7 @@
         <v>277</v>
       </c>
       <c r="E426" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F426">
         <v>3.0</v>
@@ -14078,7 +14078,7 @@
         <v>375</v>
       </c>
       <c r="E427" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F427">
         <v>6.0</v>
@@ -14090,7 +14090,7 @@
         <v>16</v>
       </c>
       <c r="I427" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="428" spans="1:9">
@@ -14104,7 +14104,7 @@
         <v>325</v>
       </c>
       <c r="E428" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F428">
         <v>6.0</v>
@@ -14116,7 +14116,7 @@
         <v>16</v>
       </c>
       <c r="I428" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="429" spans="1:9">
@@ -14127,10 +14127,10 @@
         <v>903</v>
       </c>
       <c r="C429" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E429" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F429">
         <v>3.0</v>
@@ -14156,7 +14156,7 @@
         <v>398</v>
       </c>
       <c r="E430" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F430">
         <v>1.0</v>
@@ -14182,7 +14182,7 @@
         <v>277</v>
       </c>
       <c r="E431" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F431">
         <v>1.0</v>
@@ -14208,7 +14208,7 @@
         <v>375</v>
       </c>
       <c r="E432" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F432">
         <v>4.0</v>
@@ -14234,7 +14234,7 @@
         <v>325</v>
       </c>
       <c r="E433" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F433">
         <v>3.0</v>
@@ -14257,10 +14257,10 @@
         <v>907</v>
       </c>
       <c r="C434" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E434" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F434">
         <v>2.0</v>
@@ -14286,7 +14286,7 @@
         <v>398</v>
       </c>
       <c r="E435" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F435">
         <v>2.0</v>
@@ -14312,7 +14312,7 @@
         <v>277</v>
       </c>
       <c r="E436" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F436">
         <v>5.0</v>
@@ -14324,7 +14324,7 @@
         <v>16</v>
       </c>
       <c r="I436" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="437" spans="1:9">
@@ -14338,7 +14338,7 @@
         <v>375</v>
       </c>
       <c r="E437" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F437">
         <v>10.0</v>
@@ -14364,7 +14364,7 @@
         <v>325</v>
       </c>
       <c r="E438" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F438">
         <v>10.0</v>
@@ -14387,10 +14387,10 @@
         <v>909</v>
       </c>
       <c r="C439" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E439" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F439">
         <v>6.0</v>
@@ -14416,7 +14416,7 @@
         <v>398</v>
       </c>
       <c r="E440" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F440">
         <v>4.0</v>
@@ -14433,10 +14433,10 @@
     </row>
     <row r="441" spans="1:9">
       <c r="A441" t="s">
+        <v>860</v>
+      </c>
+      <c r="B441" t="s">
         <v>861</v>
-      </c>
-      <c r="B441" t="s">
-        <v>862</v>
       </c>
       <c r="C441" t="s">
         <v>117</v>
@@ -14459,10 +14459,10 @@
     </row>
     <row r="442" spans="1:9">
       <c r="A442" t="s">
+        <v>497</v>
+      </c>
+      <c r="B442" t="s">
         <v>498</v>
-      </c>
-      <c r="B442" t="s">
-        <v>499</v>
       </c>
       <c r="C442" t="s">
         <v>107</v>
@@ -14480,7 +14480,7 @@
         <v>16</v>
       </c>
       <c r="I442" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="443" spans="1:9">
@@ -14494,7 +14494,7 @@
         <v>277</v>
       </c>
       <c r="E443" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F443">
         <v>3.0</v>
@@ -14520,7 +14520,7 @@
         <v>325</v>
       </c>
       <c r="E444" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F444">
         <v>2.0</v>
@@ -14546,7 +14546,7 @@
         <v>398</v>
       </c>
       <c r="E445" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F445">
         <v>2.0</v>
@@ -14569,10 +14569,10 @@
         <v>913</v>
       </c>
       <c r="C446" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E446" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F446">
         <v>1.0</v>
@@ -14598,7 +14598,7 @@
         <v>375</v>
       </c>
       <c r="E447" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F447">
         <v>4.0</v>
@@ -14610,21 +14610,21 @@
         <v>16</v>
       </c>
       <c r="I447" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="448" spans="1:9">
       <c r="A448" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B448" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C448" t="s">
         <v>398</v>
       </c>
       <c r="E448" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F448">
         <v>1.0</v>
